--- a/scenari_kalab.xlsx
+++ b/scenari_kalab.xlsx
@@ -14,8 +14,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stagionalità" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenari" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equilibrio" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Logistica" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confronto accordi" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ambizioso - cosa serve" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Logistica" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confronto accordi" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,8 +25,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -99,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -131,7 +133,11 @@
     <xf numFmtId="3" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -633,6 +639,272 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>Cosa succede a un ordine medio con diversi accordi (scenario medio, anno 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="40" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Accordo</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Base (lordo/netto)</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Quota %</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>B2Brand per ordine (€)</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Kalab margine per ordine (€)</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Kalab margine % prezzo</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Commento</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>50% dell'incasso lordo (proposta di Kalab)</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>lordo</t>
+        </is>
+      </c>
+      <c r="C3" s="26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D3" s="12">
+        <f>IF(B3="lordo",'Conti per prodotto'!$H$10,'Conti per prodotto'!$G$10)*C3</f>
+        <v/>
+      </c>
+      <c r="E3" s="12">
+        <f>'Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10-D3</f>
+        <v/>
+      </c>
+      <c r="F3" s="30">
+        <f>E3/'Conti per prodotto'!$B$10</f>
+        <v/>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Quota su merce + spedizione incassata, IVA inclusa: la lettura letterale di «50% dell'incasso».</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>50% dell'incassato netto (senza IVA, spedizione e commissioni)</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>netto</t>
+        </is>
+      </c>
+      <c r="C4" s="26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D4" s="12">
+        <f>IF(B4="lordo",'Conti per prodotto'!$H$10,'Conti per prodotto'!$G$10)*C4</f>
+        <v/>
+      </c>
+      <c r="E4" s="12">
+        <f>'Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10-D4</f>
+        <v/>
+      </c>
+      <c r="F4" s="30">
+        <f>E4/'Conti per prodotto'!$B$10</f>
+        <v/>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Stessa percentuale, base più piccola: è la prassi del settore (07 B1e).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>40% dell'incassato netto</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>netto</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D5" s="12">
+        <f>IF(B5="lordo",'Conti per prodotto'!$H$10,'Conti per prodotto'!$G$10)*C5</f>
+        <v/>
+      </c>
+      <c r="E5" s="12">
+        <f>'Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10-D5</f>
+        <v/>
+      </c>
+      <c r="F5" s="30">
+        <f>E5/'Conti per prodotto'!$B$10</f>
+        <v/>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Primo scaglione proposto: fino al rientro documentato dell'anticipo di B2Brand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>30% dell'incassato netto</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>netto</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D6" s="12">
+        <f>IF(B6="lordo",'Conti per prodotto'!$H$10,'Conti per prodotto'!$G$10)*C6</f>
+        <v/>
+      </c>
+      <c r="E6" s="12">
+        <f>'Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10-D6</f>
+        <v/>
+      </c>
+      <c r="F6" s="30">
+        <f>E6/'Conti per prodotto'!$B$10</f>
+        <v/>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Secondo scaglione, dopo il rientro. Fascia alta dell'outsourcing italiano (15-30%, 07).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>20% dell'incassato netto</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>netto</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D7" s="12">
+        <f>IF(B7="lordo",'Conti per prodotto'!$H$10,'Conti per prodotto'!$G$10)*C7</f>
+        <v/>
+      </c>
+      <c r="E7" s="12">
+        <f>'Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10-D7</f>
+        <v/>
+      </c>
+      <c r="F7" s="30">
+        <f>E7/'Conti per prodotto'!$B$10</f>
+        <v/>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Terzo scaglione sopra una soglia annua. Sotto, B2Brand non copre nemmeno le ore.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>10% netto sugli ordini B2B passati dal sito</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>netto</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D8" s="12">
+        <f>IF(B8="lordo",'Conti per prodotto'!$H$10,'Conti per prodotto'!$G$10)*C8</f>
+        <v/>
+      </c>
+      <c r="E8" s="12">
+        <f>'Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10-D8</f>
+        <v/>
+      </c>
+      <c r="F8" s="30">
+        <f>E8/'Conti per prodotto'!$B$10</f>
+        <v/>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Per ristoranti, bar e botteghe che ordinano dal sito con listino riservato: volumi alti, margine basso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Lettura: l'ordine medio è quello del foglio Conti (mix di categorie). Il margine di Kalab è dopo prodotto, imballo, spedizione vera e perdite. Per vedere l'effetto sui 36 mesi, cambiare quota e base nel foglio Ipotesi.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -9738,6 +10010,429 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>Scenario ambizioso: cosa deve succedere ogni mese, a regime, per arrivarci</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Celle azzurre = valori di riferimento dai benchmark (fonte in ricerca/ambizioso/02_benchmark_e_numeri.md). Ordini e pubblicità arrivano dal foglio Scenari, colonna Ambizioso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Voce</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Anno 1</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Anno 2</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>Anno 3</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>Nota</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Tasso di conversione del sito</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="C5" s="25" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D5" s="25" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>tasso di conversione del sito (ordini ÷ visite)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Ordini da clienti che ritornano</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C6" s="26" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>quota degli ordini fatta da clienti che hanno già comprato</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Costo di un clic a pagamento (€)</t>
+        </is>
+      </c>
+      <c r="B7" s="27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C7" s="27" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D7" s="27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>costo medio di un clic a pagamento (€)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Costo pubblicitario per un cliente nuovo (€)</t>
+        </is>
+      </c>
+      <c r="B8" s="27" t="n">
+        <v>25</v>
+      </c>
+      <c r="C8" s="27" t="n">
+        <v>25</v>
+      </c>
+      <c r="D8" s="27" t="n">
+        <v>25</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>costo pubblicitario per un cliente nuovo (€)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Quota degli ordini dalla newsletter</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C9" s="26" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>quota degli ordini che arriva dalla newsletter</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Ordini al mese ogni 1.000 iscritti</t>
+        </is>
+      </c>
+      <c r="B10" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="D10" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ordini al mese ogni 1.000 iscritti alla newsletter</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Ordini al mese (obiettivo a regime)</t>
+        </is>
+      </c>
+      <c r="B12" s="20">
+        <f>Scenari!$D$3</f>
+        <v/>
+      </c>
+      <c r="C12" s="20">
+        <f>Scenari!$D$4</f>
+        <v/>
+      </c>
+      <c r="D12" s="20">
+        <f>Scenari!$D$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Pubblicità al mese (€)</t>
+        </is>
+      </c>
+      <c r="B13" s="20">
+        <f>Scenari!$D$7</f>
+        <v/>
+      </c>
+      <c r="C13" s="20">
+        <f>Scenari!$D$8</f>
+        <v/>
+      </c>
+      <c r="D13" s="20">
+        <f>Scenari!$D$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Visite al mese necessarie</t>
+        </is>
+      </c>
+      <c r="B14" s="20">
+        <f>ROUND(B12/B5,0)</f>
+        <v/>
+      </c>
+      <c r="C14" s="20">
+        <f>ROUND(C12/C5,0)</f>
+        <v/>
+      </c>
+      <c r="D14" s="20">
+        <f>ROUND(D12/D5,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>…di cui comprate con la pubblicità</t>
+        </is>
+      </c>
+      <c r="B15" s="20">
+        <f>ROUND(B13/B7,0)</f>
+        <v/>
+      </c>
+      <c r="C15" s="20">
+        <f>ROUND(C13/C7,0)</f>
+        <v/>
+      </c>
+      <c r="D15" s="20">
+        <f>ROUND(D13/D7,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>…di cui da portare gratis (Google, social, eventi, passaparola)</t>
+        </is>
+      </c>
+      <c r="B16" s="20">
+        <f>MAX(0,B14-B15)</f>
+        <v/>
+      </c>
+      <c r="C16" s="20">
+        <f>MAX(0,C14-C15)</f>
+        <v/>
+      </c>
+      <c r="D16" s="20">
+        <f>MAX(0,D14-D15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Clienti nuovi al mese</t>
+        </is>
+      </c>
+      <c r="B17" s="20">
+        <f>ROUND(B12*(1-B6),0)</f>
+        <v/>
+      </c>
+      <c r="C17" s="20">
+        <f>ROUND(C12*(1-C6),0)</f>
+        <v/>
+      </c>
+      <c r="D17" s="20">
+        <f>ROUND(D12*(1-D6),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>…di cui comprati con la pubblicità</t>
+        </is>
+      </c>
+      <c r="B18" s="20">
+        <f>ROUND(B13/B8,0)</f>
+        <v/>
+      </c>
+      <c r="C18" s="20">
+        <f>ROUND(C13/C8,0)</f>
+        <v/>
+      </c>
+      <c r="D18" s="20">
+        <f>ROUND(D13/D8,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>…di cui da trovare gratis</t>
+        </is>
+      </c>
+      <c r="B19" s="20">
+        <f>MAX(0,B17-B18)</f>
+        <v/>
+      </c>
+      <c r="C19" s="20">
+        <f>MAX(0,C17-C18)</f>
+        <v/>
+      </c>
+      <c r="D19" s="20">
+        <f>MAX(0,D17-D18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Ordini di clienti che ritornano</t>
+        </is>
+      </c>
+      <c r="B20" s="20">
+        <f>ROUND(B12*B6,0)</f>
+        <v/>
+      </c>
+      <c r="C20" s="20">
+        <f>ROUND(C12*C6,0)</f>
+        <v/>
+      </c>
+      <c r="D20" s="20">
+        <f>ROUND(D12*D6,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Ordini dalla newsletter</t>
+        </is>
+      </c>
+      <c r="B21" s="20">
+        <f>ROUND(B12*B9,0)</f>
+        <v/>
+      </c>
+      <c r="C21" s="20">
+        <f>ROUND(C12*C9,0)</f>
+        <v/>
+      </c>
+      <c r="D21" s="20">
+        <f>ROUND(D12*D9,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Iscritti alla newsletter necessari</t>
+        </is>
+      </c>
+      <c r="B22" s="20">
+        <f>ROUND(B21/B10*1000,0)</f>
+        <v/>
+      </c>
+      <c r="C22" s="20">
+        <f>ROUND(C21/C10*1000,0)</f>
+        <v/>
+      </c>
+      <c r="D22" s="20">
+        <f>ROUND(D21/D10*1000,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Ordini al giorno</t>
+        </is>
+      </c>
+      <c r="B23" s="29">
+        <f>ROUND(B12/30,1)</f>
+        <v/>
+      </c>
+      <c r="C23" s="29">
+        <f>ROUND(C12/30,1)</f>
+        <v/>
+      </c>
+      <c r="D23" s="29">
+        <f>ROUND(D12/30,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Lettura: la riga «da portare gratis» è il lavoro vero del marchio. Se è troppo alta rispetto a quello che Google, social, eventi e B2B possono dare, l'ambizioso non si raggiunge con quella pubblicità.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -10150,270 +10845,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="80" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="17" t="inlineStr">
-        <is>
-          <t>Cosa succede a un ordine medio con diversi accordi (scenario medio, anno 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="40" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Accordo</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Base (lordo/netto)</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Quota %</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>B2Brand per ordine (€)</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Kalab margine per ordine (€)</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Kalab margine % prezzo</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>Commento</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>50% dell'incasso lordo (proposta di Kalab)</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>lordo</t>
-        </is>
-      </c>
-      <c r="C3" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D3" s="12">
-        <f>IF(B3="lordo",'Conti per prodotto'!$H$10,'Conti per prodotto'!$G$10)*C3</f>
-        <v/>
-      </c>
-      <c r="E3" s="12">
-        <f>'Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10-D3</f>
-        <v/>
-      </c>
-      <c r="F3" s="26">
-        <f>E3/'Conti per prodotto'!$B$10</f>
-        <v/>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Quota su merce + spedizione incassata, IVA inclusa: la lettura letterale di «50% dell'incasso».</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>50% dell'incassato netto (senza IVA, spedizione e commissioni)</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>netto</t>
-        </is>
-      </c>
-      <c r="C4" s="25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D4" s="12">
-        <f>IF(B4="lordo",'Conti per prodotto'!$H$10,'Conti per prodotto'!$G$10)*C4</f>
-        <v/>
-      </c>
-      <c r="E4" s="12">
-        <f>'Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10-D4</f>
-        <v/>
-      </c>
-      <c r="F4" s="26">
-        <f>E4/'Conti per prodotto'!$B$10</f>
-        <v/>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Stessa percentuale, base più piccola: è la prassi del settore (07 B1e).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>40% dell'incassato netto</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>netto</t>
-        </is>
-      </c>
-      <c r="C5" s="25" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D5" s="12">
-        <f>IF(B5="lordo",'Conti per prodotto'!$H$10,'Conti per prodotto'!$G$10)*C5</f>
-        <v/>
-      </c>
-      <c r="E5" s="12">
-        <f>'Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10-D5</f>
-        <v/>
-      </c>
-      <c r="F5" s="26">
-        <f>E5/'Conti per prodotto'!$B$10</f>
-        <v/>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Primo scaglione proposto: fino al rientro documentato dell'anticipo di B2Brand.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>30% dell'incassato netto</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>netto</t>
-        </is>
-      </c>
-      <c r="C6" s="25" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D6" s="12">
-        <f>IF(B6="lordo",'Conti per prodotto'!$H$10,'Conti per prodotto'!$G$10)*C6</f>
-        <v/>
-      </c>
-      <c r="E6" s="12">
-        <f>'Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10-D6</f>
-        <v/>
-      </c>
-      <c r="F6" s="26">
-        <f>E6/'Conti per prodotto'!$B$10</f>
-        <v/>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Secondo scaglione, dopo il rientro. Fascia alta dell'outsourcing italiano (15-30%, 07).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>20% dell'incassato netto</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>netto</t>
-        </is>
-      </c>
-      <c r="C7" s="25" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D7" s="12">
-        <f>IF(B7="lordo",'Conti per prodotto'!$H$10,'Conti per prodotto'!$G$10)*C7</f>
-        <v/>
-      </c>
-      <c r="E7" s="12">
-        <f>'Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10-D7</f>
-        <v/>
-      </c>
-      <c r="F7" s="26">
-        <f>E7/'Conti per prodotto'!$B$10</f>
-        <v/>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Terzo scaglione sopra una soglia annua. Sotto, B2Brand non copre nemmeno le ore.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>10% netto sugli ordini B2B passati dal sito</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>netto</t>
-        </is>
-      </c>
-      <c r="C8" s="25" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D8" s="12">
-        <f>IF(B8="lordo",'Conti per prodotto'!$H$10,'Conti per prodotto'!$G$10)*C8</f>
-        <v/>
-      </c>
-      <c r="E8" s="12">
-        <f>'Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10-D8</f>
-        <v/>
-      </c>
-      <c r="F8" s="26">
-        <f>E8/'Conti per prodotto'!$B$10</f>
-        <v/>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Per ristoranti, bar e botteghe che ordinano dal sito con listino riservato: volumi alti, margine basso.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Lettura: l'ordine medio è quello del foglio Conti (mix di categorie). Il margine di Kalab è dopo prodotto, imballo, spedizione vera e perdite. Per vedere l'effetto sui 36 mesi, cambiare quota e base nel foglio Ipotesi.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/scenari_kalab.xlsx
+++ b/scenari_kalab.xlsx
@@ -127,8 +127,8 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2233,10 +2233,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2255,6 +2257,16 @@
           <t>Nota</t>
         </is>
       </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Mese del piano nell'anno (1 = mese di avvio)</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Mese del piano × peso</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2270,6 +2282,13 @@
           <t>dopo Natale; semi iniziano</t>
         </is>
       </c>
+      <c r="D2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E2">
+        <f>D2*B2</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2285,6 +2304,13 @@
           <t>semi (Trends IT picco feb-mar)</t>
         </is>
       </c>
+      <c r="D3" t="n">
+        <v>12</v>
+      </c>
+      <c r="E3">
+        <f>D3*B3</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2300,6 +2326,13 @@
           <t>semi + piantine</t>
         </is>
       </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <f>D4*B4</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2315,6 +2348,13 @@
           <t>piantine (Trends: apr-mag)</t>
         </is>
       </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <f>D5*B5</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2330,6 +2370,13 @@
           <t>piantine</t>
         </is>
       </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <f>D6*B6</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2345,6 +2392,13 @@
           <t>estate: minimo (Trends giu-lug)</t>
         </is>
       </c>
+      <c r="D7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7">
+        <f>D7*B7</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2360,6 +2414,13 @@
           <t>minimo</t>
         </is>
       </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8">
+        <f>D8*B8</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2375,6 +2436,13 @@
           <t>raccolta: ricerche al massimo ma si compra in azienda/sagre</t>
         </is>
       </c>
+      <c r="D9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9">
+        <f>D9*B9</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2390,6 +2458,13 @@
           <t>Festival Diamante 9-13/9; raccolta</t>
         </is>
       </c>
+      <c r="D10" t="n">
+        <v>7</v>
+      </c>
+      <c r="E10">
+        <f>D10*B10</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2405,6 +2480,13 @@
           <t>secco nuovo; inizio regali</t>
         </is>
       </c>
+      <c r="D11" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11">
+        <f>D11*B11</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2420,6 +2502,13 @@
           <t>Black Friday; picco 'sauce piquante' FR</t>
         </is>
       </c>
+      <c r="D12" t="n">
+        <v>9</v>
+      </c>
+      <c r="E12">
+        <f>D12*B12</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2435,6 +2524,13 @@
           <t>Natale: picco acquisti online 5 e 16-17 dic (idealo)</t>
         </is>
       </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13">
+        <f>D13*B13</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -2444,6 +2540,15 @@
       </c>
       <c r="B14" s="7">
         <f>SUM(B2:B13)</f>
+        <v/>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Fattore di crescita (somma ÷ 12)</t>
+        </is>
+      </c>
+      <c r="E14" s="7">
+        <f>SUM(E2:E13)/12</f>
         <v/>
       </c>
     </row>
@@ -2545,7 +2650,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Ordini al mese, media anno 1</t>
+          <t>Ordini al mese a regime, anno 1 (dopo la rampa)</t>
         </is>
       </c>
       <c r="B3" s="5" t="n">
@@ -2743,6 +2848,49 @@
         <v/>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Tendenza a fine anno 2 (ordini al mese senza stagionalità)</t>
+        </is>
+      </c>
+      <c r="B13" s="19">
+        <f>B$3+(B$4*12-B$3*Stagionalità!$B$14)/Stagionalità!$E$14</f>
+        <v/>
+      </c>
+      <c r="C13" s="19">
+        <f>C$3+(C$4*12-C$3*Stagionalità!$B$14)/Stagionalità!$E$14</f>
+        <v/>
+      </c>
+      <c r="D13" s="19">
+        <f>D$3+(D$4*12-D$3*Stagionalità!$B$14)/Stagionalità!$E$14</f>
+        <v/>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Crescita continua: dalla fine dell'anno 1 gli ordini salgono in linea retta, con lo stesso totale annuo di «media × 12». Niente salti a marzo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Tendenza a fine anno 3 (ordini al mese senza stagionalità)</t>
+        </is>
+      </c>
+      <c r="B14" s="19">
+        <f>B$13+(B$5*12-B$13*Stagionalità!$B$14)/Stagionalità!$E$14</f>
+        <v/>
+      </c>
+      <c r="C14" s="19">
+        <f>C$13+(C$5*12-C$13*Stagionalità!$B$14)/Stagionalità!$E$14</f>
+        <v/>
+      </c>
+      <c r="D14" s="19">
+        <f>D$13+(D$5*12-D$13*Stagionalità!$B$14)/Stagionalità!$E$14</f>
+        <v/>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" s="17" t="inlineStr">
         <is>
@@ -2835,7 +2983,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>(appoggio) mese B2Brand sopra obiettivo</t>
+          <t>(appoggio) mese a quota obiettivo</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
@@ -2910,7 +3058,7 @@
       </c>
       <c r="AD17" s="3" t="inlineStr">
         <is>
-          <t>(appoggio) mese B2Brand sopra obiettivo</t>
+          <t>(appoggio) mese a quota obiettivo</t>
         </is>
       </c>
       <c r="AE17" s="3" t="inlineStr">
@@ -2985,7 +3133,7 @@
       </c>
       <c r="AT17" s="3" t="inlineStr">
         <is>
-          <t>(appoggio) mese B2Brand sopra obiettivo</t>
+          <t>(appoggio) mese a quota obiettivo</t>
         </is>
       </c>
       <c r="AU17" s="3" t="inlineStr">
@@ -3005,48 +3153,48 @@
         <f>ROUND(B$3*MIN(1,1/B$6)*Stagionalità!$B$4,0)</f>
         <v/>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="20">
         <f>C18*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="E18" s="19">
+      <c r="E18" s="20">
         <f>C18*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="F18" s="19">
+      <c r="F18" s="20">
         <f>'Costi B2Brand'!$C$6+'Costi B2Brand'!$B$6</f>
         <v/>
       </c>
-      <c r="G18" s="19">
+      <c r="G18" s="20">
         <f>B$7</f>
         <v/>
       </c>
-      <c r="H18" s="19">
+      <c r="H18" s="20">
         <f>0</f>
         <v/>
       </c>
-      <c r="I18" s="19">
+      <c r="I18" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(E18,F18+G18+H18+0.5*MAX(0,(E18-F18-G18)-H18)),C18*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="J18" s="20">
+      <c r="J18" s="19">
         <f>I18-F18-G18</f>
         <v/>
       </c>
-      <c r="K18" s="19">
+      <c r="K18" s="20">
         <f>J18</f>
         <v/>
       </c>
-      <c r="L18" s="20">
+      <c r="L18" s="19">
         <f>E18-I18</f>
         <v/>
       </c>
-      <c r="M18" s="19">
+      <c r="M18" s="20">
         <f>L18</f>
         <v/>
       </c>
       <c r="N18" s="21">
-        <f>IF(J18&gt;=Ipotesi!$B$14,A18,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(E18-F18-G18)/2,J18)&gt;=Ipotesi!$B$14,A18,"")</f>
         <v/>
       </c>
       <c r="O18" s="21">
@@ -3063,48 +3211,48 @@
         <f>ROUND(C$3*MIN(1,1/C$6)*Stagionalità!$B$4,0)</f>
         <v/>
       </c>
-      <c r="T18" s="19">
+      <c r="T18" s="20">
         <f>S18*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="U18" s="19">
+      <c r="U18" s="20">
         <f>S18*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="V18" s="19">
+      <c r="V18" s="20">
         <f>'Costi B2Brand'!$C$6+'Costi B2Brand'!$B$6</f>
         <v/>
       </c>
-      <c r="W18" s="19">
+      <c r="W18" s="20">
         <f>C$7</f>
         <v/>
       </c>
-      <c r="X18" s="19">
+      <c r="X18" s="20">
         <f>0</f>
         <v/>
       </c>
-      <c r="Y18" s="19">
+      <c r="Y18" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(U18,V18+W18+X18+0.5*MAX(0,(U18-V18-W18)-X18)),S18*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="Z18" s="20">
+      <c r="Z18" s="19">
         <f>Y18-V18-W18</f>
         <v/>
       </c>
-      <c r="AA18" s="19">
+      <c r="AA18" s="20">
         <f>Z18</f>
         <v/>
       </c>
-      <c r="AB18" s="20">
+      <c r="AB18" s="19">
         <f>U18-Y18</f>
         <v/>
       </c>
-      <c r="AC18" s="19">
+      <c r="AC18" s="20">
         <f>AB18</f>
         <v/>
       </c>
       <c r="AD18" s="21">
-        <f>IF(Z18&gt;=Ipotesi!$B$14,Q18,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(U18-V18-W18)/2,Z18)&gt;=Ipotesi!$B$14,Q18,"")</f>
         <v/>
       </c>
       <c r="AE18" s="21">
@@ -3121,48 +3269,48 @@
         <f>ROUND(D$3*MIN(1,1/D$6)*Stagionalità!$B$4,0)</f>
         <v/>
       </c>
-      <c r="AJ18" s="19">
+      <c r="AJ18" s="20">
         <f>AI18*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="AK18" s="19">
+      <c r="AK18" s="20">
         <f>AI18*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AL18" s="19">
+      <c r="AL18" s="20">
         <f>'Costi B2Brand'!$C$6+'Costi B2Brand'!$B$6</f>
         <v/>
       </c>
-      <c r="AM18" s="19">
+      <c r="AM18" s="20">
         <f>D$7</f>
         <v/>
       </c>
-      <c r="AN18" s="19">
+      <c r="AN18" s="20">
         <f>0</f>
         <v/>
       </c>
-      <c r="AO18" s="19">
+      <c r="AO18" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(AK18,AL18+AM18+AN18+0.5*MAX(0,(AK18-AL18-AM18)-AN18)),AI18*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AP18" s="20">
+      <c r="AP18" s="19">
         <f>AO18-AL18-AM18</f>
         <v/>
       </c>
-      <c r="AQ18" s="19">
+      <c r="AQ18" s="20">
         <f>AP18</f>
         <v/>
       </c>
-      <c r="AR18" s="20">
+      <c r="AR18" s="19">
         <f>AK18-AO18</f>
         <v/>
       </c>
-      <c r="AS18" s="19">
+      <c r="AS18" s="20">
         <f>AR18</f>
         <v/>
       </c>
       <c r="AT18" s="21">
-        <f>IF(AP18&gt;=Ipotesi!$B$14,AG18,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(AK18-AL18-AM18)/2,AP18)&gt;=Ipotesi!$B$14,AG18,"")</f>
         <v/>
       </c>
       <c r="AU18" s="21">
@@ -3181,48 +3329,48 @@
         <f>ROUND(B$3*MIN(1,2/B$6)*Stagionalità!$B$5,0)</f>
         <v/>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="20">
         <f>C19*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="E19" s="19">
+      <c r="E19" s="20">
         <f>C19*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="F19" s="19">
+      <c r="F19" s="20">
         <f>'Costi B2Brand'!$C$6</f>
         <v/>
       </c>
-      <c r="G19" s="19">
+      <c r="G19" s="20">
         <f>B$7</f>
         <v/>
       </c>
-      <c r="H19" s="19">
+      <c r="H19" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,H18-(E18-F18-G18)),0)</f>
         <v/>
       </c>
-      <c r="I19" s="19">
+      <c r="I19" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(E19,F19+G19+H19+0.5*MAX(0,(E19-F19-G19)-H19)),C19*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="J19" s="20">
+      <c r="J19" s="19">
         <f>I19-F19-G19</f>
         <v/>
       </c>
-      <c r="K19" s="19">
+      <c r="K19" s="20">
         <f>K18+J19</f>
         <v/>
       </c>
-      <c r="L19" s="20">
+      <c r="L19" s="19">
         <f>E19-I19</f>
         <v/>
       </c>
-      <c r="M19" s="19">
+      <c r="M19" s="20">
         <f>M18+L19</f>
         <v/>
       </c>
       <c r="N19" s="21">
-        <f>IF(J19&gt;=Ipotesi!$B$14,A19,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(E19-F19-G19)/2,J19)&gt;=Ipotesi!$B$14,A19,"")</f>
         <v/>
       </c>
       <c r="O19" s="21">
@@ -3239,48 +3387,48 @@
         <f>ROUND(C$3*MIN(1,2/C$6)*Stagionalità!$B$5,0)</f>
         <v/>
       </c>
-      <c r="T19" s="19">
+      <c r="T19" s="20">
         <f>S19*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="U19" s="19">
+      <c r="U19" s="20">
         <f>S19*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="V19" s="19">
+      <c r="V19" s="20">
         <f>'Costi B2Brand'!$C$6</f>
         <v/>
       </c>
-      <c r="W19" s="19">
+      <c r="W19" s="20">
         <f>C$7</f>
         <v/>
       </c>
-      <c r="X19" s="19">
+      <c r="X19" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,X18-(U18-V18-W18)),0)</f>
         <v/>
       </c>
-      <c r="Y19" s="19">
+      <c r="Y19" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(U19,V19+W19+X19+0.5*MAX(0,(U19-V19-W19)-X19)),S19*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="Z19" s="20">
+      <c r="Z19" s="19">
         <f>Y19-V19-W19</f>
         <v/>
       </c>
-      <c r="AA19" s="19">
+      <c r="AA19" s="20">
         <f>AA18+Z19</f>
         <v/>
       </c>
-      <c r="AB19" s="20">
+      <c r="AB19" s="19">
         <f>U19-Y19</f>
         <v/>
       </c>
-      <c r="AC19" s="19">
+      <c r="AC19" s="20">
         <f>AC18+AB19</f>
         <v/>
       </c>
       <c r="AD19" s="21">
-        <f>IF(Z19&gt;=Ipotesi!$B$14,Q19,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(U19-V19-W19)/2,Z19)&gt;=Ipotesi!$B$14,Q19,"")</f>
         <v/>
       </c>
       <c r="AE19" s="21">
@@ -3297,48 +3445,48 @@
         <f>ROUND(D$3*MIN(1,2/D$6)*Stagionalità!$B$5,0)</f>
         <v/>
       </c>
-      <c r="AJ19" s="19">
+      <c r="AJ19" s="20">
         <f>AI19*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="AK19" s="19">
+      <c r="AK19" s="20">
         <f>AI19*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AL19" s="19">
+      <c r="AL19" s="20">
         <f>'Costi B2Brand'!$C$6</f>
         <v/>
       </c>
-      <c r="AM19" s="19">
+      <c r="AM19" s="20">
         <f>D$7</f>
         <v/>
       </c>
-      <c r="AN19" s="19">
+      <c r="AN19" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,AN18-(AK18-AL18-AM18)),0)</f>
         <v/>
       </c>
-      <c r="AO19" s="19">
+      <c r="AO19" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(AK19,AL19+AM19+AN19+0.5*MAX(0,(AK19-AL19-AM19)-AN19)),AI19*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AP19" s="20">
+      <c r="AP19" s="19">
         <f>AO19-AL19-AM19</f>
         <v/>
       </c>
-      <c r="AQ19" s="19">
+      <c r="AQ19" s="20">
         <f>AQ18+AP19</f>
         <v/>
       </c>
-      <c r="AR19" s="20">
+      <c r="AR19" s="19">
         <f>AK19-AO19</f>
         <v/>
       </c>
-      <c r="AS19" s="19">
+      <c r="AS19" s="20">
         <f>AS18+AR19</f>
         <v/>
       </c>
       <c r="AT19" s="21">
-        <f>IF(AP19&gt;=Ipotesi!$B$14,AG19,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(AK19-AL19-AM19)/2,AP19)&gt;=Ipotesi!$B$14,AG19,"")</f>
         <v/>
       </c>
       <c r="AU19" s="21">
@@ -3357,48 +3505,48 @@
         <f>ROUND(B$3*MIN(1,3/B$6)*Stagionalità!$B$6,0)</f>
         <v/>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="20">
         <f>C20*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="E20" s="19">
+      <c r="E20" s="20">
         <f>C20*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="F20" s="19">
+      <c r="F20" s="20">
         <f>'Costi B2Brand'!$C$6</f>
         <v/>
       </c>
-      <c r="G20" s="19">
+      <c r="G20" s="20">
         <f>B$7</f>
         <v/>
       </c>
-      <c r="H20" s="19">
+      <c r="H20" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,H19-(E19-F19-G19)),0)</f>
         <v/>
       </c>
-      <c r="I20" s="19">
+      <c r="I20" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(E20,F20+G20+H20+0.5*MAX(0,(E20-F20-G20)-H20)),C20*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="J20" s="20">
+      <c r="J20" s="19">
         <f>I20-F20-G20</f>
         <v/>
       </c>
-      <c r="K20" s="19">
+      <c r="K20" s="20">
         <f>K19+J20</f>
         <v/>
       </c>
-      <c r="L20" s="20">
+      <c r="L20" s="19">
         <f>E20-I20</f>
         <v/>
       </c>
-      <c r="M20" s="19">
+      <c r="M20" s="20">
         <f>M19+L20</f>
         <v/>
       </c>
       <c r="N20" s="21">
-        <f>IF(J20&gt;=Ipotesi!$B$14,A20,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(E20-F20-G20)/2,J20)&gt;=Ipotesi!$B$14,A20,"")</f>
         <v/>
       </c>
       <c r="O20" s="21">
@@ -3415,48 +3563,48 @@
         <f>ROUND(C$3*MIN(1,3/C$6)*Stagionalità!$B$6,0)</f>
         <v/>
       </c>
-      <c r="T20" s="19">
+      <c r="T20" s="20">
         <f>S20*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="U20" s="19">
+      <c r="U20" s="20">
         <f>S20*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="V20" s="19">
+      <c r="V20" s="20">
         <f>'Costi B2Brand'!$C$6</f>
         <v/>
       </c>
-      <c r="W20" s="19">
+      <c r="W20" s="20">
         <f>C$7</f>
         <v/>
       </c>
-      <c r="X20" s="19">
+      <c r="X20" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,X19-(U19-V19-W19)),0)</f>
         <v/>
       </c>
-      <c r="Y20" s="19">
+      <c r="Y20" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(U20,V20+W20+X20+0.5*MAX(0,(U20-V20-W20)-X20)),S20*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="Z20" s="20">
+      <c r="Z20" s="19">
         <f>Y20-V20-W20</f>
         <v/>
       </c>
-      <c r="AA20" s="19">
+      <c r="AA20" s="20">
         <f>AA19+Z20</f>
         <v/>
       </c>
-      <c r="AB20" s="20">
+      <c r="AB20" s="19">
         <f>U20-Y20</f>
         <v/>
       </c>
-      <c r="AC20" s="19">
+      <c r="AC20" s="20">
         <f>AC19+AB20</f>
         <v/>
       </c>
       <c r="AD20" s="21">
-        <f>IF(Z20&gt;=Ipotesi!$B$14,Q20,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(U20-V20-W20)/2,Z20)&gt;=Ipotesi!$B$14,Q20,"")</f>
         <v/>
       </c>
       <c r="AE20" s="21">
@@ -3473,48 +3621,48 @@
         <f>ROUND(D$3*MIN(1,3/D$6)*Stagionalità!$B$6,0)</f>
         <v/>
       </c>
-      <c r="AJ20" s="19">
+      <c r="AJ20" s="20">
         <f>AI20*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="AK20" s="19">
+      <c r="AK20" s="20">
         <f>AI20*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AL20" s="19">
+      <c r="AL20" s="20">
         <f>'Costi B2Brand'!$C$6</f>
         <v/>
       </c>
-      <c r="AM20" s="19">
+      <c r="AM20" s="20">
         <f>D$7</f>
         <v/>
       </c>
-      <c r="AN20" s="19">
+      <c r="AN20" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,AN19-(AK19-AL19-AM19)),0)</f>
         <v/>
       </c>
-      <c r="AO20" s="19">
+      <c r="AO20" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(AK20,AL20+AM20+AN20+0.5*MAX(0,(AK20-AL20-AM20)-AN20)),AI20*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AP20" s="20">
+      <c r="AP20" s="19">
         <f>AO20-AL20-AM20</f>
         <v/>
       </c>
-      <c r="AQ20" s="19">
+      <c r="AQ20" s="20">
         <f>AQ19+AP20</f>
         <v/>
       </c>
-      <c r="AR20" s="20">
+      <c r="AR20" s="19">
         <f>AK20-AO20</f>
         <v/>
       </c>
-      <c r="AS20" s="19">
+      <c r="AS20" s="20">
         <f>AS19+AR20</f>
         <v/>
       </c>
       <c r="AT20" s="21">
-        <f>IF(AP20&gt;=Ipotesi!$B$14,AG20,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(AK20-AL20-AM20)/2,AP20)&gt;=Ipotesi!$B$14,AG20,"")</f>
         <v/>
       </c>
       <c r="AU20" s="21">
@@ -3533,48 +3681,48 @@
         <f>ROUND(B$3*MIN(1,4/B$6)*Stagionalità!$B$7,0)</f>
         <v/>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="20">
         <f>C21*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="E21" s="19">
+      <c r="E21" s="20">
         <f>C21*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="F21" s="19">
+      <c r="F21" s="20">
         <f>'Costi B2Brand'!$C$6</f>
         <v/>
       </c>
-      <c r="G21" s="19">
+      <c r="G21" s="20">
         <f>B$7</f>
         <v/>
       </c>
-      <c r="H21" s="19">
+      <c r="H21" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,H20-(E20-F20-G20)),0)</f>
         <v/>
       </c>
-      <c r="I21" s="19">
+      <c r="I21" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(E21,F21+G21+H21+0.5*MAX(0,(E21-F21-G21)-H21)),C21*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="J21" s="20">
+      <c r="J21" s="19">
         <f>I21-F21-G21</f>
         <v/>
       </c>
-      <c r="K21" s="19">
+      <c r="K21" s="20">
         <f>K20+J21</f>
         <v/>
       </c>
-      <c r="L21" s="20">
+      <c r="L21" s="19">
         <f>E21-I21</f>
         <v/>
       </c>
-      <c r="M21" s="19">
+      <c r="M21" s="20">
         <f>M20+L21</f>
         <v/>
       </c>
       <c r="N21" s="21">
-        <f>IF(J21&gt;=Ipotesi!$B$14,A21,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(E21-F21-G21)/2,J21)&gt;=Ipotesi!$B$14,A21,"")</f>
         <v/>
       </c>
       <c r="O21" s="21">
@@ -3591,48 +3739,48 @@
         <f>ROUND(C$3*MIN(1,4/C$6)*Stagionalità!$B$7,0)</f>
         <v/>
       </c>
-      <c r="T21" s="19">
+      <c r="T21" s="20">
         <f>S21*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="U21" s="19">
+      <c r="U21" s="20">
         <f>S21*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="V21" s="19">
+      <c r="V21" s="20">
         <f>'Costi B2Brand'!$C$6</f>
         <v/>
       </c>
-      <c r="W21" s="19">
+      <c r="W21" s="20">
         <f>C$7</f>
         <v/>
       </c>
-      <c r="X21" s="19">
+      <c r="X21" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,X20-(U20-V20-W20)),0)</f>
         <v/>
       </c>
-      <c r="Y21" s="19">
+      <c r="Y21" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(U21,V21+W21+X21+0.5*MAX(0,(U21-V21-W21)-X21)),S21*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="Z21" s="20">
+      <c r="Z21" s="19">
         <f>Y21-V21-W21</f>
         <v/>
       </c>
-      <c r="AA21" s="19">
+      <c r="AA21" s="20">
         <f>AA20+Z21</f>
         <v/>
       </c>
-      <c r="AB21" s="20">
+      <c r="AB21" s="19">
         <f>U21-Y21</f>
         <v/>
       </c>
-      <c r="AC21" s="19">
+      <c r="AC21" s="20">
         <f>AC20+AB21</f>
         <v/>
       </c>
       <c r="AD21" s="21">
-        <f>IF(Z21&gt;=Ipotesi!$B$14,Q21,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(U21-V21-W21)/2,Z21)&gt;=Ipotesi!$B$14,Q21,"")</f>
         <v/>
       </c>
       <c r="AE21" s="21">
@@ -3649,48 +3797,48 @@
         <f>ROUND(D$3*MIN(1,4/D$6)*Stagionalità!$B$7,0)</f>
         <v/>
       </c>
-      <c r="AJ21" s="19">
+      <c r="AJ21" s="20">
         <f>AI21*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="AK21" s="19">
+      <c r="AK21" s="20">
         <f>AI21*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AL21" s="19">
+      <c r="AL21" s="20">
         <f>'Costi B2Brand'!$C$6</f>
         <v/>
       </c>
-      <c r="AM21" s="19">
+      <c r="AM21" s="20">
         <f>D$7</f>
         <v/>
       </c>
-      <c r="AN21" s="19">
+      <c r="AN21" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,AN20-(AK20-AL20-AM20)),0)</f>
         <v/>
       </c>
-      <c r="AO21" s="19">
+      <c r="AO21" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(AK21,AL21+AM21+AN21+0.5*MAX(0,(AK21-AL21-AM21)-AN21)),AI21*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AP21" s="20">
+      <c r="AP21" s="19">
         <f>AO21-AL21-AM21</f>
         <v/>
       </c>
-      <c r="AQ21" s="19">
+      <c r="AQ21" s="20">
         <f>AQ20+AP21</f>
         <v/>
       </c>
-      <c r="AR21" s="20">
+      <c r="AR21" s="19">
         <f>AK21-AO21</f>
         <v/>
       </c>
-      <c r="AS21" s="19">
+      <c r="AS21" s="20">
         <f>AS20+AR21</f>
         <v/>
       </c>
       <c r="AT21" s="21">
-        <f>IF(AP21&gt;=Ipotesi!$B$14,AG21,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(AK21-AL21-AM21)/2,AP21)&gt;=Ipotesi!$B$14,AG21,"")</f>
         <v/>
       </c>
       <c r="AU21" s="21">
@@ -3709,48 +3857,48 @@
         <f>ROUND(B$3*MIN(1,5/B$6)*Stagionalità!$B$8,0)</f>
         <v/>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="20">
         <f>C22*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="E22" s="19">
+      <c r="E22" s="20">
         <f>C22*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="F22" s="19">
+      <c r="F22" s="20">
         <f>'Costi B2Brand'!$C$6</f>
         <v/>
       </c>
-      <c r="G22" s="19">
+      <c r="G22" s="20">
         <f>B$7</f>
         <v/>
       </c>
-      <c r="H22" s="19">
+      <c r="H22" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,H21-(E21-F21-G21)),0)</f>
         <v/>
       </c>
-      <c r="I22" s="19">
+      <c r="I22" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(E22,F22+G22+H22+0.5*MAX(0,(E22-F22-G22)-H22)),C22*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="J22" s="20">
+      <c r="J22" s="19">
         <f>I22-F22-G22</f>
         <v/>
       </c>
-      <c r="K22" s="19">
+      <c r="K22" s="20">
         <f>K21+J22</f>
         <v/>
       </c>
-      <c r="L22" s="20">
+      <c r="L22" s="19">
         <f>E22-I22</f>
         <v/>
       </c>
-      <c r="M22" s="19">
+      <c r="M22" s="20">
         <f>M21+L22</f>
         <v/>
       </c>
       <c r="N22" s="21">
-        <f>IF(J22&gt;=Ipotesi!$B$14,A22,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(E22-F22-G22)/2,J22)&gt;=Ipotesi!$B$14,A22,"")</f>
         <v/>
       </c>
       <c r="O22" s="21">
@@ -3767,48 +3915,48 @@
         <f>ROUND(C$3*MIN(1,5/C$6)*Stagionalità!$B$8,0)</f>
         <v/>
       </c>
-      <c r="T22" s="19">
+      <c r="T22" s="20">
         <f>S22*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="U22" s="19">
+      <c r="U22" s="20">
         <f>S22*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="V22" s="19">
+      <c r="V22" s="20">
         <f>'Costi B2Brand'!$C$6</f>
         <v/>
       </c>
-      <c r="W22" s="19">
+      <c r="W22" s="20">
         <f>C$7</f>
         <v/>
       </c>
-      <c r="X22" s="19">
+      <c r="X22" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,X21-(U21-V21-W21)),0)</f>
         <v/>
       </c>
-      <c r="Y22" s="19">
+      <c r="Y22" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(U22,V22+W22+X22+0.5*MAX(0,(U22-V22-W22)-X22)),S22*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="Z22" s="20">
+      <c r="Z22" s="19">
         <f>Y22-V22-W22</f>
         <v/>
       </c>
-      <c r="AA22" s="19">
+      <c r="AA22" s="20">
         <f>AA21+Z22</f>
         <v/>
       </c>
-      <c r="AB22" s="20">
+      <c r="AB22" s="19">
         <f>U22-Y22</f>
         <v/>
       </c>
-      <c r="AC22" s="19">
+      <c r="AC22" s="20">
         <f>AC21+AB22</f>
         <v/>
       </c>
       <c r="AD22" s="21">
-        <f>IF(Z22&gt;=Ipotesi!$B$14,Q22,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(U22-V22-W22)/2,Z22)&gt;=Ipotesi!$B$14,Q22,"")</f>
         <v/>
       </c>
       <c r="AE22" s="21">
@@ -3825,48 +3973,48 @@
         <f>ROUND(D$3*MIN(1,5/D$6)*Stagionalità!$B$8,0)</f>
         <v/>
       </c>
-      <c r="AJ22" s="19">
+      <c r="AJ22" s="20">
         <f>AI22*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="AK22" s="19">
+      <c r="AK22" s="20">
         <f>AI22*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AL22" s="19">
+      <c r="AL22" s="20">
         <f>'Costi B2Brand'!$C$6</f>
         <v/>
       </c>
-      <c r="AM22" s="19">
+      <c r="AM22" s="20">
         <f>D$7</f>
         <v/>
       </c>
-      <c r="AN22" s="19">
+      <c r="AN22" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,AN21-(AK21-AL21-AM21)),0)</f>
         <v/>
       </c>
-      <c r="AO22" s="19">
+      <c r="AO22" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(AK22,AL22+AM22+AN22+0.5*MAX(0,(AK22-AL22-AM22)-AN22)),AI22*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AP22" s="20">
+      <c r="AP22" s="19">
         <f>AO22-AL22-AM22</f>
         <v/>
       </c>
-      <c r="AQ22" s="19">
+      <c r="AQ22" s="20">
         <f>AQ21+AP22</f>
         <v/>
       </c>
-      <c r="AR22" s="20">
+      <c r="AR22" s="19">
         <f>AK22-AO22</f>
         <v/>
       </c>
-      <c r="AS22" s="19">
+      <c r="AS22" s="20">
         <f>AS21+AR22</f>
         <v/>
       </c>
       <c r="AT22" s="21">
-        <f>IF(AP22&gt;=Ipotesi!$B$14,AG22,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(AK22-AL22-AM22)/2,AP22)&gt;=Ipotesi!$B$14,AG22,"")</f>
         <v/>
       </c>
       <c r="AU22" s="21">
@@ -3885,48 +4033,48 @@
         <f>ROUND(B$3*MIN(1,6/B$6)*Stagionalità!$B$9,0)</f>
         <v/>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="20">
         <f>C23*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="E23" s="19">
+      <c r="E23" s="20">
         <f>C23*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="F23" s="19">
+      <c r="F23" s="20">
         <f>'Costi B2Brand'!$C$6</f>
         <v/>
       </c>
-      <c r="G23" s="19">
+      <c r="G23" s="20">
         <f>B$7</f>
         <v/>
       </c>
-      <c r="H23" s="19">
+      <c r="H23" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,H22-(E22-F22-G22)),0)</f>
         <v/>
       </c>
-      <c r="I23" s="19">
+      <c r="I23" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(E23,F23+G23+H23+0.5*MAX(0,(E23-F23-G23)-H23)),C23*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="J23" s="20">
+      <c r="J23" s="19">
         <f>I23-F23-G23</f>
         <v/>
       </c>
-      <c r="K23" s="19">
+      <c r="K23" s="20">
         <f>K22+J23</f>
         <v/>
       </c>
-      <c r="L23" s="20">
+      <c r="L23" s="19">
         <f>E23-I23</f>
         <v/>
       </c>
-      <c r="M23" s="19">
+      <c r="M23" s="20">
         <f>M22+L23</f>
         <v/>
       </c>
       <c r="N23" s="21">
-        <f>IF(J23&gt;=Ipotesi!$B$14,A23,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(E23-F23-G23)/2,J23)&gt;=Ipotesi!$B$14,A23,"")</f>
         <v/>
       </c>
       <c r="O23" s="21">
@@ -3943,48 +4091,48 @@
         <f>ROUND(C$3*MIN(1,6/C$6)*Stagionalità!$B$9,0)</f>
         <v/>
       </c>
-      <c r="T23" s="19">
+      <c r="T23" s="20">
         <f>S23*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="U23" s="19">
+      <c r="U23" s="20">
         <f>S23*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="V23" s="19">
+      <c r="V23" s="20">
         <f>'Costi B2Brand'!$C$6</f>
         <v/>
       </c>
-      <c r="W23" s="19">
+      <c r="W23" s="20">
         <f>C$7</f>
         <v/>
       </c>
-      <c r="X23" s="19">
+      <c r="X23" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,X22-(U22-V22-W22)),0)</f>
         <v/>
       </c>
-      <c r="Y23" s="19">
+      <c r="Y23" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(U23,V23+W23+X23+0.5*MAX(0,(U23-V23-W23)-X23)),S23*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="Z23" s="20">
+      <c r="Z23" s="19">
         <f>Y23-V23-W23</f>
         <v/>
       </c>
-      <c r="AA23" s="19">
+      <c r="AA23" s="20">
         <f>AA22+Z23</f>
         <v/>
       </c>
-      <c r="AB23" s="20">
+      <c r="AB23" s="19">
         <f>U23-Y23</f>
         <v/>
       </c>
-      <c r="AC23" s="19">
+      <c r="AC23" s="20">
         <f>AC22+AB23</f>
         <v/>
       </c>
       <c r="AD23" s="21">
-        <f>IF(Z23&gt;=Ipotesi!$B$14,Q23,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(U23-V23-W23)/2,Z23)&gt;=Ipotesi!$B$14,Q23,"")</f>
         <v/>
       </c>
       <c r="AE23" s="21">
@@ -4001,48 +4149,48 @@
         <f>ROUND(D$3*MIN(1,6/D$6)*Stagionalità!$B$9,0)</f>
         <v/>
       </c>
-      <c r="AJ23" s="19">
+      <c r="AJ23" s="20">
         <f>AI23*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="AK23" s="19">
+      <c r="AK23" s="20">
         <f>AI23*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AL23" s="19">
+      <c r="AL23" s="20">
         <f>'Costi B2Brand'!$C$6</f>
         <v/>
       </c>
-      <c r="AM23" s="19">
+      <c r="AM23" s="20">
         <f>D$7</f>
         <v/>
       </c>
-      <c r="AN23" s="19">
+      <c r="AN23" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,AN22-(AK22-AL22-AM22)),0)</f>
         <v/>
       </c>
-      <c r="AO23" s="19">
+      <c r="AO23" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(AK23,AL23+AM23+AN23+0.5*MAX(0,(AK23-AL23-AM23)-AN23)),AI23*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AP23" s="20">
+      <c r="AP23" s="19">
         <f>AO23-AL23-AM23</f>
         <v/>
       </c>
-      <c r="AQ23" s="19">
+      <c r="AQ23" s="20">
         <f>AQ22+AP23</f>
         <v/>
       </c>
-      <c r="AR23" s="20">
+      <c r="AR23" s="19">
         <f>AK23-AO23</f>
         <v/>
       </c>
-      <c r="AS23" s="19">
+      <c r="AS23" s="20">
         <f>AS22+AR23</f>
         <v/>
       </c>
       <c r="AT23" s="21">
-        <f>IF(AP23&gt;=Ipotesi!$B$14,AG23,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(AK23-AL23-AM23)/2,AP23)&gt;=Ipotesi!$B$14,AG23,"")</f>
         <v/>
       </c>
       <c r="AU23" s="21">
@@ -4061,48 +4209,48 @@
         <f>ROUND(B$3*MIN(1,7/B$6)*Stagionalità!$B$10,0)</f>
         <v/>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="20">
         <f>C24*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="E24" s="19">
+      <c r="E24" s="20">
         <f>C24*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="F24" s="19">
+      <c r="F24" s="20">
         <f>'Costi B2Brand'!$C$6</f>
         <v/>
       </c>
-      <c r="G24" s="19">
+      <c r="G24" s="20">
         <f>B$7</f>
         <v/>
       </c>
-      <c r="H24" s="19">
+      <c r="H24" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,H23-(E23-F23-G23)),0)</f>
         <v/>
       </c>
-      <c r="I24" s="19">
+      <c r="I24" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(E24,F24+G24+H24+0.5*MAX(0,(E24-F24-G24)-H24)),C24*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="J24" s="20">
+      <c r="J24" s="19">
         <f>I24-F24-G24</f>
         <v/>
       </c>
-      <c r="K24" s="19">
+      <c r="K24" s="20">
         <f>K23+J24</f>
         <v/>
       </c>
-      <c r="L24" s="20">
+      <c r="L24" s="19">
         <f>E24-I24</f>
         <v/>
       </c>
-      <c r="M24" s="19">
+      <c r="M24" s="20">
         <f>M23+L24</f>
         <v/>
       </c>
       <c r="N24" s="21">
-        <f>IF(J24&gt;=Ipotesi!$B$14,A24,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(E24-F24-G24)/2,J24)&gt;=Ipotesi!$B$14,A24,"")</f>
         <v/>
       </c>
       <c r="O24" s="21">
@@ -4119,48 +4267,48 @@
         <f>ROUND(C$3*MIN(1,7/C$6)*Stagionalità!$B$10,0)</f>
         <v/>
       </c>
-      <c r="T24" s="19">
+      <c r="T24" s="20">
         <f>S24*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="U24" s="19">
+      <c r="U24" s="20">
         <f>S24*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="V24" s="19">
+      <c r="V24" s="20">
         <f>'Costi B2Brand'!$C$6</f>
         <v/>
       </c>
-      <c r="W24" s="19">
+      <c r="W24" s="20">
         <f>C$7</f>
         <v/>
       </c>
-      <c r="X24" s="19">
+      <c r="X24" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,X23-(U23-V23-W23)),0)</f>
         <v/>
       </c>
-      <c r="Y24" s="19">
+      <c r="Y24" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(U24,V24+W24+X24+0.5*MAX(0,(U24-V24-W24)-X24)),S24*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="Z24" s="20">
+      <c r="Z24" s="19">
         <f>Y24-V24-W24</f>
         <v/>
       </c>
-      <c r="AA24" s="19">
+      <c r="AA24" s="20">
         <f>AA23+Z24</f>
         <v/>
       </c>
-      <c r="AB24" s="20">
+      <c r="AB24" s="19">
         <f>U24-Y24</f>
         <v/>
       </c>
-      <c r="AC24" s="19">
+      <c r="AC24" s="20">
         <f>AC23+AB24</f>
         <v/>
       </c>
       <c r="AD24" s="21">
-        <f>IF(Z24&gt;=Ipotesi!$B$14,Q24,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(U24-V24-W24)/2,Z24)&gt;=Ipotesi!$B$14,Q24,"")</f>
         <v/>
       </c>
       <c r="AE24" s="21">
@@ -4177,48 +4325,48 @@
         <f>ROUND(D$3*MIN(1,7/D$6)*Stagionalità!$B$10,0)</f>
         <v/>
       </c>
-      <c r="AJ24" s="19">
+      <c r="AJ24" s="20">
         <f>AI24*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="AK24" s="19">
+      <c r="AK24" s="20">
         <f>AI24*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AL24" s="19">
+      <c r="AL24" s="20">
         <f>'Costi B2Brand'!$C$6</f>
         <v/>
       </c>
-      <c r="AM24" s="19">
+      <c r="AM24" s="20">
         <f>D$7</f>
         <v/>
       </c>
-      <c r="AN24" s="19">
+      <c r="AN24" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,AN23-(AK23-AL23-AM23)),0)</f>
         <v/>
       </c>
-      <c r="AO24" s="19">
+      <c r="AO24" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(AK24,AL24+AM24+AN24+0.5*MAX(0,(AK24-AL24-AM24)-AN24)),AI24*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AP24" s="20">
+      <c r="AP24" s="19">
         <f>AO24-AL24-AM24</f>
         <v/>
       </c>
-      <c r="AQ24" s="19">
+      <c r="AQ24" s="20">
         <f>AQ23+AP24</f>
         <v/>
       </c>
-      <c r="AR24" s="20">
+      <c r="AR24" s="19">
         <f>AK24-AO24</f>
         <v/>
       </c>
-      <c r="AS24" s="19">
+      <c r="AS24" s="20">
         <f>AS23+AR24</f>
         <v/>
       </c>
       <c r="AT24" s="21">
-        <f>IF(AP24&gt;=Ipotesi!$B$14,AG24,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(AK24-AL24-AM24)/2,AP24)&gt;=Ipotesi!$B$14,AG24,"")</f>
         <v/>
       </c>
       <c r="AU24" s="21">
@@ -4237,48 +4385,48 @@
         <f>ROUND(B$3*MIN(1,8/B$6)*Stagionalità!$B$11,0)</f>
         <v/>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="20">
         <f>C25*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="E25" s="19">
+      <c r="E25" s="20">
         <f>C25*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="F25" s="19">
+      <c r="F25" s="20">
         <f>'Costi B2Brand'!$C$6</f>
         <v/>
       </c>
-      <c r="G25" s="19">
+      <c r="G25" s="20">
         <f>B$7</f>
         <v/>
       </c>
-      <c r="H25" s="19">
+      <c r="H25" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,H24-(E24-F24-G24)),0)</f>
         <v/>
       </c>
-      <c r="I25" s="19">
+      <c r="I25" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(E25,F25+G25+H25+0.5*MAX(0,(E25-F25-G25)-H25)),C25*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="J25" s="20">
+      <c r="J25" s="19">
         <f>I25-F25-G25</f>
         <v/>
       </c>
-      <c r="K25" s="19">
+      <c r="K25" s="20">
         <f>K24+J25</f>
         <v/>
       </c>
-      <c r="L25" s="20">
+      <c r="L25" s="19">
         <f>E25-I25</f>
         <v/>
       </c>
-      <c r="M25" s="19">
+      <c r="M25" s="20">
         <f>M24+L25</f>
         <v/>
       </c>
       <c r="N25" s="21">
-        <f>IF(J25&gt;=Ipotesi!$B$14,A25,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(E25-F25-G25)/2,J25)&gt;=Ipotesi!$B$14,A25,"")</f>
         <v/>
       </c>
       <c r="O25" s="21">
@@ -4295,48 +4443,48 @@
         <f>ROUND(C$3*MIN(1,8/C$6)*Stagionalità!$B$11,0)</f>
         <v/>
       </c>
-      <c r="T25" s="19">
+      <c r="T25" s="20">
         <f>S25*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="U25" s="19">
+      <c r="U25" s="20">
         <f>S25*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="V25" s="19">
+      <c r="V25" s="20">
         <f>'Costi B2Brand'!$C$6</f>
         <v/>
       </c>
-      <c r="W25" s="19">
+      <c r="W25" s="20">
         <f>C$7</f>
         <v/>
       </c>
-      <c r="X25" s="19">
+      <c r="X25" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,X24-(U24-V24-W24)),0)</f>
         <v/>
       </c>
-      <c r="Y25" s="19">
+      <c r="Y25" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(U25,V25+W25+X25+0.5*MAX(0,(U25-V25-W25)-X25)),S25*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="Z25" s="20">
+      <c r="Z25" s="19">
         <f>Y25-V25-W25</f>
         <v/>
       </c>
-      <c r="AA25" s="19">
+      <c r="AA25" s="20">
         <f>AA24+Z25</f>
         <v/>
       </c>
-      <c r="AB25" s="20">
+      <c r="AB25" s="19">
         <f>U25-Y25</f>
         <v/>
       </c>
-      <c r="AC25" s="19">
+      <c r="AC25" s="20">
         <f>AC24+AB25</f>
         <v/>
       </c>
       <c r="AD25" s="21">
-        <f>IF(Z25&gt;=Ipotesi!$B$14,Q25,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(U25-V25-W25)/2,Z25)&gt;=Ipotesi!$B$14,Q25,"")</f>
         <v/>
       </c>
       <c r="AE25" s="21">
@@ -4353,48 +4501,48 @@
         <f>ROUND(D$3*MIN(1,8/D$6)*Stagionalità!$B$11,0)</f>
         <v/>
       </c>
-      <c r="AJ25" s="19">
+      <c r="AJ25" s="20">
         <f>AI25*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="AK25" s="19">
+      <c r="AK25" s="20">
         <f>AI25*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AL25" s="19">
+      <c r="AL25" s="20">
         <f>'Costi B2Brand'!$C$6</f>
         <v/>
       </c>
-      <c r="AM25" s="19">
+      <c r="AM25" s="20">
         <f>D$7</f>
         <v/>
       </c>
-      <c r="AN25" s="19">
+      <c r="AN25" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,AN24-(AK24-AL24-AM24)),0)</f>
         <v/>
       </c>
-      <c r="AO25" s="19">
+      <c r="AO25" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(AK25,AL25+AM25+AN25+0.5*MAX(0,(AK25-AL25-AM25)-AN25)),AI25*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AP25" s="20">
+      <c r="AP25" s="19">
         <f>AO25-AL25-AM25</f>
         <v/>
       </c>
-      <c r="AQ25" s="19">
+      <c r="AQ25" s="20">
         <f>AQ24+AP25</f>
         <v/>
       </c>
-      <c r="AR25" s="20">
+      <c r="AR25" s="19">
         <f>AK25-AO25</f>
         <v/>
       </c>
-      <c r="AS25" s="19">
+      <c r="AS25" s="20">
         <f>AS24+AR25</f>
         <v/>
       </c>
       <c r="AT25" s="21">
-        <f>IF(AP25&gt;=Ipotesi!$B$14,AG25,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(AK25-AL25-AM25)/2,AP25)&gt;=Ipotesi!$B$14,AG25,"")</f>
         <v/>
       </c>
       <c r="AU25" s="21">
@@ -4413,48 +4561,48 @@
         <f>ROUND(B$3*MIN(1,9/B$6)*Stagionalità!$B$12,0)</f>
         <v/>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="20">
         <f>C26*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="E26" s="19">
+      <c r="E26" s="20">
         <f>C26*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="F26" s="19">
+      <c r="F26" s="20">
         <f>'Costi B2Brand'!$C$6</f>
         <v/>
       </c>
-      <c r="G26" s="19">
+      <c r="G26" s="20">
         <f>B$7</f>
         <v/>
       </c>
-      <c r="H26" s="19">
+      <c r="H26" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,H25-(E25-F25-G25)),0)</f>
         <v/>
       </c>
-      <c r="I26" s="19">
+      <c r="I26" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(E26,F26+G26+H26+0.5*MAX(0,(E26-F26-G26)-H26)),C26*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="J26" s="20">
+      <c r="J26" s="19">
         <f>I26-F26-G26</f>
         <v/>
       </c>
-      <c r="K26" s="19">
+      <c r="K26" s="20">
         <f>K25+J26</f>
         <v/>
       </c>
-      <c r="L26" s="20">
+      <c r="L26" s="19">
         <f>E26-I26</f>
         <v/>
       </c>
-      <c r="M26" s="19">
+      <c r="M26" s="20">
         <f>M25+L26</f>
         <v/>
       </c>
       <c r="N26" s="21">
-        <f>IF(J26&gt;=Ipotesi!$B$14,A26,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(E26-F26-G26)/2,J26)&gt;=Ipotesi!$B$14,A26,"")</f>
         <v/>
       </c>
       <c r="O26" s="21">
@@ -4471,48 +4619,48 @@
         <f>ROUND(C$3*MIN(1,9/C$6)*Stagionalità!$B$12,0)</f>
         <v/>
       </c>
-      <c r="T26" s="19">
+      <c r="T26" s="20">
         <f>S26*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="U26" s="19">
+      <c r="U26" s="20">
         <f>S26*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="V26" s="19">
+      <c r="V26" s="20">
         <f>'Costi B2Brand'!$C$6</f>
         <v/>
       </c>
-      <c r="W26" s="19">
+      <c r="W26" s="20">
         <f>C$7</f>
         <v/>
       </c>
-      <c r="X26" s="19">
+      <c r="X26" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,X25-(U25-V25-W25)),0)</f>
         <v/>
       </c>
-      <c r="Y26" s="19">
+      <c r="Y26" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(U26,V26+W26+X26+0.5*MAX(0,(U26-V26-W26)-X26)),S26*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="Z26" s="20">
+      <c r="Z26" s="19">
         <f>Y26-V26-W26</f>
         <v/>
       </c>
-      <c r="AA26" s="19">
+      <c r="AA26" s="20">
         <f>AA25+Z26</f>
         <v/>
       </c>
-      <c r="AB26" s="20">
+      <c r="AB26" s="19">
         <f>U26-Y26</f>
         <v/>
       </c>
-      <c r="AC26" s="19">
+      <c r="AC26" s="20">
         <f>AC25+AB26</f>
         <v/>
       </c>
       <c r="AD26" s="21">
-        <f>IF(Z26&gt;=Ipotesi!$B$14,Q26,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(U26-V26-W26)/2,Z26)&gt;=Ipotesi!$B$14,Q26,"")</f>
         <v/>
       </c>
       <c r="AE26" s="21">
@@ -4529,48 +4677,48 @@
         <f>ROUND(D$3*MIN(1,9/D$6)*Stagionalità!$B$12,0)</f>
         <v/>
       </c>
-      <c r="AJ26" s="19">
+      <c r="AJ26" s="20">
         <f>AI26*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="AK26" s="19">
+      <c r="AK26" s="20">
         <f>AI26*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AL26" s="19">
+      <c r="AL26" s="20">
         <f>'Costi B2Brand'!$C$6</f>
         <v/>
       </c>
-      <c r="AM26" s="19">
+      <c r="AM26" s="20">
         <f>D$7</f>
         <v/>
       </c>
-      <c r="AN26" s="19">
+      <c r="AN26" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,AN25-(AK25-AL25-AM25)),0)</f>
         <v/>
       </c>
-      <c r="AO26" s="19">
+      <c r="AO26" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(AK26,AL26+AM26+AN26+0.5*MAX(0,(AK26-AL26-AM26)-AN26)),AI26*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AP26" s="20">
+      <c r="AP26" s="19">
         <f>AO26-AL26-AM26</f>
         <v/>
       </c>
-      <c r="AQ26" s="19">
+      <c r="AQ26" s="20">
         <f>AQ25+AP26</f>
         <v/>
       </c>
-      <c r="AR26" s="20">
+      <c r="AR26" s="19">
         <f>AK26-AO26</f>
         <v/>
       </c>
-      <c r="AS26" s="19">
+      <c r="AS26" s="20">
         <f>AS25+AR26</f>
         <v/>
       </c>
       <c r="AT26" s="21">
-        <f>IF(AP26&gt;=Ipotesi!$B$14,AG26,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(AK26-AL26-AM26)/2,AP26)&gt;=Ipotesi!$B$14,AG26,"")</f>
         <v/>
       </c>
       <c r="AU26" s="21">
@@ -4589,48 +4737,48 @@
         <f>ROUND(B$3*MIN(1,10/B$6)*Stagionalità!$B$13,0)</f>
         <v/>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="20">
         <f>C27*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="E27" s="19">
+      <c r="E27" s="20">
         <f>C27*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="F27" s="19">
+      <c r="F27" s="20">
         <f>'Costi B2Brand'!$C$6</f>
         <v/>
       </c>
-      <c r="G27" s="19">
+      <c r="G27" s="20">
         <f>B$7</f>
         <v/>
       </c>
-      <c r="H27" s="19">
+      <c r="H27" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,H26-(E26-F26-G26)),0)</f>
         <v/>
       </c>
-      <c r="I27" s="19">
+      <c r="I27" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(E27,F27+G27+H27+0.5*MAX(0,(E27-F27-G27)-H27)),C27*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="J27" s="20">
+      <c r="J27" s="19">
         <f>I27-F27-G27</f>
         <v/>
       </c>
-      <c r="K27" s="19">
+      <c r="K27" s="20">
         <f>K26+J27</f>
         <v/>
       </c>
-      <c r="L27" s="20">
+      <c r="L27" s="19">
         <f>E27-I27</f>
         <v/>
       </c>
-      <c r="M27" s="19">
+      <c r="M27" s="20">
         <f>M26+L27</f>
         <v/>
       </c>
       <c r="N27" s="21">
-        <f>IF(J27&gt;=Ipotesi!$B$14,A27,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(E27-F27-G27)/2,J27)&gt;=Ipotesi!$B$14,A27,"")</f>
         <v/>
       </c>
       <c r="O27" s="21">
@@ -4647,48 +4795,48 @@
         <f>ROUND(C$3*MIN(1,10/C$6)*Stagionalità!$B$13,0)</f>
         <v/>
       </c>
-      <c r="T27" s="19">
+      <c r="T27" s="20">
         <f>S27*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="U27" s="19">
+      <c r="U27" s="20">
         <f>S27*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="V27" s="19">
+      <c r="V27" s="20">
         <f>'Costi B2Brand'!$C$6</f>
         <v/>
       </c>
-      <c r="W27" s="19">
+      <c r="W27" s="20">
         <f>C$7</f>
         <v/>
       </c>
-      <c r="X27" s="19">
+      <c r="X27" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,X26-(U26-V26-W26)),0)</f>
         <v/>
       </c>
-      <c r="Y27" s="19">
+      <c r="Y27" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(U27,V27+W27+X27+0.5*MAX(0,(U27-V27-W27)-X27)),S27*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="Z27" s="20">
+      <c r="Z27" s="19">
         <f>Y27-V27-W27</f>
         <v/>
       </c>
-      <c r="AA27" s="19">
+      <c r="AA27" s="20">
         <f>AA26+Z27</f>
         <v/>
       </c>
-      <c r="AB27" s="20">
+      <c r="AB27" s="19">
         <f>U27-Y27</f>
         <v/>
       </c>
-      <c r="AC27" s="19">
+      <c r="AC27" s="20">
         <f>AC26+AB27</f>
         <v/>
       </c>
       <c r="AD27" s="21">
-        <f>IF(Z27&gt;=Ipotesi!$B$14,Q27,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(U27-V27-W27)/2,Z27)&gt;=Ipotesi!$B$14,Q27,"")</f>
         <v/>
       </c>
       <c r="AE27" s="21">
@@ -4705,48 +4853,48 @@
         <f>ROUND(D$3*MIN(1,10/D$6)*Stagionalità!$B$13,0)</f>
         <v/>
       </c>
-      <c r="AJ27" s="19">
+      <c r="AJ27" s="20">
         <f>AI27*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="AK27" s="19">
+      <c r="AK27" s="20">
         <f>AI27*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AL27" s="19">
+      <c r="AL27" s="20">
         <f>'Costi B2Brand'!$C$6</f>
         <v/>
       </c>
-      <c r="AM27" s="19">
+      <c r="AM27" s="20">
         <f>D$7</f>
         <v/>
       </c>
-      <c r="AN27" s="19">
+      <c r="AN27" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,AN26-(AK26-AL26-AM26)),0)</f>
         <v/>
       </c>
-      <c r="AO27" s="19">
+      <c r="AO27" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(AK27,AL27+AM27+AN27+0.5*MAX(0,(AK27-AL27-AM27)-AN27)),AI27*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AP27" s="20">
+      <c r="AP27" s="19">
         <f>AO27-AL27-AM27</f>
         <v/>
       </c>
-      <c r="AQ27" s="19">
+      <c r="AQ27" s="20">
         <f>AQ26+AP27</f>
         <v/>
       </c>
-      <c r="AR27" s="20">
+      <c r="AR27" s="19">
         <f>AK27-AO27</f>
         <v/>
       </c>
-      <c r="AS27" s="19">
+      <c r="AS27" s="20">
         <f>AS26+AR27</f>
         <v/>
       </c>
       <c r="AT27" s="21">
-        <f>IF(AP27&gt;=Ipotesi!$B$14,AG27,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(AK27-AL27-AM27)/2,AP27)&gt;=Ipotesi!$B$14,AG27,"")</f>
         <v/>
       </c>
       <c r="AU27" s="21">
@@ -4765,48 +4913,48 @@
         <f>ROUND(B$3*MIN(1,11/B$6)*Stagionalità!$B$2,0)</f>
         <v/>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="20">
         <f>C28*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="E28" s="19">
+      <c r="E28" s="20">
         <f>C28*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="F28" s="19">
+      <c r="F28" s="20">
         <f>'Costi B2Brand'!$C$6</f>
         <v/>
       </c>
-      <c r="G28" s="19">
+      <c r="G28" s="20">
         <f>B$7</f>
         <v/>
       </c>
-      <c r="H28" s="19">
+      <c r="H28" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,H27-(E27-F27-G27)),0)</f>
         <v/>
       </c>
-      <c r="I28" s="19">
+      <c r="I28" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(E28,F28+G28+H28+0.5*MAX(0,(E28-F28-G28)-H28)),C28*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="J28" s="20">
+      <c r="J28" s="19">
         <f>I28-F28-G28</f>
         <v/>
       </c>
-      <c r="K28" s="19">
+      <c r="K28" s="20">
         <f>K27+J28</f>
         <v/>
       </c>
-      <c r="L28" s="20">
+      <c r="L28" s="19">
         <f>E28-I28</f>
         <v/>
       </c>
-      <c r="M28" s="19">
+      <c r="M28" s="20">
         <f>M27+L28</f>
         <v/>
       </c>
       <c r="N28" s="21">
-        <f>IF(J28&gt;=Ipotesi!$B$14,A28,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(E28-F28-G28)/2,J28)&gt;=Ipotesi!$B$14,A28,"")</f>
         <v/>
       </c>
       <c r="O28" s="21">
@@ -4823,48 +4971,48 @@
         <f>ROUND(C$3*MIN(1,11/C$6)*Stagionalità!$B$2,0)</f>
         <v/>
       </c>
-      <c r="T28" s="19">
+      <c r="T28" s="20">
         <f>S28*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="U28" s="19">
+      <c r="U28" s="20">
         <f>S28*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="V28" s="19">
+      <c r="V28" s="20">
         <f>'Costi B2Brand'!$C$6</f>
         <v/>
       </c>
-      <c r="W28" s="19">
+      <c r="W28" s="20">
         <f>C$7</f>
         <v/>
       </c>
-      <c r="X28" s="19">
+      <c r="X28" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,X27-(U27-V27-W27)),0)</f>
         <v/>
       </c>
-      <c r="Y28" s="19">
+      <c r="Y28" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(U28,V28+W28+X28+0.5*MAX(0,(U28-V28-W28)-X28)),S28*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="Z28" s="20">
+      <c r="Z28" s="19">
         <f>Y28-V28-W28</f>
         <v/>
       </c>
-      <c r="AA28" s="19">
+      <c r="AA28" s="20">
         <f>AA27+Z28</f>
         <v/>
       </c>
-      <c r="AB28" s="20">
+      <c r="AB28" s="19">
         <f>U28-Y28</f>
         <v/>
       </c>
-      <c r="AC28" s="19">
+      <c r="AC28" s="20">
         <f>AC27+AB28</f>
         <v/>
       </c>
       <c r="AD28" s="21">
-        <f>IF(Z28&gt;=Ipotesi!$B$14,Q28,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(U28-V28-W28)/2,Z28)&gt;=Ipotesi!$B$14,Q28,"")</f>
         <v/>
       </c>
       <c r="AE28" s="21">
@@ -4881,48 +5029,48 @@
         <f>ROUND(D$3*MIN(1,11/D$6)*Stagionalità!$B$2,0)</f>
         <v/>
       </c>
-      <c r="AJ28" s="19">
+      <c r="AJ28" s="20">
         <f>AI28*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="AK28" s="19">
+      <c r="AK28" s="20">
         <f>AI28*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AL28" s="19">
+      <c r="AL28" s="20">
         <f>'Costi B2Brand'!$C$6</f>
         <v/>
       </c>
-      <c r="AM28" s="19">
+      <c r="AM28" s="20">
         <f>D$7</f>
         <v/>
       </c>
-      <c r="AN28" s="19">
+      <c r="AN28" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,AN27-(AK27-AL27-AM27)),0)</f>
         <v/>
       </c>
-      <c r="AO28" s="19">
+      <c r="AO28" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(AK28,AL28+AM28+AN28+0.5*MAX(0,(AK28-AL28-AM28)-AN28)),AI28*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AP28" s="20">
+      <c r="AP28" s="19">
         <f>AO28-AL28-AM28</f>
         <v/>
       </c>
-      <c r="AQ28" s="19">
+      <c r="AQ28" s="20">
         <f>AQ27+AP28</f>
         <v/>
       </c>
-      <c r="AR28" s="20">
+      <c r="AR28" s="19">
         <f>AK28-AO28</f>
         <v/>
       </c>
-      <c r="AS28" s="19">
+      <c r="AS28" s="20">
         <f>AS27+AR28</f>
         <v/>
       </c>
       <c r="AT28" s="21">
-        <f>IF(AP28&gt;=Ipotesi!$B$14,AG28,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(AK28-AL28-AM28)/2,AP28)&gt;=Ipotesi!$B$14,AG28,"")</f>
         <v/>
       </c>
       <c r="AU28" s="21">
@@ -4941,48 +5089,48 @@
         <f>ROUND(B$3*MIN(1,12/B$6)*Stagionalità!$B$3,0)</f>
         <v/>
       </c>
-      <c r="D29" s="19">
+      <c r="D29" s="20">
         <f>C29*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="E29" s="19">
+      <c r="E29" s="20">
         <f>C29*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="F29" s="19">
+      <c r="F29" s="20">
         <f>'Costi B2Brand'!$C$6</f>
         <v/>
       </c>
-      <c r="G29" s="19">
+      <c r="G29" s="20">
         <f>B$7</f>
         <v/>
       </c>
-      <c r="H29" s="19">
+      <c r="H29" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,H28-(E28-F28-G28)),0)</f>
         <v/>
       </c>
-      <c r="I29" s="19">
+      <c r="I29" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(E29,F29+G29+H29+0.5*MAX(0,(E29-F29-G29)-H29)),C29*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="J29" s="20">
+      <c r="J29" s="19">
         <f>I29-F29-G29</f>
         <v/>
       </c>
-      <c r="K29" s="19">
+      <c r="K29" s="20">
         <f>K28+J29</f>
         <v/>
       </c>
-      <c r="L29" s="20">
+      <c r="L29" s="19">
         <f>E29-I29</f>
         <v/>
       </c>
-      <c r="M29" s="19">
+      <c r="M29" s="20">
         <f>M28+L29</f>
         <v/>
       </c>
       <c r="N29" s="21">
-        <f>IF(J29&gt;=Ipotesi!$B$14,A29,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(E29-F29-G29)/2,J29)&gt;=Ipotesi!$B$14,A29,"")</f>
         <v/>
       </c>
       <c r="O29" s="21">
@@ -4999,48 +5147,48 @@
         <f>ROUND(C$3*MIN(1,12/C$6)*Stagionalità!$B$3,0)</f>
         <v/>
       </c>
-      <c r="T29" s="19">
+      <c r="T29" s="20">
         <f>S29*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="U29" s="19">
+      <c r="U29" s="20">
         <f>S29*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="V29" s="19">
+      <c r="V29" s="20">
         <f>'Costi B2Brand'!$C$6</f>
         <v/>
       </c>
-      <c r="W29" s="19">
+      <c r="W29" s="20">
         <f>C$7</f>
         <v/>
       </c>
-      <c r="X29" s="19">
+      <c r="X29" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,X28-(U28-V28-W28)),0)</f>
         <v/>
       </c>
-      <c r="Y29" s="19">
+      <c r="Y29" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(U29,V29+W29+X29+0.5*MAX(0,(U29-V29-W29)-X29)),S29*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="Z29" s="20">
+      <c r="Z29" s="19">
         <f>Y29-V29-W29</f>
         <v/>
       </c>
-      <c r="AA29" s="19">
+      <c r="AA29" s="20">
         <f>AA28+Z29</f>
         <v/>
       </c>
-      <c r="AB29" s="20">
+      <c r="AB29" s="19">
         <f>U29-Y29</f>
         <v/>
       </c>
-      <c r="AC29" s="19">
+      <c r="AC29" s="20">
         <f>AC28+AB29</f>
         <v/>
       </c>
       <c r="AD29" s="21">
-        <f>IF(Z29&gt;=Ipotesi!$B$14,Q29,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(U29-V29-W29)/2,Z29)&gt;=Ipotesi!$B$14,Q29,"")</f>
         <v/>
       </c>
       <c r="AE29" s="21">
@@ -5057,48 +5205,48 @@
         <f>ROUND(D$3*MIN(1,12/D$6)*Stagionalità!$B$3,0)</f>
         <v/>
       </c>
-      <c r="AJ29" s="19">
+      <c r="AJ29" s="20">
         <f>AI29*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="AK29" s="19">
+      <c r="AK29" s="20">
         <f>AI29*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AL29" s="19">
+      <c r="AL29" s="20">
         <f>'Costi B2Brand'!$C$6</f>
         <v/>
       </c>
-      <c r="AM29" s="19">
+      <c r="AM29" s="20">
         <f>D$7</f>
         <v/>
       </c>
-      <c r="AN29" s="19">
+      <c r="AN29" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,AN28-(AK28-AL28-AM28)),0)</f>
         <v/>
       </c>
-      <c r="AO29" s="19">
+      <c r="AO29" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(AK29,AL29+AM29+AN29+0.5*MAX(0,(AK29-AL29-AM29)-AN29)),AI29*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AP29" s="20">
+      <c r="AP29" s="19">
         <f>AO29-AL29-AM29</f>
         <v/>
       </c>
-      <c r="AQ29" s="19">
+      <c r="AQ29" s="20">
         <f>AQ28+AP29</f>
         <v/>
       </c>
-      <c r="AR29" s="20">
+      <c r="AR29" s="19">
         <f>AK29-AO29</f>
         <v/>
       </c>
-      <c r="AS29" s="19">
+      <c r="AS29" s="20">
         <f>AS28+AR29</f>
         <v/>
       </c>
       <c r="AT29" s="21">
-        <f>IF(AP29&gt;=Ipotesi!$B$14,AG29,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(AK29-AL29-AM29)/2,AP29)&gt;=Ipotesi!$B$14,AG29,"")</f>
         <v/>
       </c>
       <c r="AU29" s="21">
@@ -5114,51 +5262,51 @@
         <v>2</v>
       </c>
       <c r="C30" s="4">
-        <f>ROUND(B$4*Stagionalità!$B$4,0)</f>
-        <v/>
-      </c>
-      <c r="D30" s="19">
+        <f>ROUND((B$3+(B$13-B$3)*1/12)*Stagionalità!$B$4,0)</f>
+        <v/>
+      </c>
+      <c r="D30" s="20">
         <f>C30*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="E30" s="19">
+      <c r="E30" s="20">
         <f>C30*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="F30" s="19">
+      <c r="F30" s="20">
         <f>'Costi B2Brand'!$D$6</f>
         <v/>
       </c>
-      <c r="G30" s="19">
+      <c r="G30" s="20">
         <f>B$8</f>
         <v/>
       </c>
-      <c r="H30" s="19">
+      <c r="H30" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,H29-(E29-F29-G29)),0)</f>
         <v/>
       </c>
-      <c r="I30" s="19">
+      <c r="I30" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(E30,F30+G30+H30+0.5*MAX(0,(E30-F30-G30)-H30)),C30*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="J30" s="20">
+      <c r="J30" s="19">
         <f>I30-F30-G30</f>
         <v/>
       </c>
-      <c r="K30" s="19">
+      <c r="K30" s="20">
         <f>K29+J30</f>
         <v/>
       </c>
-      <c r="L30" s="20">
+      <c r="L30" s="19">
         <f>E30-I30</f>
         <v/>
       </c>
-      <c r="M30" s="19">
+      <c r="M30" s="20">
         <f>M29+L30</f>
         <v/>
       </c>
       <c r="N30" s="21">
-        <f>IF(J30&gt;=Ipotesi!$B$14,A30,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(E30-F30-G30)/2,J30)&gt;=Ipotesi!$B$14,A30,"")</f>
         <v/>
       </c>
       <c r="O30" s="21">
@@ -5172,51 +5320,51 @@
         <v>2</v>
       </c>
       <c r="S30" s="4">
-        <f>ROUND(C$4*Stagionalità!$B$4,0)</f>
-        <v/>
-      </c>
-      <c r="T30" s="19">
+        <f>ROUND((C$3+(C$13-C$3)*1/12)*Stagionalità!$B$4,0)</f>
+        <v/>
+      </c>
+      <c r="T30" s="20">
         <f>S30*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="U30" s="19">
+      <c r="U30" s="20">
         <f>S30*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="V30" s="19">
+      <c r="V30" s="20">
         <f>'Costi B2Brand'!$D$6</f>
         <v/>
       </c>
-      <c r="W30" s="19">
+      <c r="W30" s="20">
         <f>C$8</f>
         <v/>
       </c>
-      <c r="X30" s="19">
+      <c r="X30" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,X29-(U29-V29-W29)),0)</f>
         <v/>
       </c>
-      <c r="Y30" s="19">
+      <c r="Y30" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(U30,V30+W30+X30+0.5*MAX(0,(U30-V30-W30)-X30)),S30*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="Z30" s="20">
+      <c r="Z30" s="19">
         <f>Y30-V30-W30</f>
         <v/>
       </c>
-      <c r="AA30" s="19">
+      <c r="AA30" s="20">
         <f>AA29+Z30</f>
         <v/>
       </c>
-      <c r="AB30" s="20">
+      <c r="AB30" s="19">
         <f>U30-Y30</f>
         <v/>
       </c>
-      <c r="AC30" s="19">
+      <c r="AC30" s="20">
         <f>AC29+AB30</f>
         <v/>
       </c>
       <c r="AD30" s="21">
-        <f>IF(Z30&gt;=Ipotesi!$B$14,Q30,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(U30-V30-W30)/2,Z30)&gt;=Ipotesi!$B$14,Q30,"")</f>
         <v/>
       </c>
       <c r="AE30" s="21">
@@ -5230,51 +5378,51 @@
         <v>2</v>
       </c>
       <c r="AI30" s="4">
-        <f>ROUND(D$4*Stagionalità!$B$4,0)</f>
-        <v/>
-      </c>
-      <c r="AJ30" s="19">
+        <f>ROUND((D$3+(D$13-D$3)*1/12)*Stagionalità!$B$4,0)</f>
+        <v/>
+      </c>
+      <c r="AJ30" s="20">
         <f>AI30*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="AK30" s="19">
+      <c r="AK30" s="20">
         <f>AI30*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AL30" s="19">
+      <c r="AL30" s="20">
         <f>'Costi B2Brand'!$D$6</f>
         <v/>
       </c>
-      <c r="AM30" s="19">
+      <c r="AM30" s="20">
         <f>D$8</f>
         <v/>
       </c>
-      <c r="AN30" s="19">
+      <c r="AN30" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,AN29-(AK29-AL29-AM29)),0)</f>
         <v/>
       </c>
-      <c r="AO30" s="19">
+      <c r="AO30" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(AK30,AL30+AM30+AN30+0.5*MAX(0,(AK30-AL30-AM30)-AN30)),AI30*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AP30" s="20">
+      <c r="AP30" s="19">
         <f>AO30-AL30-AM30</f>
         <v/>
       </c>
-      <c r="AQ30" s="19">
+      <c r="AQ30" s="20">
         <f>AQ29+AP30</f>
         <v/>
       </c>
-      <c r="AR30" s="20">
+      <c r="AR30" s="19">
         <f>AK30-AO30</f>
         <v/>
       </c>
-      <c r="AS30" s="19">
+      <c r="AS30" s="20">
         <f>AS29+AR30</f>
         <v/>
       </c>
       <c r="AT30" s="21">
-        <f>IF(AP30&gt;=Ipotesi!$B$14,AG30,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(AK30-AL30-AM30)/2,AP30)&gt;=Ipotesi!$B$14,AG30,"")</f>
         <v/>
       </c>
       <c r="AU30" s="21">
@@ -5290,51 +5438,51 @@
         <v>2</v>
       </c>
       <c r="C31" s="4">
-        <f>ROUND(B$4*Stagionalità!$B$5,0)</f>
-        <v/>
-      </c>
-      <c r="D31" s="19">
+        <f>ROUND((B$3+(B$13-B$3)*2/12)*Stagionalità!$B$5,0)</f>
+        <v/>
+      </c>
+      <c r="D31" s="20">
         <f>C31*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="E31" s="19">
+      <c r="E31" s="20">
         <f>C31*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="F31" s="19">
+      <c r="F31" s="20">
         <f>'Costi B2Brand'!$D$6</f>
         <v/>
       </c>
-      <c r="G31" s="19">
+      <c r="G31" s="20">
         <f>B$8</f>
         <v/>
       </c>
-      <c r="H31" s="19">
+      <c r="H31" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,H30-(E30-F30-G30)),0)</f>
         <v/>
       </c>
-      <c r="I31" s="19">
+      <c r="I31" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(E31,F31+G31+H31+0.5*MAX(0,(E31-F31-G31)-H31)),C31*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="J31" s="20">
+      <c r="J31" s="19">
         <f>I31-F31-G31</f>
         <v/>
       </c>
-      <c r="K31" s="19">
+      <c r="K31" s="20">
         <f>K30+J31</f>
         <v/>
       </c>
-      <c r="L31" s="20">
+      <c r="L31" s="19">
         <f>E31-I31</f>
         <v/>
       </c>
-      <c r="M31" s="19">
+      <c r="M31" s="20">
         <f>M30+L31</f>
         <v/>
       </c>
       <c r="N31" s="21">
-        <f>IF(J31&gt;=Ipotesi!$B$14,A31,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(E31-F31-G31)/2,J31)&gt;=Ipotesi!$B$14,A31,"")</f>
         <v/>
       </c>
       <c r="O31" s="21">
@@ -5348,51 +5496,51 @@
         <v>2</v>
       </c>
       <c r="S31" s="4">
-        <f>ROUND(C$4*Stagionalità!$B$5,0)</f>
-        <v/>
-      </c>
-      <c r="T31" s="19">
+        <f>ROUND((C$3+(C$13-C$3)*2/12)*Stagionalità!$B$5,0)</f>
+        <v/>
+      </c>
+      <c r="T31" s="20">
         <f>S31*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="U31" s="19">
+      <c r="U31" s="20">
         <f>S31*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="V31" s="19">
+      <c r="V31" s="20">
         <f>'Costi B2Brand'!$D$6</f>
         <v/>
       </c>
-      <c r="W31" s="19">
+      <c r="W31" s="20">
         <f>C$8</f>
         <v/>
       </c>
-      <c r="X31" s="19">
+      <c r="X31" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,X30-(U30-V30-W30)),0)</f>
         <v/>
       </c>
-      <c r="Y31" s="19">
+      <c r="Y31" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(U31,V31+W31+X31+0.5*MAX(0,(U31-V31-W31)-X31)),S31*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="Z31" s="20">
+      <c r="Z31" s="19">
         <f>Y31-V31-W31</f>
         <v/>
       </c>
-      <c r="AA31" s="19">
+      <c r="AA31" s="20">
         <f>AA30+Z31</f>
         <v/>
       </c>
-      <c r="AB31" s="20">
+      <c r="AB31" s="19">
         <f>U31-Y31</f>
         <v/>
       </c>
-      <c r="AC31" s="19">
+      <c r="AC31" s="20">
         <f>AC30+AB31</f>
         <v/>
       </c>
       <c r="AD31" s="21">
-        <f>IF(Z31&gt;=Ipotesi!$B$14,Q31,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(U31-V31-W31)/2,Z31)&gt;=Ipotesi!$B$14,Q31,"")</f>
         <v/>
       </c>
       <c r="AE31" s="21">
@@ -5406,51 +5554,51 @@
         <v>2</v>
       </c>
       <c r="AI31" s="4">
-        <f>ROUND(D$4*Stagionalità!$B$5,0)</f>
-        <v/>
-      </c>
-      <c r="AJ31" s="19">
+        <f>ROUND((D$3+(D$13-D$3)*2/12)*Stagionalità!$B$5,0)</f>
+        <v/>
+      </c>
+      <c r="AJ31" s="20">
         <f>AI31*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="AK31" s="19">
+      <c r="AK31" s="20">
         <f>AI31*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AL31" s="19">
+      <c r="AL31" s="20">
         <f>'Costi B2Brand'!$D$6</f>
         <v/>
       </c>
-      <c r="AM31" s="19">
+      <c r="AM31" s="20">
         <f>D$8</f>
         <v/>
       </c>
-      <c r="AN31" s="19">
+      <c r="AN31" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,AN30-(AK30-AL30-AM30)),0)</f>
         <v/>
       </c>
-      <c r="AO31" s="19">
+      <c r="AO31" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(AK31,AL31+AM31+AN31+0.5*MAX(0,(AK31-AL31-AM31)-AN31)),AI31*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AP31" s="20">
+      <c r="AP31" s="19">
         <f>AO31-AL31-AM31</f>
         <v/>
       </c>
-      <c r="AQ31" s="19">
+      <c r="AQ31" s="20">
         <f>AQ30+AP31</f>
         <v/>
       </c>
-      <c r="AR31" s="20">
+      <c r="AR31" s="19">
         <f>AK31-AO31</f>
         <v/>
       </c>
-      <c r="AS31" s="19">
+      <c r="AS31" s="20">
         <f>AS30+AR31</f>
         <v/>
       </c>
       <c r="AT31" s="21">
-        <f>IF(AP31&gt;=Ipotesi!$B$14,AG31,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(AK31-AL31-AM31)/2,AP31)&gt;=Ipotesi!$B$14,AG31,"")</f>
         <v/>
       </c>
       <c r="AU31" s="21">
@@ -5466,51 +5614,51 @@
         <v>2</v>
       </c>
       <c r="C32" s="4">
-        <f>ROUND(B$4*Stagionalità!$B$6,0)</f>
-        <v/>
-      </c>
-      <c r="D32" s="19">
+        <f>ROUND((B$3+(B$13-B$3)*3/12)*Stagionalità!$B$6,0)</f>
+        <v/>
+      </c>
+      <c r="D32" s="20">
         <f>C32*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="E32" s="19">
+      <c r="E32" s="20">
         <f>C32*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="F32" s="19">
+      <c r="F32" s="20">
         <f>'Costi B2Brand'!$D$6</f>
         <v/>
       </c>
-      <c r="G32" s="19">
+      <c r="G32" s="20">
         <f>B$8</f>
         <v/>
       </c>
-      <c r="H32" s="19">
+      <c r="H32" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,H31-(E31-F31-G31)),0)</f>
         <v/>
       </c>
-      <c r="I32" s="19">
+      <c r="I32" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(E32,F32+G32+H32+0.5*MAX(0,(E32-F32-G32)-H32)),C32*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="J32" s="20">
+      <c r="J32" s="19">
         <f>I32-F32-G32</f>
         <v/>
       </c>
-      <c r="K32" s="19">
+      <c r="K32" s="20">
         <f>K31+J32</f>
         <v/>
       </c>
-      <c r="L32" s="20">
+      <c r="L32" s="19">
         <f>E32-I32</f>
         <v/>
       </c>
-      <c r="M32" s="19">
+      <c r="M32" s="20">
         <f>M31+L32</f>
         <v/>
       </c>
       <c r="N32" s="21">
-        <f>IF(J32&gt;=Ipotesi!$B$14,A32,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(E32-F32-G32)/2,J32)&gt;=Ipotesi!$B$14,A32,"")</f>
         <v/>
       </c>
       <c r="O32" s="21">
@@ -5524,51 +5672,51 @@
         <v>2</v>
       </c>
       <c r="S32" s="4">
-        <f>ROUND(C$4*Stagionalità!$B$6,0)</f>
-        <v/>
-      </c>
-      <c r="T32" s="19">
+        <f>ROUND((C$3+(C$13-C$3)*3/12)*Stagionalità!$B$6,0)</f>
+        <v/>
+      </c>
+      <c r="T32" s="20">
         <f>S32*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="U32" s="19">
+      <c r="U32" s="20">
         <f>S32*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="V32" s="19">
+      <c r="V32" s="20">
         <f>'Costi B2Brand'!$D$6</f>
         <v/>
       </c>
-      <c r="W32" s="19">
+      <c r="W32" s="20">
         <f>C$8</f>
         <v/>
       </c>
-      <c r="X32" s="19">
+      <c r="X32" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,X31-(U31-V31-W31)),0)</f>
         <v/>
       </c>
-      <c r="Y32" s="19">
+      <c r="Y32" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(U32,V32+W32+X32+0.5*MAX(0,(U32-V32-W32)-X32)),S32*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="Z32" s="20">
+      <c r="Z32" s="19">
         <f>Y32-V32-W32</f>
         <v/>
       </c>
-      <c r="AA32" s="19">
+      <c r="AA32" s="20">
         <f>AA31+Z32</f>
         <v/>
       </c>
-      <c r="AB32" s="20">
+      <c r="AB32" s="19">
         <f>U32-Y32</f>
         <v/>
       </c>
-      <c r="AC32" s="19">
+      <c r="AC32" s="20">
         <f>AC31+AB32</f>
         <v/>
       </c>
       <c r="AD32" s="21">
-        <f>IF(Z32&gt;=Ipotesi!$B$14,Q32,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(U32-V32-W32)/2,Z32)&gt;=Ipotesi!$B$14,Q32,"")</f>
         <v/>
       </c>
       <c r="AE32" s="21">
@@ -5582,51 +5730,51 @@
         <v>2</v>
       </c>
       <c r="AI32" s="4">
-        <f>ROUND(D$4*Stagionalità!$B$6,0)</f>
-        <v/>
-      </c>
-      <c r="AJ32" s="19">
+        <f>ROUND((D$3+(D$13-D$3)*3/12)*Stagionalità!$B$6,0)</f>
+        <v/>
+      </c>
+      <c r="AJ32" s="20">
         <f>AI32*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="AK32" s="19">
+      <c r="AK32" s="20">
         <f>AI32*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AL32" s="19">
+      <c r="AL32" s="20">
         <f>'Costi B2Brand'!$D$6</f>
         <v/>
       </c>
-      <c r="AM32" s="19">
+      <c r="AM32" s="20">
         <f>D$8</f>
         <v/>
       </c>
-      <c r="AN32" s="19">
+      <c r="AN32" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,AN31-(AK31-AL31-AM31)),0)</f>
         <v/>
       </c>
-      <c r="AO32" s="19">
+      <c r="AO32" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(AK32,AL32+AM32+AN32+0.5*MAX(0,(AK32-AL32-AM32)-AN32)),AI32*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AP32" s="20">
+      <c r="AP32" s="19">
         <f>AO32-AL32-AM32</f>
         <v/>
       </c>
-      <c r="AQ32" s="19">
+      <c r="AQ32" s="20">
         <f>AQ31+AP32</f>
         <v/>
       </c>
-      <c r="AR32" s="20">
+      <c r="AR32" s="19">
         <f>AK32-AO32</f>
         <v/>
       </c>
-      <c r="AS32" s="19">
+      <c r="AS32" s="20">
         <f>AS31+AR32</f>
         <v/>
       </c>
       <c r="AT32" s="21">
-        <f>IF(AP32&gt;=Ipotesi!$B$14,AG32,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(AK32-AL32-AM32)/2,AP32)&gt;=Ipotesi!$B$14,AG32,"")</f>
         <v/>
       </c>
       <c r="AU32" s="21">
@@ -5642,51 +5790,51 @@
         <v>2</v>
       </c>
       <c r="C33" s="4">
-        <f>ROUND(B$4*Stagionalità!$B$7,0)</f>
-        <v/>
-      </c>
-      <c r="D33" s="19">
+        <f>ROUND((B$3+(B$13-B$3)*4/12)*Stagionalità!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="D33" s="20">
         <f>C33*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="E33" s="19">
+      <c r="E33" s="20">
         <f>C33*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="F33" s="19">
+      <c r="F33" s="20">
         <f>'Costi B2Brand'!$D$6</f>
         <v/>
       </c>
-      <c r="G33" s="19">
+      <c r="G33" s="20">
         <f>B$8</f>
         <v/>
       </c>
-      <c r="H33" s="19">
+      <c r="H33" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,H32-(E32-F32-G32)),0)</f>
         <v/>
       </c>
-      <c r="I33" s="19">
+      <c r="I33" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(E33,F33+G33+H33+0.5*MAX(0,(E33-F33-G33)-H33)),C33*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="J33" s="20">
+      <c r="J33" s="19">
         <f>I33-F33-G33</f>
         <v/>
       </c>
-      <c r="K33" s="19">
+      <c r="K33" s="20">
         <f>K32+J33</f>
         <v/>
       </c>
-      <c r="L33" s="20">
+      <c r="L33" s="19">
         <f>E33-I33</f>
         <v/>
       </c>
-      <c r="M33" s="19">
+      <c r="M33" s="20">
         <f>M32+L33</f>
         <v/>
       </c>
       <c r="N33" s="21">
-        <f>IF(J33&gt;=Ipotesi!$B$14,A33,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(E33-F33-G33)/2,J33)&gt;=Ipotesi!$B$14,A33,"")</f>
         <v/>
       </c>
       <c r="O33" s="21">
@@ -5700,51 +5848,51 @@
         <v>2</v>
       </c>
       <c r="S33" s="4">
-        <f>ROUND(C$4*Stagionalità!$B$7,0)</f>
-        <v/>
-      </c>
-      <c r="T33" s="19">
+        <f>ROUND((C$3+(C$13-C$3)*4/12)*Stagionalità!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="T33" s="20">
         <f>S33*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="U33" s="19">
+      <c r="U33" s="20">
         <f>S33*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="V33" s="19">
+      <c r="V33" s="20">
         <f>'Costi B2Brand'!$D$6</f>
         <v/>
       </c>
-      <c r="W33" s="19">
+      <c r="W33" s="20">
         <f>C$8</f>
         <v/>
       </c>
-      <c r="X33" s="19">
+      <c r="X33" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,X32-(U32-V32-W32)),0)</f>
         <v/>
       </c>
-      <c r="Y33" s="19">
+      <c r="Y33" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(U33,V33+W33+X33+0.5*MAX(0,(U33-V33-W33)-X33)),S33*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="Z33" s="20">
+      <c r="Z33" s="19">
         <f>Y33-V33-W33</f>
         <v/>
       </c>
-      <c r="AA33" s="19">
+      <c r="AA33" s="20">
         <f>AA32+Z33</f>
         <v/>
       </c>
-      <c r="AB33" s="20">
+      <c r="AB33" s="19">
         <f>U33-Y33</f>
         <v/>
       </c>
-      <c r="AC33" s="19">
+      <c r="AC33" s="20">
         <f>AC32+AB33</f>
         <v/>
       </c>
       <c r="AD33" s="21">
-        <f>IF(Z33&gt;=Ipotesi!$B$14,Q33,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(U33-V33-W33)/2,Z33)&gt;=Ipotesi!$B$14,Q33,"")</f>
         <v/>
       </c>
       <c r="AE33" s="21">
@@ -5758,51 +5906,51 @@
         <v>2</v>
       </c>
       <c r="AI33" s="4">
-        <f>ROUND(D$4*Stagionalità!$B$7,0)</f>
-        <v/>
-      </c>
-      <c r="AJ33" s="19">
+        <f>ROUND((D$3+(D$13-D$3)*4/12)*Stagionalità!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="AJ33" s="20">
         <f>AI33*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="AK33" s="19">
+      <c r="AK33" s="20">
         <f>AI33*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AL33" s="19">
+      <c r="AL33" s="20">
         <f>'Costi B2Brand'!$D$6</f>
         <v/>
       </c>
-      <c r="AM33" s="19">
+      <c r="AM33" s="20">
         <f>D$8</f>
         <v/>
       </c>
-      <c r="AN33" s="19">
+      <c r="AN33" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,AN32-(AK32-AL32-AM32)),0)</f>
         <v/>
       </c>
-      <c r="AO33" s="19">
+      <c r="AO33" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(AK33,AL33+AM33+AN33+0.5*MAX(0,(AK33-AL33-AM33)-AN33)),AI33*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AP33" s="20">
+      <c r="AP33" s="19">
         <f>AO33-AL33-AM33</f>
         <v/>
       </c>
-      <c r="AQ33" s="19">
+      <c r="AQ33" s="20">
         <f>AQ32+AP33</f>
         <v/>
       </c>
-      <c r="AR33" s="20">
+      <c r="AR33" s="19">
         <f>AK33-AO33</f>
         <v/>
       </c>
-      <c r="AS33" s="19">
+      <c r="AS33" s="20">
         <f>AS32+AR33</f>
         <v/>
       </c>
       <c r="AT33" s="21">
-        <f>IF(AP33&gt;=Ipotesi!$B$14,AG33,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(AK33-AL33-AM33)/2,AP33)&gt;=Ipotesi!$B$14,AG33,"")</f>
         <v/>
       </c>
       <c r="AU33" s="21">
@@ -5818,51 +5966,51 @@
         <v>2</v>
       </c>
       <c r="C34" s="4">
-        <f>ROUND(B$4*Stagionalità!$B$8,0)</f>
-        <v/>
-      </c>
-      <c r="D34" s="19">
+        <f>ROUND((B$3+(B$13-B$3)*5/12)*Stagionalità!$B$8,0)</f>
+        <v/>
+      </c>
+      <c r="D34" s="20">
         <f>C34*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="E34" s="19">
+      <c r="E34" s="20">
         <f>C34*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="F34" s="19">
+      <c r="F34" s="20">
         <f>'Costi B2Brand'!$D$6</f>
         <v/>
       </c>
-      <c r="G34" s="19">
+      <c r="G34" s="20">
         <f>B$8</f>
         <v/>
       </c>
-      <c r="H34" s="19">
+      <c r="H34" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,H33-(E33-F33-G33)),0)</f>
         <v/>
       </c>
-      <c r="I34" s="19">
+      <c r="I34" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(E34,F34+G34+H34+0.5*MAX(0,(E34-F34-G34)-H34)),C34*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="J34" s="20">
+      <c r="J34" s="19">
         <f>I34-F34-G34</f>
         <v/>
       </c>
-      <c r="K34" s="19">
+      <c r="K34" s="20">
         <f>K33+J34</f>
         <v/>
       </c>
-      <c r="L34" s="20">
+      <c r="L34" s="19">
         <f>E34-I34</f>
         <v/>
       </c>
-      <c r="M34" s="19">
+      <c r="M34" s="20">
         <f>M33+L34</f>
         <v/>
       </c>
       <c r="N34" s="21">
-        <f>IF(J34&gt;=Ipotesi!$B$14,A34,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(E34-F34-G34)/2,J34)&gt;=Ipotesi!$B$14,A34,"")</f>
         <v/>
       </c>
       <c r="O34" s="21">
@@ -5876,51 +6024,51 @@
         <v>2</v>
       </c>
       <c r="S34" s="4">
-        <f>ROUND(C$4*Stagionalità!$B$8,0)</f>
-        <v/>
-      </c>
-      <c r="T34" s="19">
+        <f>ROUND((C$3+(C$13-C$3)*5/12)*Stagionalità!$B$8,0)</f>
+        <v/>
+      </c>
+      <c r="T34" s="20">
         <f>S34*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="U34" s="19">
+      <c r="U34" s="20">
         <f>S34*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="V34" s="19">
+      <c r="V34" s="20">
         <f>'Costi B2Brand'!$D$6</f>
         <v/>
       </c>
-      <c r="W34" s="19">
+      <c r="W34" s="20">
         <f>C$8</f>
         <v/>
       </c>
-      <c r="X34" s="19">
+      <c r="X34" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,X33-(U33-V33-W33)),0)</f>
         <v/>
       </c>
-      <c r="Y34" s="19">
+      <c r="Y34" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(U34,V34+W34+X34+0.5*MAX(0,(U34-V34-W34)-X34)),S34*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="Z34" s="20">
+      <c r="Z34" s="19">
         <f>Y34-V34-W34</f>
         <v/>
       </c>
-      <c r="AA34" s="19">
+      <c r="AA34" s="20">
         <f>AA33+Z34</f>
         <v/>
       </c>
-      <c r="AB34" s="20">
+      <c r="AB34" s="19">
         <f>U34-Y34</f>
         <v/>
       </c>
-      <c r="AC34" s="19">
+      <c r="AC34" s="20">
         <f>AC33+AB34</f>
         <v/>
       </c>
       <c r="AD34" s="21">
-        <f>IF(Z34&gt;=Ipotesi!$B$14,Q34,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(U34-V34-W34)/2,Z34)&gt;=Ipotesi!$B$14,Q34,"")</f>
         <v/>
       </c>
       <c r="AE34" s="21">
@@ -5934,51 +6082,51 @@
         <v>2</v>
       </c>
       <c r="AI34" s="4">
-        <f>ROUND(D$4*Stagionalità!$B$8,0)</f>
-        <v/>
-      </c>
-      <c r="AJ34" s="19">
+        <f>ROUND((D$3+(D$13-D$3)*5/12)*Stagionalità!$B$8,0)</f>
+        <v/>
+      </c>
+      <c r="AJ34" s="20">
         <f>AI34*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="AK34" s="19">
+      <c r="AK34" s="20">
         <f>AI34*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AL34" s="19">
+      <c r="AL34" s="20">
         <f>'Costi B2Brand'!$D$6</f>
         <v/>
       </c>
-      <c r="AM34" s="19">
+      <c r="AM34" s="20">
         <f>D$8</f>
         <v/>
       </c>
-      <c r="AN34" s="19">
+      <c r="AN34" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,AN33-(AK33-AL33-AM33)),0)</f>
         <v/>
       </c>
-      <c r="AO34" s="19">
+      <c r="AO34" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(AK34,AL34+AM34+AN34+0.5*MAX(0,(AK34-AL34-AM34)-AN34)),AI34*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AP34" s="20">
+      <c r="AP34" s="19">
         <f>AO34-AL34-AM34</f>
         <v/>
       </c>
-      <c r="AQ34" s="19">
+      <c r="AQ34" s="20">
         <f>AQ33+AP34</f>
         <v/>
       </c>
-      <c r="AR34" s="20">
+      <c r="AR34" s="19">
         <f>AK34-AO34</f>
         <v/>
       </c>
-      <c r="AS34" s="19">
+      <c r="AS34" s="20">
         <f>AS33+AR34</f>
         <v/>
       </c>
       <c r="AT34" s="21">
-        <f>IF(AP34&gt;=Ipotesi!$B$14,AG34,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(AK34-AL34-AM34)/2,AP34)&gt;=Ipotesi!$B$14,AG34,"")</f>
         <v/>
       </c>
       <c r="AU34" s="21">
@@ -5994,51 +6142,51 @@
         <v>2</v>
       </c>
       <c r="C35" s="4">
-        <f>ROUND(B$4*Stagionalità!$B$9,0)</f>
-        <v/>
-      </c>
-      <c r="D35" s="19">
+        <f>ROUND((B$3+(B$13-B$3)*6/12)*Stagionalità!$B$9,0)</f>
+        <v/>
+      </c>
+      <c r="D35" s="20">
         <f>C35*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="E35" s="19">
+      <c r="E35" s="20">
         <f>C35*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="F35" s="19">
+      <c r="F35" s="20">
         <f>'Costi B2Brand'!$D$6</f>
         <v/>
       </c>
-      <c r="G35" s="19">
+      <c r="G35" s="20">
         <f>B$8</f>
         <v/>
       </c>
-      <c r="H35" s="19">
+      <c r="H35" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,H34-(E34-F34-G34)),0)</f>
         <v/>
       </c>
-      <c r="I35" s="19">
+      <c r="I35" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(E35,F35+G35+H35+0.5*MAX(0,(E35-F35-G35)-H35)),C35*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="J35" s="20">
+      <c r="J35" s="19">
         <f>I35-F35-G35</f>
         <v/>
       </c>
-      <c r="K35" s="19">
+      <c r="K35" s="20">
         <f>K34+J35</f>
         <v/>
       </c>
-      <c r="L35" s="20">
+      <c r="L35" s="19">
         <f>E35-I35</f>
         <v/>
       </c>
-      <c r="M35" s="19">
+      <c r="M35" s="20">
         <f>M34+L35</f>
         <v/>
       </c>
       <c r="N35" s="21">
-        <f>IF(J35&gt;=Ipotesi!$B$14,A35,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(E35-F35-G35)/2,J35)&gt;=Ipotesi!$B$14,A35,"")</f>
         <v/>
       </c>
       <c r="O35" s="21">
@@ -6052,51 +6200,51 @@
         <v>2</v>
       </c>
       <c r="S35" s="4">
-        <f>ROUND(C$4*Stagionalità!$B$9,0)</f>
-        <v/>
-      </c>
-      <c r="T35" s="19">
+        <f>ROUND((C$3+(C$13-C$3)*6/12)*Stagionalità!$B$9,0)</f>
+        <v/>
+      </c>
+      <c r="T35" s="20">
         <f>S35*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="U35" s="19">
+      <c r="U35" s="20">
         <f>S35*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="V35" s="19">
+      <c r="V35" s="20">
         <f>'Costi B2Brand'!$D$6</f>
         <v/>
       </c>
-      <c r="W35" s="19">
+      <c r="W35" s="20">
         <f>C$8</f>
         <v/>
       </c>
-      <c r="X35" s="19">
+      <c r="X35" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,X34-(U34-V34-W34)),0)</f>
         <v/>
       </c>
-      <c r="Y35" s="19">
+      <c r="Y35" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(U35,V35+W35+X35+0.5*MAX(0,(U35-V35-W35)-X35)),S35*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="Z35" s="20">
+      <c r="Z35" s="19">
         <f>Y35-V35-W35</f>
         <v/>
       </c>
-      <c r="AA35" s="19">
+      <c r="AA35" s="20">
         <f>AA34+Z35</f>
         <v/>
       </c>
-      <c r="AB35" s="20">
+      <c r="AB35" s="19">
         <f>U35-Y35</f>
         <v/>
       </c>
-      <c r="AC35" s="19">
+      <c r="AC35" s="20">
         <f>AC34+AB35</f>
         <v/>
       </c>
       <c r="AD35" s="21">
-        <f>IF(Z35&gt;=Ipotesi!$B$14,Q35,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(U35-V35-W35)/2,Z35)&gt;=Ipotesi!$B$14,Q35,"")</f>
         <v/>
       </c>
       <c r="AE35" s="21">
@@ -6110,51 +6258,51 @@
         <v>2</v>
       </c>
       <c r="AI35" s="4">
-        <f>ROUND(D$4*Stagionalità!$B$9,0)</f>
-        <v/>
-      </c>
-      <c r="AJ35" s="19">
+        <f>ROUND((D$3+(D$13-D$3)*6/12)*Stagionalità!$B$9,0)</f>
+        <v/>
+      </c>
+      <c r="AJ35" s="20">
         <f>AI35*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="AK35" s="19">
+      <c r="AK35" s="20">
         <f>AI35*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AL35" s="19">
+      <c r="AL35" s="20">
         <f>'Costi B2Brand'!$D$6</f>
         <v/>
       </c>
-      <c r="AM35" s="19">
+      <c r="AM35" s="20">
         <f>D$8</f>
         <v/>
       </c>
-      <c r="AN35" s="19">
+      <c r="AN35" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,AN34-(AK34-AL34-AM34)),0)</f>
         <v/>
       </c>
-      <c r="AO35" s="19">
+      <c r="AO35" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(AK35,AL35+AM35+AN35+0.5*MAX(0,(AK35-AL35-AM35)-AN35)),AI35*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AP35" s="20">
+      <c r="AP35" s="19">
         <f>AO35-AL35-AM35</f>
         <v/>
       </c>
-      <c r="AQ35" s="19">
+      <c r="AQ35" s="20">
         <f>AQ34+AP35</f>
         <v/>
       </c>
-      <c r="AR35" s="20">
+      <c r="AR35" s="19">
         <f>AK35-AO35</f>
         <v/>
       </c>
-      <c r="AS35" s="19">
+      <c r="AS35" s="20">
         <f>AS34+AR35</f>
         <v/>
       </c>
       <c r="AT35" s="21">
-        <f>IF(AP35&gt;=Ipotesi!$B$14,AG35,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(AK35-AL35-AM35)/2,AP35)&gt;=Ipotesi!$B$14,AG35,"")</f>
         <v/>
       </c>
       <c r="AU35" s="21">
@@ -6170,51 +6318,51 @@
         <v>2</v>
       </c>
       <c r="C36" s="4">
-        <f>ROUND(B$4*Stagionalità!$B$10,0)</f>
-        <v/>
-      </c>
-      <c r="D36" s="19">
+        <f>ROUND((B$3+(B$13-B$3)*7/12)*Stagionalità!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="D36" s="20">
         <f>C36*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="E36" s="19">
+      <c r="E36" s="20">
         <f>C36*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="F36" s="19">
+      <c r="F36" s="20">
         <f>'Costi B2Brand'!$D$6</f>
         <v/>
       </c>
-      <c r="G36" s="19">
+      <c r="G36" s="20">
         <f>B$8</f>
         <v/>
       </c>
-      <c r="H36" s="19">
+      <c r="H36" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,H35-(E35-F35-G35)),0)</f>
         <v/>
       </c>
-      <c r="I36" s="19">
+      <c r="I36" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(E36,F36+G36+H36+0.5*MAX(0,(E36-F36-G36)-H36)),C36*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="J36" s="20">
+      <c r="J36" s="19">
         <f>I36-F36-G36</f>
         <v/>
       </c>
-      <c r="K36" s="19">
+      <c r="K36" s="20">
         <f>K35+J36</f>
         <v/>
       </c>
-      <c r="L36" s="20">
+      <c r="L36" s="19">
         <f>E36-I36</f>
         <v/>
       </c>
-      <c r="M36" s="19">
+      <c r="M36" s="20">
         <f>M35+L36</f>
         <v/>
       </c>
       <c r="N36" s="21">
-        <f>IF(J36&gt;=Ipotesi!$B$14,A36,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(E36-F36-G36)/2,J36)&gt;=Ipotesi!$B$14,A36,"")</f>
         <v/>
       </c>
       <c r="O36" s="21">
@@ -6228,51 +6376,51 @@
         <v>2</v>
       </c>
       <c r="S36" s="4">
-        <f>ROUND(C$4*Stagionalità!$B$10,0)</f>
-        <v/>
-      </c>
-      <c r="T36" s="19">
+        <f>ROUND((C$3+(C$13-C$3)*7/12)*Stagionalità!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="T36" s="20">
         <f>S36*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="U36" s="19">
+      <c r="U36" s="20">
         <f>S36*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="V36" s="19">
+      <c r="V36" s="20">
         <f>'Costi B2Brand'!$D$6</f>
         <v/>
       </c>
-      <c r="W36" s="19">
+      <c r="W36" s="20">
         <f>C$8</f>
         <v/>
       </c>
-      <c r="X36" s="19">
+      <c r="X36" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,X35-(U35-V35-W35)),0)</f>
         <v/>
       </c>
-      <c r="Y36" s="19">
+      <c r="Y36" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(U36,V36+W36+X36+0.5*MAX(0,(U36-V36-W36)-X36)),S36*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="Z36" s="20">
+      <c r="Z36" s="19">
         <f>Y36-V36-W36</f>
         <v/>
       </c>
-      <c r="AA36" s="19">
+      <c r="AA36" s="20">
         <f>AA35+Z36</f>
         <v/>
       </c>
-      <c r="AB36" s="20">
+      <c r="AB36" s="19">
         <f>U36-Y36</f>
         <v/>
       </c>
-      <c r="AC36" s="19">
+      <c r="AC36" s="20">
         <f>AC35+AB36</f>
         <v/>
       </c>
       <c r="AD36" s="21">
-        <f>IF(Z36&gt;=Ipotesi!$B$14,Q36,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(U36-V36-W36)/2,Z36)&gt;=Ipotesi!$B$14,Q36,"")</f>
         <v/>
       </c>
       <c r="AE36" s="21">
@@ -6286,51 +6434,51 @@
         <v>2</v>
       </c>
       <c r="AI36" s="4">
-        <f>ROUND(D$4*Stagionalità!$B$10,0)</f>
-        <v/>
-      </c>
-      <c r="AJ36" s="19">
+        <f>ROUND((D$3+(D$13-D$3)*7/12)*Stagionalità!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="AJ36" s="20">
         <f>AI36*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="AK36" s="19">
+      <c r="AK36" s="20">
         <f>AI36*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AL36" s="19">
+      <c r="AL36" s="20">
         <f>'Costi B2Brand'!$D$6</f>
         <v/>
       </c>
-      <c r="AM36" s="19">
+      <c r="AM36" s="20">
         <f>D$8</f>
         <v/>
       </c>
-      <c r="AN36" s="19">
+      <c r="AN36" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,AN35-(AK35-AL35-AM35)),0)</f>
         <v/>
       </c>
-      <c r="AO36" s="19">
+      <c r="AO36" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(AK36,AL36+AM36+AN36+0.5*MAX(0,(AK36-AL36-AM36)-AN36)),AI36*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AP36" s="20">
+      <c r="AP36" s="19">
         <f>AO36-AL36-AM36</f>
         <v/>
       </c>
-      <c r="AQ36" s="19">
+      <c r="AQ36" s="20">
         <f>AQ35+AP36</f>
         <v/>
       </c>
-      <c r="AR36" s="20">
+      <c r="AR36" s="19">
         <f>AK36-AO36</f>
         <v/>
       </c>
-      <c r="AS36" s="19">
+      <c r="AS36" s="20">
         <f>AS35+AR36</f>
         <v/>
       </c>
       <c r="AT36" s="21">
-        <f>IF(AP36&gt;=Ipotesi!$B$14,AG36,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(AK36-AL36-AM36)/2,AP36)&gt;=Ipotesi!$B$14,AG36,"")</f>
         <v/>
       </c>
       <c r="AU36" s="21">
@@ -6346,51 +6494,51 @@
         <v>2</v>
       </c>
       <c r="C37" s="4">
-        <f>ROUND(B$4*Stagionalità!$B$11,0)</f>
-        <v/>
-      </c>
-      <c r="D37" s="19">
+        <f>ROUND((B$3+(B$13-B$3)*8/12)*Stagionalità!$B$11,0)</f>
+        <v/>
+      </c>
+      <c r="D37" s="20">
         <f>C37*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="E37" s="19">
+      <c r="E37" s="20">
         <f>C37*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="F37" s="19">
+      <c r="F37" s="20">
         <f>'Costi B2Brand'!$D$6</f>
         <v/>
       </c>
-      <c r="G37" s="19">
+      <c r="G37" s="20">
         <f>B$8</f>
         <v/>
       </c>
-      <c r="H37" s="19">
+      <c r="H37" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,H36-(E36-F36-G36)),0)</f>
         <v/>
       </c>
-      <c r="I37" s="19">
+      <c r="I37" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(E37,F37+G37+H37+0.5*MAX(0,(E37-F37-G37)-H37)),C37*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="J37" s="20">
+      <c r="J37" s="19">
         <f>I37-F37-G37</f>
         <v/>
       </c>
-      <c r="K37" s="19">
+      <c r="K37" s="20">
         <f>K36+J37</f>
         <v/>
       </c>
-      <c r="L37" s="20">
+      <c r="L37" s="19">
         <f>E37-I37</f>
         <v/>
       </c>
-      <c r="M37" s="19">
+      <c r="M37" s="20">
         <f>M36+L37</f>
         <v/>
       </c>
       <c r="N37" s="21">
-        <f>IF(J37&gt;=Ipotesi!$B$14,A37,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(E37-F37-G37)/2,J37)&gt;=Ipotesi!$B$14,A37,"")</f>
         <v/>
       </c>
       <c r="O37" s="21">
@@ -6404,51 +6552,51 @@
         <v>2</v>
       </c>
       <c r="S37" s="4">
-        <f>ROUND(C$4*Stagionalità!$B$11,0)</f>
-        <v/>
-      </c>
-      <c r="T37" s="19">
+        <f>ROUND((C$3+(C$13-C$3)*8/12)*Stagionalità!$B$11,0)</f>
+        <v/>
+      </c>
+      <c r="T37" s="20">
         <f>S37*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="U37" s="19">
+      <c r="U37" s="20">
         <f>S37*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="V37" s="19">
+      <c r="V37" s="20">
         <f>'Costi B2Brand'!$D$6</f>
         <v/>
       </c>
-      <c r="W37" s="19">
+      <c r="W37" s="20">
         <f>C$8</f>
         <v/>
       </c>
-      <c r="X37" s="19">
+      <c r="X37" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,X36-(U36-V36-W36)),0)</f>
         <v/>
       </c>
-      <c r="Y37" s="19">
+      <c r="Y37" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(U37,V37+W37+X37+0.5*MAX(0,(U37-V37-W37)-X37)),S37*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="Z37" s="20">
+      <c r="Z37" s="19">
         <f>Y37-V37-W37</f>
         <v/>
       </c>
-      <c r="AA37" s="19">
+      <c r="AA37" s="20">
         <f>AA36+Z37</f>
         <v/>
       </c>
-      <c r="AB37" s="20">
+      <c r="AB37" s="19">
         <f>U37-Y37</f>
         <v/>
       </c>
-      <c r="AC37" s="19">
+      <c r="AC37" s="20">
         <f>AC36+AB37</f>
         <v/>
       </c>
       <c r="AD37" s="21">
-        <f>IF(Z37&gt;=Ipotesi!$B$14,Q37,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(U37-V37-W37)/2,Z37)&gt;=Ipotesi!$B$14,Q37,"")</f>
         <v/>
       </c>
       <c r="AE37" s="21">
@@ -6462,51 +6610,51 @@
         <v>2</v>
       </c>
       <c r="AI37" s="4">
-        <f>ROUND(D$4*Stagionalità!$B$11,0)</f>
-        <v/>
-      </c>
-      <c r="AJ37" s="19">
+        <f>ROUND((D$3+(D$13-D$3)*8/12)*Stagionalità!$B$11,0)</f>
+        <v/>
+      </c>
+      <c r="AJ37" s="20">
         <f>AI37*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="AK37" s="19">
+      <c r="AK37" s="20">
         <f>AI37*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AL37" s="19">
+      <c r="AL37" s="20">
         <f>'Costi B2Brand'!$D$6</f>
         <v/>
       </c>
-      <c r="AM37" s="19">
+      <c r="AM37" s="20">
         <f>D$8</f>
         <v/>
       </c>
-      <c r="AN37" s="19">
+      <c r="AN37" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,AN36-(AK36-AL36-AM36)),0)</f>
         <v/>
       </c>
-      <c r="AO37" s="19">
+      <c r="AO37" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(AK37,AL37+AM37+AN37+0.5*MAX(0,(AK37-AL37-AM37)-AN37)),AI37*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AP37" s="20">
+      <c r="AP37" s="19">
         <f>AO37-AL37-AM37</f>
         <v/>
       </c>
-      <c r="AQ37" s="19">
+      <c r="AQ37" s="20">
         <f>AQ36+AP37</f>
         <v/>
       </c>
-      <c r="AR37" s="20">
+      <c r="AR37" s="19">
         <f>AK37-AO37</f>
         <v/>
       </c>
-      <c r="AS37" s="19">
+      <c r="AS37" s="20">
         <f>AS36+AR37</f>
         <v/>
       </c>
       <c r="AT37" s="21">
-        <f>IF(AP37&gt;=Ipotesi!$B$14,AG37,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(AK37-AL37-AM37)/2,AP37)&gt;=Ipotesi!$B$14,AG37,"")</f>
         <v/>
       </c>
       <c r="AU37" s="21">
@@ -6522,51 +6670,51 @@
         <v>2</v>
       </c>
       <c r="C38" s="4">
-        <f>ROUND(B$4*Stagionalità!$B$12,0)</f>
-        <v/>
-      </c>
-      <c r="D38" s="19">
+        <f>ROUND((B$3+(B$13-B$3)*9/12)*Stagionalità!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="D38" s="20">
         <f>C38*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="E38" s="19">
+      <c r="E38" s="20">
         <f>C38*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="F38" s="19">
+      <c r="F38" s="20">
         <f>'Costi B2Brand'!$D$6</f>
         <v/>
       </c>
-      <c r="G38" s="19">
+      <c r="G38" s="20">
         <f>B$8</f>
         <v/>
       </c>
-      <c r="H38" s="19">
+      <c r="H38" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,H37-(E37-F37-G37)),0)</f>
         <v/>
       </c>
-      <c r="I38" s="19">
+      <c r="I38" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(E38,F38+G38+H38+0.5*MAX(0,(E38-F38-G38)-H38)),C38*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="J38" s="20">
+      <c r="J38" s="19">
         <f>I38-F38-G38</f>
         <v/>
       </c>
-      <c r="K38" s="19">
+      <c r="K38" s="20">
         <f>K37+J38</f>
         <v/>
       </c>
-      <c r="L38" s="20">
+      <c r="L38" s="19">
         <f>E38-I38</f>
         <v/>
       </c>
-      <c r="M38" s="19">
+      <c r="M38" s="20">
         <f>M37+L38</f>
         <v/>
       </c>
       <c r="N38" s="21">
-        <f>IF(J38&gt;=Ipotesi!$B$14,A38,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(E38-F38-G38)/2,J38)&gt;=Ipotesi!$B$14,A38,"")</f>
         <v/>
       </c>
       <c r="O38" s="21">
@@ -6580,51 +6728,51 @@
         <v>2</v>
       </c>
       <c r="S38" s="4">
-        <f>ROUND(C$4*Stagionalità!$B$12,0)</f>
-        <v/>
-      </c>
-      <c r="T38" s="19">
+        <f>ROUND((C$3+(C$13-C$3)*9/12)*Stagionalità!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="T38" s="20">
         <f>S38*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="U38" s="19">
+      <c r="U38" s="20">
         <f>S38*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="V38" s="19">
+      <c r="V38" s="20">
         <f>'Costi B2Brand'!$D$6</f>
         <v/>
       </c>
-      <c r="W38" s="19">
+      <c r="W38" s="20">
         <f>C$8</f>
         <v/>
       </c>
-      <c r="X38" s="19">
+      <c r="X38" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,X37-(U37-V37-W37)),0)</f>
         <v/>
       </c>
-      <c r="Y38" s="19">
+      <c r="Y38" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(U38,V38+W38+X38+0.5*MAX(0,(U38-V38-W38)-X38)),S38*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="Z38" s="20">
+      <c r="Z38" s="19">
         <f>Y38-V38-W38</f>
         <v/>
       </c>
-      <c r="AA38" s="19">
+      <c r="AA38" s="20">
         <f>AA37+Z38</f>
         <v/>
       </c>
-      <c r="AB38" s="20">
+      <c r="AB38" s="19">
         <f>U38-Y38</f>
         <v/>
       </c>
-      <c r="AC38" s="19">
+      <c r="AC38" s="20">
         <f>AC37+AB38</f>
         <v/>
       </c>
       <c r="AD38" s="21">
-        <f>IF(Z38&gt;=Ipotesi!$B$14,Q38,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(U38-V38-W38)/2,Z38)&gt;=Ipotesi!$B$14,Q38,"")</f>
         <v/>
       </c>
       <c r="AE38" s="21">
@@ -6638,51 +6786,51 @@
         <v>2</v>
       </c>
       <c r="AI38" s="4">
-        <f>ROUND(D$4*Stagionalità!$B$12,0)</f>
-        <v/>
-      </c>
-      <c r="AJ38" s="19">
+        <f>ROUND((D$3+(D$13-D$3)*9/12)*Stagionalità!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="AJ38" s="20">
         <f>AI38*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="AK38" s="19">
+      <c r="AK38" s="20">
         <f>AI38*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AL38" s="19">
+      <c r="AL38" s="20">
         <f>'Costi B2Brand'!$D$6</f>
         <v/>
       </c>
-      <c r="AM38" s="19">
+      <c r="AM38" s="20">
         <f>D$8</f>
         <v/>
       </c>
-      <c r="AN38" s="19">
+      <c r="AN38" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,AN37-(AK37-AL37-AM37)),0)</f>
         <v/>
       </c>
-      <c r="AO38" s="19">
+      <c r="AO38" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(AK38,AL38+AM38+AN38+0.5*MAX(0,(AK38-AL38-AM38)-AN38)),AI38*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AP38" s="20">
+      <c r="AP38" s="19">
         <f>AO38-AL38-AM38</f>
         <v/>
       </c>
-      <c r="AQ38" s="19">
+      <c r="AQ38" s="20">
         <f>AQ37+AP38</f>
         <v/>
       </c>
-      <c r="AR38" s="20">
+      <c r="AR38" s="19">
         <f>AK38-AO38</f>
         <v/>
       </c>
-      <c r="AS38" s="19">
+      <c r="AS38" s="20">
         <f>AS37+AR38</f>
         <v/>
       </c>
       <c r="AT38" s="21">
-        <f>IF(AP38&gt;=Ipotesi!$B$14,AG38,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(AK38-AL38-AM38)/2,AP38)&gt;=Ipotesi!$B$14,AG38,"")</f>
         <v/>
       </c>
       <c r="AU38" s="21">
@@ -6698,51 +6846,51 @@
         <v>2</v>
       </c>
       <c r="C39" s="4">
-        <f>ROUND(B$4*Stagionalità!$B$13,0)</f>
-        <v/>
-      </c>
-      <c r="D39" s="19">
+        <f>ROUND((B$3+(B$13-B$3)*10/12)*Stagionalità!$B$13,0)</f>
+        <v/>
+      </c>
+      <c r="D39" s="20">
         <f>C39*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="E39" s="19">
+      <c r="E39" s="20">
         <f>C39*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="F39" s="19">
+      <c r="F39" s="20">
         <f>'Costi B2Brand'!$D$6</f>
         <v/>
       </c>
-      <c r="G39" s="19">
+      <c r="G39" s="20">
         <f>B$8</f>
         <v/>
       </c>
-      <c r="H39" s="19">
+      <c r="H39" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,H38-(E38-F38-G38)),0)</f>
         <v/>
       </c>
-      <c r="I39" s="19">
+      <c r="I39" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(E39,F39+G39+H39+0.5*MAX(0,(E39-F39-G39)-H39)),C39*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="J39" s="20">
+      <c r="J39" s="19">
         <f>I39-F39-G39</f>
         <v/>
       </c>
-      <c r="K39" s="19">
+      <c r="K39" s="20">
         <f>K38+J39</f>
         <v/>
       </c>
-      <c r="L39" s="20">
+      <c r="L39" s="19">
         <f>E39-I39</f>
         <v/>
       </c>
-      <c r="M39" s="19">
+      <c r="M39" s="20">
         <f>M38+L39</f>
         <v/>
       </c>
       <c r="N39" s="21">
-        <f>IF(J39&gt;=Ipotesi!$B$14,A39,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(E39-F39-G39)/2,J39)&gt;=Ipotesi!$B$14,A39,"")</f>
         <v/>
       </c>
       <c r="O39" s="21">
@@ -6756,51 +6904,51 @@
         <v>2</v>
       </c>
       <c r="S39" s="4">
-        <f>ROUND(C$4*Stagionalità!$B$13,0)</f>
-        <v/>
-      </c>
-      <c r="T39" s="19">
+        <f>ROUND((C$3+(C$13-C$3)*10/12)*Stagionalità!$B$13,0)</f>
+        <v/>
+      </c>
+      <c r="T39" s="20">
         <f>S39*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="U39" s="19">
+      <c r="U39" s="20">
         <f>S39*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="V39" s="19">
+      <c r="V39" s="20">
         <f>'Costi B2Brand'!$D$6</f>
         <v/>
       </c>
-      <c r="W39" s="19">
+      <c r="W39" s="20">
         <f>C$8</f>
         <v/>
       </c>
-      <c r="X39" s="19">
+      <c r="X39" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,X38-(U38-V38-W38)),0)</f>
         <v/>
       </c>
-      <c r="Y39" s="19">
+      <c r="Y39" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(U39,V39+W39+X39+0.5*MAX(0,(U39-V39-W39)-X39)),S39*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="Z39" s="20">
+      <c r="Z39" s="19">
         <f>Y39-V39-W39</f>
         <v/>
       </c>
-      <c r="AA39" s="19">
+      <c r="AA39" s="20">
         <f>AA38+Z39</f>
         <v/>
       </c>
-      <c r="AB39" s="20">
+      <c r="AB39" s="19">
         <f>U39-Y39</f>
         <v/>
       </c>
-      <c r="AC39" s="19">
+      <c r="AC39" s="20">
         <f>AC38+AB39</f>
         <v/>
       </c>
       <c r="AD39" s="21">
-        <f>IF(Z39&gt;=Ipotesi!$B$14,Q39,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(U39-V39-W39)/2,Z39)&gt;=Ipotesi!$B$14,Q39,"")</f>
         <v/>
       </c>
       <c r="AE39" s="21">
@@ -6814,51 +6962,51 @@
         <v>2</v>
       </c>
       <c r="AI39" s="4">
-        <f>ROUND(D$4*Stagionalità!$B$13,0)</f>
-        <v/>
-      </c>
-      <c r="AJ39" s="19">
+        <f>ROUND((D$3+(D$13-D$3)*10/12)*Stagionalità!$B$13,0)</f>
+        <v/>
+      </c>
+      <c r="AJ39" s="20">
         <f>AI39*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="AK39" s="19">
+      <c r="AK39" s="20">
         <f>AI39*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AL39" s="19">
+      <c r="AL39" s="20">
         <f>'Costi B2Brand'!$D$6</f>
         <v/>
       </c>
-      <c r="AM39" s="19">
+      <c r="AM39" s="20">
         <f>D$8</f>
         <v/>
       </c>
-      <c r="AN39" s="19">
+      <c r="AN39" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,AN38-(AK38-AL38-AM38)),0)</f>
         <v/>
       </c>
-      <c r="AO39" s="19">
+      <c r="AO39" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(AK39,AL39+AM39+AN39+0.5*MAX(0,(AK39-AL39-AM39)-AN39)),AI39*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AP39" s="20">
+      <c r="AP39" s="19">
         <f>AO39-AL39-AM39</f>
         <v/>
       </c>
-      <c r="AQ39" s="19">
+      <c r="AQ39" s="20">
         <f>AQ38+AP39</f>
         <v/>
       </c>
-      <c r="AR39" s="20">
+      <c r="AR39" s="19">
         <f>AK39-AO39</f>
         <v/>
       </c>
-      <c r="AS39" s="19">
+      <c r="AS39" s="20">
         <f>AS38+AR39</f>
         <v/>
       </c>
       <c r="AT39" s="21">
-        <f>IF(AP39&gt;=Ipotesi!$B$14,AG39,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(AK39-AL39-AM39)/2,AP39)&gt;=Ipotesi!$B$14,AG39,"")</f>
         <v/>
       </c>
       <c r="AU39" s="21">
@@ -6874,51 +7022,51 @@
         <v>2</v>
       </c>
       <c r="C40" s="4">
-        <f>ROUND(B$4*Stagionalità!$B$2,0)</f>
-        <v/>
-      </c>
-      <c r="D40" s="19">
+        <f>ROUND((B$3+(B$13-B$3)*11/12)*Stagionalità!$B$2,0)</f>
+        <v/>
+      </c>
+      <c r="D40" s="20">
         <f>C40*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="E40" s="19">
+      <c r="E40" s="20">
         <f>C40*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="F40" s="19">
+      <c r="F40" s="20">
         <f>'Costi B2Brand'!$D$6</f>
         <v/>
       </c>
-      <c r="G40" s="19">
+      <c r="G40" s="20">
         <f>B$8</f>
         <v/>
       </c>
-      <c r="H40" s="19">
+      <c r="H40" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,H39-(E39-F39-G39)),0)</f>
         <v/>
       </c>
-      <c r="I40" s="19">
+      <c r="I40" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(E40,F40+G40+H40+0.5*MAX(0,(E40-F40-G40)-H40)),C40*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="J40" s="20">
+      <c r="J40" s="19">
         <f>I40-F40-G40</f>
         <v/>
       </c>
-      <c r="K40" s="19">
+      <c r="K40" s="20">
         <f>K39+J40</f>
         <v/>
       </c>
-      <c r="L40" s="20">
+      <c r="L40" s="19">
         <f>E40-I40</f>
         <v/>
       </c>
-      <c r="M40" s="19">
+      <c r="M40" s="20">
         <f>M39+L40</f>
         <v/>
       </c>
       <c r="N40" s="21">
-        <f>IF(J40&gt;=Ipotesi!$B$14,A40,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(E40-F40-G40)/2,J40)&gt;=Ipotesi!$B$14,A40,"")</f>
         <v/>
       </c>
       <c r="O40" s="21">
@@ -6932,51 +7080,51 @@
         <v>2</v>
       </c>
       <c r="S40" s="4">
-        <f>ROUND(C$4*Stagionalità!$B$2,0)</f>
-        <v/>
-      </c>
-      <c r="T40" s="19">
+        <f>ROUND((C$3+(C$13-C$3)*11/12)*Stagionalità!$B$2,0)</f>
+        <v/>
+      </c>
+      <c r="T40" s="20">
         <f>S40*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="U40" s="19">
+      <c r="U40" s="20">
         <f>S40*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="V40" s="19">
+      <c r="V40" s="20">
         <f>'Costi B2Brand'!$D$6</f>
         <v/>
       </c>
-      <c r="W40" s="19">
+      <c r="W40" s="20">
         <f>C$8</f>
         <v/>
       </c>
-      <c r="X40" s="19">
+      <c r="X40" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,X39-(U39-V39-W39)),0)</f>
         <v/>
       </c>
-      <c r="Y40" s="19">
+      <c r="Y40" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(U40,V40+W40+X40+0.5*MAX(0,(U40-V40-W40)-X40)),S40*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="Z40" s="20">
+      <c r="Z40" s="19">
         <f>Y40-V40-W40</f>
         <v/>
       </c>
-      <c r="AA40" s="19">
+      <c r="AA40" s="20">
         <f>AA39+Z40</f>
         <v/>
       </c>
-      <c r="AB40" s="20">
+      <c r="AB40" s="19">
         <f>U40-Y40</f>
         <v/>
       </c>
-      <c r="AC40" s="19">
+      <c r="AC40" s="20">
         <f>AC39+AB40</f>
         <v/>
       </c>
       <c r="AD40" s="21">
-        <f>IF(Z40&gt;=Ipotesi!$B$14,Q40,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(U40-V40-W40)/2,Z40)&gt;=Ipotesi!$B$14,Q40,"")</f>
         <v/>
       </c>
       <c r="AE40" s="21">
@@ -6990,51 +7138,51 @@
         <v>2</v>
       </c>
       <c r="AI40" s="4">
-        <f>ROUND(D$4*Stagionalità!$B$2,0)</f>
-        <v/>
-      </c>
-      <c r="AJ40" s="19">
+        <f>ROUND((D$3+(D$13-D$3)*11/12)*Stagionalità!$B$2,0)</f>
+        <v/>
+      </c>
+      <c r="AJ40" s="20">
         <f>AI40*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="AK40" s="19">
+      <c r="AK40" s="20">
         <f>AI40*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AL40" s="19">
+      <c r="AL40" s="20">
         <f>'Costi B2Brand'!$D$6</f>
         <v/>
       </c>
-      <c r="AM40" s="19">
+      <c r="AM40" s="20">
         <f>D$8</f>
         <v/>
       </c>
-      <c r="AN40" s="19">
+      <c r="AN40" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,AN39-(AK39-AL39-AM39)),0)</f>
         <v/>
       </c>
-      <c r="AO40" s="19">
+      <c r="AO40" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(AK40,AL40+AM40+AN40+0.5*MAX(0,(AK40-AL40-AM40)-AN40)),AI40*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AP40" s="20">
+      <c r="AP40" s="19">
         <f>AO40-AL40-AM40</f>
         <v/>
       </c>
-      <c r="AQ40" s="19">
+      <c r="AQ40" s="20">
         <f>AQ39+AP40</f>
         <v/>
       </c>
-      <c r="AR40" s="20">
+      <c r="AR40" s="19">
         <f>AK40-AO40</f>
         <v/>
       </c>
-      <c r="AS40" s="19">
+      <c r="AS40" s="20">
         <f>AS39+AR40</f>
         <v/>
       </c>
       <c r="AT40" s="21">
-        <f>IF(AP40&gt;=Ipotesi!$B$14,AG40,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(AK40-AL40-AM40)/2,AP40)&gt;=Ipotesi!$B$14,AG40,"")</f>
         <v/>
       </c>
       <c r="AU40" s="21">
@@ -7050,51 +7198,51 @@
         <v>2</v>
       </c>
       <c r="C41" s="4">
-        <f>ROUND(B$4*Stagionalità!$B$3,0)</f>
-        <v/>
-      </c>
-      <c r="D41" s="19">
+        <f>ROUND((B$3+(B$13-B$3)*12/12)*Stagionalità!$B$3,0)</f>
+        <v/>
+      </c>
+      <c r="D41" s="20">
         <f>C41*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="E41" s="19">
+      <c r="E41" s="20">
         <f>C41*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="F41" s="19">
+      <c r="F41" s="20">
         <f>'Costi B2Brand'!$D$6</f>
         <v/>
       </c>
-      <c r="G41" s="19">
+      <c r="G41" s="20">
         <f>B$8</f>
         <v/>
       </c>
-      <c r="H41" s="19">
+      <c r="H41" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,H40-(E40-F40-G40)),0)</f>
         <v/>
       </c>
-      <c r="I41" s="19">
+      <c r="I41" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(E41,F41+G41+H41+0.5*MAX(0,(E41-F41-G41)-H41)),C41*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="J41" s="20">
+      <c r="J41" s="19">
         <f>I41-F41-G41</f>
         <v/>
       </c>
-      <c r="K41" s="19">
+      <c r="K41" s="20">
         <f>K40+J41</f>
         <v/>
       </c>
-      <c r="L41" s="20">
+      <c r="L41" s="19">
         <f>E41-I41</f>
         <v/>
       </c>
-      <c r="M41" s="19">
+      <c r="M41" s="20">
         <f>M40+L41</f>
         <v/>
       </c>
       <c r="N41" s="21">
-        <f>IF(J41&gt;=Ipotesi!$B$14,A41,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(E41-F41-G41)/2,J41)&gt;=Ipotesi!$B$14,A41,"")</f>
         <v/>
       </c>
       <c r="O41" s="21">
@@ -7108,51 +7256,51 @@
         <v>2</v>
       </c>
       <c r="S41" s="4">
-        <f>ROUND(C$4*Stagionalità!$B$3,0)</f>
-        <v/>
-      </c>
-      <c r="T41" s="19">
+        <f>ROUND((C$3+(C$13-C$3)*12/12)*Stagionalità!$B$3,0)</f>
+        <v/>
+      </c>
+      <c r="T41" s="20">
         <f>S41*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="U41" s="19">
+      <c r="U41" s="20">
         <f>S41*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="V41" s="19">
+      <c r="V41" s="20">
         <f>'Costi B2Brand'!$D$6</f>
         <v/>
       </c>
-      <c r="W41" s="19">
+      <c r="W41" s="20">
         <f>C$8</f>
         <v/>
       </c>
-      <c r="X41" s="19">
+      <c r="X41" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,X40-(U40-V40-W40)),0)</f>
         <v/>
       </c>
-      <c r="Y41" s="19">
+      <c r="Y41" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(U41,V41+W41+X41+0.5*MAX(0,(U41-V41-W41)-X41)),S41*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="Z41" s="20">
+      <c r="Z41" s="19">
         <f>Y41-V41-W41</f>
         <v/>
       </c>
-      <c r="AA41" s="19">
+      <c r="AA41" s="20">
         <f>AA40+Z41</f>
         <v/>
       </c>
-      <c r="AB41" s="20">
+      <c r="AB41" s="19">
         <f>U41-Y41</f>
         <v/>
       </c>
-      <c r="AC41" s="19">
+      <c r="AC41" s="20">
         <f>AC40+AB41</f>
         <v/>
       </c>
       <c r="AD41" s="21">
-        <f>IF(Z41&gt;=Ipotesi!$B$14,Q41,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(U41-V41-W41)/2,Z41)&gt;=Ipotesi!$B$14,Q41,"")</f>
         <v/>
       </c>
       <c r="AE41" s="21">
@@ -7166,51 +7314,51 @@
         <v>2</v>
       </c>
       <c r="AI41" s="4">
-        <f>ROUND(D$4*Stagionalità!$B$3,0)</f>
-        <v/>
-      </c>
-      <c r="AJ41" s="19">
+        <f>ROUND((D$3+(D$13-D$3)*12/12)*Stagionalità!$B$3,0)</f>
+        <v/>
+      </c>
+      <c r="AJ41" s="20">
         <f>AI41*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="AK41" s="19">
+      <c r="AK41" s="20">
         <f>AI41*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AL41" s="19">
+      <c r="AL41" s="20">
         <f>'Costi B2Brand'!$D$6</f>
         <v/>
       </c>
-      <c r="AM41" s="19">
+      <c r="AM41" s="20">
         <f>D$8</f>
         <v/>
       </c>
-      <c r="AN41" s="19">
+      <c r="AN41" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,AN40-(AK40-AL40-AM40)),0)</f>
         <v/>
       </c>
-      <c r="AO41" s="19">
+      <c r="AO41" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(AK41,AL41+AM41+AN41+0.5*MAX(0,(AK41-AL41-AM41)-AN41)),AI41*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AP41" s="20">
+      <c r="AP41" s="19">
         <f>AO41-AL41-AM41</f>
         <v/>
       </c>
-      <c r="AQ41" s="19">
+      <c r="AQ41" s="20">
         <f>AQ40+AP41</f>
         <v/>
       </c>
-      <c r="AR41" s="20">
+      <c r="AR41" s="19">
         <f>AK41-AO41</f>
         <v/>
       </c>
-      <c r="AS41" s="19">
+      <c r="AS41" s="20">
         <f>AS40+AR41</f>
         <v/>
       </c>
       <c r="AT41" s="21">
-        <f>IF(AP41&gt;=Ipotesi!$B$14,AG41,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(AK41-AL41-AM41)/2,AP41)&gt;=Ipotesi!$B$14,AG41,"")</f>
         <v/>
       </c>
       <c r="AU41" s="21">
@@ -7226,51 +7374,51 @@
         <v>3</v>
       </c>
       <c r="C42" s="4">
-        <f>ROUND(B$5*Stagionalità!$B$4,0)</f>
-        <v/>
-      </c>
-      <c r="D42" s="19">
+        <f>ROUND((B$13+(B$14-B$13)*1/12)*Stagionalità!$B$4,0)</f>
+        <v/>
+      </c>
+      <c r="D42" s="20">
         <f>C42*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="E42" s="19">
+      <c r="E42" s="20">
         <f>C42*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="F42" s="19">
+      <c r="F42" s="20">
         <f>'Costi B2Brand'!$E$6</f>
         <v/>
       </c>
-      <c r="G42" s="19">
+      <c r="G42" s="20">
         <f>B$9</f>
         <v/>
       </c>
-      <c r="H42" s="19">
+      <c r="H42" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,H41-(E41-F41-G41)),0)</f>
         <v/>
       </c>
-      <c r="I42" s="19">
+      <c r="I42" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(E42,F42+G42+H42+0.5*MAX(0,(E42-F42-G42)-H42)),C42*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="J42" s="20">
+      <c r="J42" s="19">
         <f>I42-F42-G42</f>
         <v/>
       </c>
-      <c r="K42" s="19">
+      <c r="K42" s="20">
         <f>K41+J42</f>
         <v/>
       </c>
-      <c r="L42" s="20">
+      <c r="L42" s="19">
         <f>E42-I42</f>
         <v/>
       </c>
-      <c r="M42" s="19">
+      <c r="M42" s="20">
         <f>M41+L42</f>
         <v/>
       </c>
       <c r="N42" s="21">
-        <f>IF(J42&gt;=Ipotesi!$B$14,A42,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(E42-F42-G42)/2,J42)&gt;=Ipotesi!$B$14,A42,"")</f>
         <v/>
       </c>
       <c r="O42" s="21">
@@ -7284,51 +7432,51 @@
         <v>3</v>
       </c>
       <c r="S42" s="4">
-        <f>ROUND(C$5*Stagionalità!$B$4,0)</f>
-        <v/>
-      </c>
-      <c r="T42" s="19">
+        <f>ROUND((C$13+(C$14-C$13)*1/12)*Stagionalità!$B$4,0)</f>
+        <v/>
+      </c>
+      <c r="T42" s="20">
         <f>S42*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="U42" s="19">
+      <c r="U42" s="20">
         <f>S42*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="V42" s="19">
+      <c r="V42" s="20">
         <f>'Costi B2Brand'!$E$6</f>
         <v/>
       </c>
-      <c r="W42" s="19">
+      <c r="W42" s="20">
         <f>C$9</f>
         <v/>
       </c>
-      <c r="X42" s="19">
+      <c r="X42" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,X41-(U41-V41-W41)),0)</f>
         <v/>
       </c>
-      <c r="Y42" s="19">
+      <c r="Y42" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(U42,V42+W42+X42+0.5*MAX(0,(U42-V42-W42)-X42)),S42*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="Z42" s="20">
+      <c r="Z42" s="19">
         <f>Y42-V42-W42</f>
         <v/>
       </c>
-      <c r="AA42" s="19">
+      <c r="AA42" s="20">
         <f>AA41+Z42</f>
         <v/>
       </c>
-      <c r="AB42" s="20">
+      <c r="AB42" s="19">
         <f>U42-Y42</f>
         <v/>
       </c>
-      <c r="AC42" s="19">
+      <c r="AC42" s="20">
         <f>AC41+AB42</f>
         <v/>
       </c>
       <c r="AD42" s="21">
-        <f>IF(Z42&gt;=Ipotesi!$B$14,Q42,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(U42-V42-W42)/2,Z42)&gt;=Ipotesi!$B$14,Q42,"")</f>
         <v/>
       </c>
       <c r="AE42" s="21">
@@ -7342,51 +7490,51 @@
         <v>3</v>
       </c>
       <c r="AI42" s="4">
-        <f>ROUND(D$5*Stagionalità!$B$4,0)</f>
-        <v/>
-      </c>
-      <c r="AJ42" s="19">
+        <f>ROUND((D$13+(D$14-D$13)*1/12)*Stagionalità!$B$4,0)</f>
+        <v/>
+      </c>
+      <c r="AJ42" s="20">
         <f>AI42*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="AK42" s="19">
+      <c r="AK42" s="20">
         <f>AI42*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AL42" s="19">
+      <c r="AL42" s="20">
         <f>'Costi B2Brand'!$E$6</f>
         <v/>
       </c>
-      <c r="AM42" s="19">
+      <c r="AM42" s="20">
         <f>D$9</f>
         <v/>
       </c>
-      <c r="AN42" s="19">
+      <c r="AN42" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,AN41-(AK41-AL41-AM41)),0)</f>
         <v/>
       </c>
-      <c r="AO42" s="19">
+      <c r="AO42" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(AK42,AL42+AM42+AN42+0.5*MAX(0,(AK42-AL42-AM42)-AN42)),AI42*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AP42" s="20">
+      <c r="AP42" s="19">
         <f>AO42-AL42-AM42</f>
         <v/>
       </c>
-      <c r="AQ42" s="19">
+      <c r="AQ42" s="20">
         <f>AQ41+AP42</f>
         <v/>
       </c>
-      <c r="AR42" s="20">
+      <c r="AR42" s="19">
         <f>AK42-AO42</f>
         <v/>
       </c>
-      <c r="AS42" s="19">
+      <c r="AS42" s="20">
         <f>AS41+AR42</f>
         <v/>
       </c>
       <c r="AT42" s="21">
-        <f>IF(AP42&gt;=Ipotesi!$B$14,AG42,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(AK42-AL42-AM42)/2,AP42)&gt;=Ipotesi!$B$14,AG42,"")</f>
         <v/>
       </c>
       <c r="AU42" s="21">
@@ -7402,51 +7550,51 @@
         <v>3</v>
       </c>
       <c r="C43" s="4">
-        <f>ROUND(B$5*Stagionalità!$B$5,0)</f>
-        <v/>
-      </c>
-      <c r="D43" s="19">
+        <f>ROUND((B$13+(B$14-B$13)*2/12)*Stagionalità!$B$5,0)</f>
+        <v/>
+      </c>
+      <c r="D43" s="20">
         <f>C43*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="E43" s="19">
+      <c r="E43" s="20">
         <f>C43*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="F43" s="19">
+      <c r="F43" s="20">
         <f>'Costi B2Brand'!$E$6</f>
         <v/>
       </c>
-      <c r="G43" s="19">
+      <c r="G43" s="20">
         <f>B$9</f>
         <v/>
       </c>
-      <c r="H43" s="19">
+      <c r="H43" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,H42-(E42-F42-G42)),0)</f>
         <v/>
       </c>
-      <c r="I43" s="19">
+      <c r="I43" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(E43,F43+G43+H43+0.5*MAX(0,(E43-F43-G43)-H43)),C43*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="J43" s="20">
+      <c r="J43" s="19">
         <f>I43-F43-G43</f>
         <v/>
       </c>
-      <c r="K43" s="19">
+      <c r="K43" s="20">
         <f>K42+J43</f>
         <v/>
       </c>
-      <c r="L43" s="20">
+      <c r="L43" s="19">
         <f>E43-I43</f>
         <v/>
       </c>
-      <c r="M43" s="19">
+      <c r="M43" s="20">
         <f>M42+L43</f>
         <v/>
       </c>
       <c r="N43" s="21">
-        <f>IF(J43&gt;=Ipotesi!$B$14,A43,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(E43-F43-G43)/2,J43)&gt;=Ipotesi!$B$14,A43,"")</f>
         <v/>
       </c>
       <c r="O43" s="21">
@@ -7460,51 +7608,51 @@
         <v>3</v>
       </c>
       <c r="S43" s="4">
-        <f>ROUND(C$5*Stagionalità!$B$5,0)</f>
-        <v/>
-      </c>
-      <c r="T43" s="19">
+        <f>ROUND((C$13+(C$14-C$13)*2/12)*Stagionalità!$B$5,0)</f>
+        <v/>
+      </c>
+      <c r="T43" s="20">
         <f>S43*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="U43" s="19">
+      <c r="U43" s="20">
         <f>S43*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="V43" s="19">
+      <c r="V43" s="20">
         <f>'Costi B2Brand'!$E$6</f>
         <v/>
       </c>
-      <c r="W43" s="19">
+      <c r="W43" s="20">
         <f>C$9</f>
         <v/>
       </c>
-      <c r="X43" s="19">
+      <c r="X43" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,X42-(U42-V42-W42)),0)</f>
         <v/>
       </c>
-      <c r="Y43" s="19">
+      <c r="Y43" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(U43,V43+W43+X43+0.5*MAX(0,(U43-V43-W43)-X43)),S43*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="Z43" s="20">
+      <c r="Z43" s="19">
         <f>Y43-V43-W43</f>
         <v/>
       </c>
-      <c r="AA43" s="19">
+      <c r="AA43" s="20">
         <f>AA42+Z43</f>
         <v/>
       </c>
-      <c r="AB43" s="20">
+      <c r="AB43" s="19">
         <f>U43-Y43</f>
         <v/>
       </c>
-      <c r="AC43" s="19">
+      <c r="AC43" s="20">
         <f>AC42+AB43</f>
         <v/>
       </c>
       <c r="AD43" s="21">
-        <f>IF(Z43&gt;=Ipotesi!$B$14,Q43,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(U43-V43-W43)/2,Z43)&gt;=Ipotesi!$B$14,Q43,"")</f>
         <v/>
       </c>
       <c r="AE43" s="21">
@@ -7518,51 +7666,51 @@
         <v>3</v>
       </c>
       <c r="AI43" s="4">
-        <f>ROUND(D$5*Stagionalità!$B$5,0)</f>
-        <v/>
-      </c>
-      <c r="AJ43" s="19">
+        <f>ROUND((D$13+(D$14-D$13)*2/12)*Stagionalità!$B$5,0)</f>
+        <v/>
+      </c>
+      <c r="AJ43" s="20">
         <f>AI43*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="AK43" s="19">
+      <c r="AK43" s="20">
         <f>AI43*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AL43" s="19">
+      <c r="AL43" s="20">
         <f>'Costi B2Brand'!$E$6</f>
         <v/>
       </c>
-      <c r="AM43" s="19">
+      <c r="AM43" s="20">
         <f>D$9</f>
         <v/>
       </c>
-      <c r="AN43" s="19">
+      <c r="AN43" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,AN42-(AK42-AL42-AM42)),0)</f>
         <v/>
       </c>
-      <c r="AO43" s="19">
+      <c r="AO43" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(AK43,AL43+AM43+AN43+0.5*MAX(0,(AK43-AL43-AM43)-AN43)),AI43*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AP43" s="20">
+      <c r="AP43" s="19">
         <f>AO43-AL43-AM43</f>
         <v/>
       </c>
-      <c r="AQ43" s="19">
+      <c r="AQ43" s="20">
         <f>AQ42+AP43</f>
         <v/>
       </c>
-      <c r="AR43" s="20">
+      <c r="AR43" s="19">
         <f>AK43-AO43</f>
         <v/>
       </c>
-      <c r="AS43" s="19">
+      <c r="AS43" s="20">
         <f>AS42+AR43</f>
         <v/>
       </c>
       <c r="AT43" s="21">
-        <f>IF(AP43&gt;=Ipotesi!$B$14,AG43,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(AK43-AL43-AM43)/2,AP43)&gt;=Ipotesi!$B$14,AG43,"")</f>
         <v/>
       </c>
       <c r="AU43" s="21">
@@ -7578,51 +7726,51 @@
         <v>3</v>
       </c>
       <c r="C44" s="4">
-        <f>ROUND(B$5*Stagionalità!$B$6,0)</f>
-        <v/>
-      </c>
-      <c r="D44" s="19">
+        <f>ROUND((B$13+(B$14-B$13)*3/12)*Stagionalità!$B$6,0)</f>
+        <v/>
+      </c>
+      <c r="D44" s="20">
         <f>C44*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="E44" s="19">
+      <c r="E44" s="20">
         <f>C44*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="F44" s="19">
+      <c r="F44" s="20">
         <f>'Costi B2Brand'!$E$6</f>
         <v/>
       </c>
-      <c r="G44" s="19">
+      <c r="G44" s="20">
         <f>B$9</f>
         <v/>
       </c>
-      <c r="H44" s="19">
+      <c r="H44" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,H43-(E43-F43-G43)),0)</f>
         <v/>
       </c>
-      <c r="I44" s="19">
+      <c r="I44" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(E44,F44+G44+H44+0.5*MAX(0,(E44-F44-G44)-H44)),C44*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="J44" s="20">
+      <c r="J44" s="19">
         <f>I44-F44-G44</f>
         <v/>
       </c>
-      <c r="K44" s="19">
+      <c r="K44" s="20">
         <f>K43+J44</f>
         <v/>
       </c>
-      <c r="L44" s="20">
+      <c r="L44" s="19">
         <f>E44-I44</f>
         <v/>
       </c>
-      <c r="M44" s="19">
+      <c r="M44" s="20">
         <f>M43+L44</f>
         <v/>
       </c>
       <c r="N44" s="21">
-        <f>IF(J44&gt;=Ipotesi!$B$14,A44,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(E44-F44-G44)/2,J44)&gt;=Ipotesi!$B$14,A44,"")</f>
         <v/>
       </c>
       <c r="O44" s="21">
@@ -7636,51 +7784,51 @@
         <v>3</v>
       </c>
       <c r="S44" s="4">
-        <f>ROUND(C$5*Stagionalità!$B$6,0)</f>
-        <v/>
-      </c>
-      <c r="T44" s="19">
+        <f>ROUND((C$13+(C$14-C$13)*3/12)*Stagionalità!$B$6,0)</f>
+        <v/>
+      </c>
+      <c r="T44" s="20">
         <f>S44*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="U44" s="19">
+      <c r="U44" s="20">
         <f>S44*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="V44" s="19">
+      <c r="V44" s="20">
         <f>'Costi B2Brand'!$E$6</f>
         <v/>
       </c>
-      <c r="W44" s="19">
+      <c r="W44" s="20">
         <f>C$9</f>
         <v/>
       </c>
-      <c r="X44" s="19">
+      <c r="X44" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,X43-(U43-V43-W43)),0)</f>
         <v/>
       </c>
-      <c r="Y44" s="19">
+      <c r="Y44" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(U44,V44+W44+X44+0.5*MAX(0,(U44-V44-W44)-X44)),S44*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="Z44" s="20">
+      <c r="Z44" s="19">
         <f>Y44-V44-W44</f>
         <v/>
       </c>
-      <c r="AA44" s="19">
+      <c r="AA44" s="20">
         <f>AA43+Z44</f>
         <v/>
       </c>
-      <c r="AB44" s="20">
+      <c r="AB44" s="19">
         <f>U44-Y44</f>
         <v/>
       </c>
-      <c r="AC44" s="19">
+      <c r="AC44" s="20">
         <f>AC43+AB44</f>
         <v/>
       </c>
       <c r="AD44" s="21">
-        <f>IF(Z44&gt;=Ipotesi!$B$14,Q44,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(U44-V44-W44)/2,Z44)&gt;=Ipotesi!$B$14,Q44,"")</f>
         <v/>
       </c>
       <c r="AE44" s="21">
@@ -7694,51 +7842,51 @@
         <v>3</v>
       </c>
       <c r="AI44" s="4">
-        <f>ROUND(D$5*Stagionalità!$B$6,0)</f>
-        <v/>
-      </c>
-      <c r="AJ44" s="19">
+        <f>ROUND((D$13+(D$14-D$13)*3/12)*Stagionalità!$B$6,0)</f>
+        <v/>
+      </c>
+      <c r="AJ44" s="20">
         <f>AI44*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="AK44" s="19">
+      <c r="AK44" s="20">
         <f>AI44*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AL44" s="19">
+      <c r="AL44" s="20">
         <f>'Costi B2Brand'!$E$6</f>
         <v/>
       </c>
-      <c r="AM44" s="19">
+      <c r="AM44" s="20">
         <f>D$9</f>
         <v/>
       </c>
-      <c r="AN44" s="19">
+      <c r="AN44" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,AN43-(AK43-AL43-AM43)),0)</f>
         <v/>
       </c>
-      <c r="AO44" s="19">
+      <c r="AO44" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(AK44,AL44+AM44+AN44+0.5*MAX(0,(AK44-AL44-AM44)-AN44)),AI44*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AP44" s="20">
+      <c r="AP44" s="19">
         <f>AO44-AL44-AM44</f>
         <v/>
       </c>
-      <c r="AQ44" s="19">
+      <c r="AQ44" s="20">
         <f>AQ43+AP44</f>
         <v/>
       </c>
-      <c r="AR44" s="20">
+      <c r="AR44" s="19">
         <f>AK44-AO44</f>
         <v/>
       </c>
-      <c r="AS44" s="19">
+      <c r="AS44" s="20">
         <f>AS43+AR44</f>
         <v/>
       </c>
       <c r="AT44" s="21">
-        <f>IF(AP44&gt;=Ipotesi!$B$14,AG44,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(AK44-AL44-AM44)/2,AP44)&gt;=Ipotesi!$B$14,AG44,"")</f>
         <v/>
       </c>
       <c r="AU44" s="21">
@@ -7754,51 +7902,51 @@
         <v>3</v>
       </c>
       <c r="C45" s="4">
-        <f>ROUND(B$5*Stagionalità!$B$7,0)</f>
-        <v/>
-      </c>
-      <c r="D45" s="19">
+        <f>ROUND((B$13+(B$14-B$13)*4/12)*Stagionalità!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="D45" s="20">
         <f>C45*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="E45" s="19">
+      <c r="E45" s="20">
         <f>C45*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="F45" s="19">
+      <c r="F45" s="20">
         <f>'Costi B2Brand'!$E$6</f>
         <v/>
       </c>
-      <c r="G45" s="19">
+      <c r="G45" s="20">
         <f>B$9</f>
         <v/>
       </c>
-      <c r="H45" s="19">
+      <c r="H45" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,H44-(E44-F44-G44)),0)</f>
         <v/>
       </c>
-      <c r="I45" s="19">
+      <c r="I45" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(E45,F45+G45+H45+0.5*MAX(0,(E45-F45-G45)-H45)),C45*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="J45" s="20">
+      <c r="J45" s="19">
         <f>I45-F45-G45</f>
         <v/>
       </c>
-      <c r="K45" s="19">
+      <c r="K45" s="20">
         <f>K44+J45</f>
         <v/>
       </c>
-      <c r="L45" s="20">
+      <c r="L45" s="19">
         <f>E45-I45</f>
         <v/>
       </c>
-      <c r="M45" s="19">
+      <c r="M45" s="20">
         <f>M44+L45</f>
         <v/>
       </c>
       <c r="N45" s="21">
-        <f>IF(J45&gt;=Ipotesi!$B$14,A45,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(E45-F45-G45)/2,J45)&gt;=Ipotesi!$B$14,A45,"")</f>
         <v/>
       </c>
       <c r="O45" s="21">
@@ -7812,51 +7960,51 @@
         <v>3</v>
       </c>
       <c r="S45" s="4">
-        <f>ROUND(C$5*Stagionalità!$B$7,0)</f>
-        <v/>
-      </c>
-      <c r="T45" s="19">
+        <f>ROUND((C$13+(C$14-C$13)*4/12)*Stagionalità!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="T45" s="20">
         <f>S45*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="U45" s="19">
+      <c r="U45" s="20">
         <f>S45*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="V45" s="19">
+      <c r="V45" s="20">
         <f>'Costi B2Brand'!$E$6</f>
         <v/>
       </c>
-      <c r="W45" s="19">
+      <c r="W45" s="20">
         <f>C$9</f>
         <v/>
       </c>
-      <c r="X45" s="19">
+      <c r="X45" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,X44-(U44-V44-W44)),0)</f>
         <v/>
       </c>
-      <c r="Y45" s="19">
+      <c r="Y45" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(U45,V45+W45+X45+0.5*MAX(0,(U45-V45-W45)-X45)),S45*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="Z45" s="20">
+      <c r="Z45" s="19">
         <f>Y45-V45-W45</f>
         <v/>
       </c>
-      <c r="AA45" s="19">
+      <c r="AA45" s="20">
         <f>AA44+Z45</f>
         <v/>
       </c>
-      <c r="AB45" s="20">
+      <c r="AB45" s="19">
         <f>U45-Y45</f>
         <v/>
       </c>
-      <c r="AC45" s="19">
+      <c r="AC45" s="20">
         <f>AC44+AB45</f>
         <v/>
       </c>
       <c r="AD45" s="21">
-        <f>IF(Z45&gt;=Ipotesi!$B$14,Q45,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(U45-V45-W45)/2,Z45)&gt;=Ipotesi!$B$14,Q45,"")</f>
         <v/>
       </c>
       <c r="AE45" s="21">
@@ -7870,51 +8018,51 @@
         <v>3</v>
       </c>
       <c r="AI45" s="4">
-        <f>ROUND(D$5*Stagionalità!$B$7,0)</f>
-        <v/>
-      </c>
-      <c r="AJ45" s="19">
+        <f>ROUND((D$13+(D$14-D$13)*4/12)*Stagionalità!$B$7,0)</f>
+        <v/>
+      </c>
+      <c r="AJ45" s="20">
         <f>AI45*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="AK45" s="19">
+      <c r="AK45" s="20">
         <f>AI45*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AL45" s="19">
+      <c r="AL45" s="20">
         <f>'Costi B2Brand'!$E$6</f>
         <v/>
       </c>
-      <c r="AM45" s="19">
+      <c r="AM45" s="20">
         <f>D$9</f>
         <v/>
       </c>
-      <c r="AN45" s="19">
+      <c r="AN45" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,AN44-(AK44-AL44-AM44)),0)</f>
         <v/>
       </c>
-      <c r="AO45" s="19">
+      <c r="AO45" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(AK45,AL45+AM45+AN45+0.5*MAX(0,(AK45-AL45-AM45)-AN45)),AI45*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AP45" s="20">
+      <c r="AP45" s="19">
         <f>AO45-AL45-AM45</f>
         <v/>
       </c>
-      <c r="AQ45" s="19">
+      <c r="AQ45" s="20">
         <f>AQ44+AP45</f>
         <v/>
       </c>
-      <c r="AR45" s="20">
+      <c r="AR45" s="19">
         <f>AK45-AO45</f>
         <v/>
       </c>
-      <c r="AS45" s="19">
+      <c r="AS45" s="20">
         <f>AS44+AR45</f>
         <v/>
       </c>
       <c r="AT45" s="21">
-        <f>IF(AP45&gt;=Ipotesi!$B$14,AG45,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(AK45-AL45-AM45)/2,AP45)&gt;=Ipotesi!$B$14,AG45,"")</f>
         <v/>
       </c>
       <c r="AU45" s="21">
@@ -7930,51 +8078,51 @@
         <v>3</v>
       </c>
       <c r="C46" s="4">
-        <f>ROUND(B$5*Stagionalità!$B$8,0)</f>
-        <v/>
-      </c>
-      <c r="D46" s="19">
+        <f>ROUND((B$13+(B$14-B$13)*5/12)*Stagionalità!$B$8,0)</f>
+        <v/>
+      </c>
+      <c r="D46" s="20">
         <f>C46*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="E46" s="19">
+      <c r="E46" s="20">
         <f>C46*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="F46" s="19">
+      <c r="F46" s="20">
         <f>'Costi B2Brand'!$E$6</f>
         <v/>
       </c>
-      <c r="G46" s="19">
+      <c r="G46" s="20">
         <f>B$9</f>
         <v/>
       </c>
-      <c r="H46" s="19">
+      <c r="H46" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,H45-(E45-F45-G45)),0)</f>
         <v/>
       </c>
-      <c r="I46" s="19">
+      <c r="I46" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(E46,F46+G46+H46+0.5*MAX(0,(E46-F46-G46)-H46)),C46*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="J46" s="20">
+      <c r="J46" s="19">
         <f>I46-F46-G46</f>
         <v/>
       </c>
-      <c r="K46" s="19">
+      <c r="K46" s="20">
         <f>K45+J46</f>
         <v/>
       </c>
-      <c r="L46" s="20">
+      <c r="L46" s="19">
         <f>E46-I46</f>
         <v/>
       </c>
-      <c r="M46" s="19">
+      <c r="M46" s="20">
         <f>M45+L46</f>
         <v/>
       </c>
       <c r="N46" s="21">
-        <f>IF(J46&gt;=Ipotesi!$B$14,A46,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(E46-F46-G46)/2,J46)&gt;=Ipotesi!$B$14,A46,"")</f>
         <v/>
       </c>
       <c r="O46" s="21">
@@ -7988,51 +8136,51 @@
         <v>3</v>
       </c>
       <c r="S46" s="4">
-        <f>ROUND(C$5*Stagionalità!$B$8,0)</f>
-        <v/>
-      </c>
-      <c r="T46" s="19">
+        <f>ROUND((C$13+(C$14-C$13)*5/12)*Stagionalità!$B$8,0)</f>
+        <v/>
+      </c>
+      <c r="T46" s="20">
         <f>S46*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="U46" s="19">
+      <c r="U46" s="20">
         <f>S46*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="V46" s="19">
+      <c r="V46" s="20">
         <f>'Costi B2Brand'!$E$6</f>
         <v/>
       </c>
-      <c r="W46" s="19">
+      <c r="W46" s="20">
         <f>C$9</f>
         <v/>
       </c>
-      <c r="X46" s="19">
+      <c r="X46" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,X45-(U45-V45-W45)),0)</f>
         <v/>
       </c>
-      <c r="Y46" s="19">
+      <c r="Y46" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(U46,V46+W46+X46+0.5*MAX(0,(U46-V46-W46)-X46)),S46*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="Z46" s="20">
+      <c r="Z46" s="19">
         <f>Y46-V46-W46</f>
         <v/>
       </c>
-      <c r="AA46" s="19">
+      <c r="AA46" s="20">
         <f>AA45+Z46</f>
         <v/>
       </c>
-      <c r="AB46" s="20">
+      <c r="AB46" s="19">
         <f>U46-Y46</f>
         <v/>
       </c>
-      <c r="AC46" s="19">
+      <c r="AC46" s="20">
         <f>AC45+AB46</f>
         <v/>
       </c>
       <c r="AD46" s="21">
-        <f>IF(Z46&gt;=Ipotesi!$B$14,Q46,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(U46-V46-W46)/2,Z46)&gt;=Ipotesi!$B$14,Q46,"")</f>
         <v/>
       </c>
       <c r="AE46" s="21">
@@ -8046,51 +8194,51 @@
         <v>3</v>
       </c>
       <c r="AI46" s="4">
-        <f>ROUND(D$5*Stagionalità!$B$8,0)</f>
-        <v/>
-      </c>
-      <c r="AJ46" s="19">
+        <f>ROUND((D$13+(D$14-D$13)*5/12)*Stagionalità!$B$8,0)</f>
+        <v/>
+      </c>
+      <c r="AJ46" s="20">
         <f>AI46*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="AK46" s="19">
+      <c r="AK46" s="20">
         <f>AI46*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AL46" s="19">
+      <c r="AL46" s="20">
         <f>'Costi B2Brand'!$E$6</f>
         <v/>
       </c>
-      <c r="AM46" s="19">
+      <c r="AM46" s="20">
         <f>D$9</f>
         <v/>
       </c>
-      <c r="AN46" s="19">
+      <c r="AN46" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,AN45-(AK45-AL45-AM45)),0)</f>
         <v/>
       </c>
-      <c r="AO46" s="19">
+      <c r="AO46" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(AK46,AL46+AM46+AN46+0.5*MAX(0,(AK46-AL46-AM46)-AN46)),AI46*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AP46" s="20">
+      <c r="AP46" s="19">
         <f>AO46-AL46-AM46</f>
         <v/>
       </c>
-      <c r="AQ46" s="19">
+      <c r="AQ46" s="20">
         <f>AQ45+AP46</f>
         <v/>
       </c>
-      <c r="AR46" s="20">
+      <c r="AR46" s="19">
         <f>AK46-AO46</f>
         <v/>
       </c>
-      <c r="AS46" s="19">
+      <c r="AS46" s="20">
         <f>AS45+AR46</f>
         <v/>
       </c>
       <c r="AT46" s="21">
-        <f>IF(AP46&gt;=Ipotesi!$B$14,AG46,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(AK46-AL46-AM46)/2,AP46)&gt;=Ipotesi!$B$14,AG46,"")</f>
         <v/>
       </c>
       <c r="AU46" s="21">
@@ -8106,51 +8254,51 @@
         <v>3</v>
       </c>
       <c r="C47" s="4">
-        <f>ROUND(B$5*Stagionalità!$B$9,0)</f>
-        <v/>
-      </c>
-      <c r="D47" s="19">
+        <f>ROUND((B$13+(B$14-B$13)*6/12)*Stagionalità!$B$9,0)</f>
+        <v/>
+      </c>
+      <c r="D47" s="20">
         <f>C47*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="E47" s="19">
+      <c r="E47" s="20">
         <f>C47*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="F47" s="19">
+      <c r="F47" s="20">
         <f>'Costi B2Brand'!$E$6</f>
         <v/>
       </c>
-      <c r="G47" s="19">
+      <c r="G47" s="20">
         <f>B$9</f>
         <v/>
       </c>
-      <c r="H47" s="19">
+      <c r="H47" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,H46-(E46-F46-G46)),0)</f>
         <v/>
       </c>
-      <c r="I47" s="19">
+      <c r="I47" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(E47,F47+G47+H47+0.5*MAX(0,(E47-F47-G47)-H47)),C47*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="J47" s="20">
+      <c r="J47" s="19">
         <f>I47-F47-G47</f>
         <v/>
       </c>
-      <c r="K47" s="19">
+      <c r="K47" s="20">
         <f>K46+J47</f>
         <v/>
       </c>
-      <c r="L47" s="20">
+      <c r="L47" s="19">
         <f>E47-I47</f>
         <v/>
       </c>
-      <c r="M47" s="19">
+      <c r="M47" s="20">
         <f>M46+L47</f>
         <v/>
       </c>
       <c r="N47" s="21">
-        <f>IF(J47&gt;=Ipotesi!$B$14,A47,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(E47-F47-G47)/2,J47)&gt;=Ipotesi!$B$14,A47,"")</f>
         <v/>
       </c>
       <c r="O47" s="21">
@@ -8164,51 +8312,51 @@
         <v>3</v>
       </c>
       <c r="S47" s="4">
-        <f>ROUND(C$5*Stagionalità!$B$9,0)</f>
-        <v/>
-      </c>
-      <c r="T47" s="19">
+        <f>ROUND((C$13+(C$14-C$13)*6/12)*Stagionalità!$B$9,0)</f>
+        <v/>
+      </c>
+      <c r="T47" s="20">
         <f>S47*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="U47" s="19">
+      <c r="U47" s="20">
         <f>S47*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="V47" s="19">
+      <c r="V47" s="20">
         <f>'Costi B2Brand'!$E$6</f>
         <v/>
       </c>
-      <c r="W47" s="19">
+      <c r="W47" s="20">
         <f>C$9</f>
         <v/>
       </c>
-      <c r="X47" s="19">
+      <c r="X47" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,X46-(U46-V46-W46)),0)</f>
         <v/>
       </c>
-      <c r="Y47" s="19">
+      <c r="Y47" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(U47,V47+W47+X47+0.5*MAX(0,(U47-V47-W47)-X47)),S47*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="Z47" s="20">
+      <c r="Z47" s="19">
         <f>Y47-V47-W47</f>
         <v/>
       </c>
-      <c r="AA47" s="19">
+      <c r="AA47" s="20">
         <f>AA46+Z47</f>
         <v/>
       </c>
-      <c r="AB47" s="20">
+      <c r="AB47" s="19">
         <f>U47-Y47</f>
         <v/>
       </c>
-      <c r="AC47" s="19">
+      <c r="AC47" s="20">
         <f>AC46+AB47</f>
         <v/>
       </c>
       <c r="AD47" s="21">
-        <f>IF(Z47&gt;=Ipotesi!$B$14,Q47,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(U47-V47-W47)/2,Z47)&gt;=Ipotesi!$B$14,Q47,"")</f>
         <v/>
       </c>
       <c r="AE47" s="21">
@@ -8222,51 +8370,51 @@
         <v>3</v>
       </c>
       <c r="AI47" s="4">
-        <f>ROUND(D$5*Stagionalità!$B$9,0)</f>
-        <v/>
-      </c>
-      <c r="AJ47" s="19">
+        <f>ROUND((D$13+(D$14-D$13)*6/12)*Stagionalità!$B$9,0)</f>
+        <v/>
+      </c>
+      <c r="AJ47" s="20">
         <f>AI47*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="AK47" s="19">
+      <c r="AK47" s="20">
         <f>AI47*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AL47" s="19">
+      <c r="AL47" s="20">
         <f>'Costi B2Brand'!$E$6</f>
         <v/>
       </c>
-      <c r="AM47" s="19">
+      <c r="AM47" s="20">
         <f>D$9</f>
         <v/>
       </c>
-      <c r="AN47" s="19">
+      <c r="AN47" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,AN46-(AK46-AL46-AM46)),0)</f>
         <v/>
       </c>
-      <c r="AO47" s="19">
+      <c r="AO47" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(AK47,AL47+AM47+AN47+0.5*MAX(0,(AK47-AL47-AM47)-AN47)),AI47*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AP47" s="20">
+      <c r="AP47" s="19">
         <f>AO47-AL47-AM47</f>
         <v/>
       </c>
-      <c r="AQ47" s="19">
+      <c r="AQ47" s="20">
         <f>AQ46+AP47</f>
         <v/>
       </c>
-      <c r="AR47" s="20">
+      <c r="AR47" s="19">
         <f>AK47-AO47</f>
         <v/>
       </c>
-      <c r="AS47" s="19">
+      <c r="AS47" s="20">
         <f>AS46+AR47</f>
         <v/>
       </c>
       <c r="AT47" s="21">
-        <f>IF(AP47&gt;=Ipotesi!$B$14,AG47,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(AK47-AL47-AM47)/2,AP47)&gt;=Ipotesi!$B$14,AG47,"")</f>
         <v/>
       </c>
       <c r="AU47" s="21">
@@ -8282,51 +8430,51 @@
         <v>3</v>
       </c>
       <c r="C48" s="4">
-        <f>ROUND(B$5*Stagionalità!$B$10,0)</f>
-        <v/>
-      </c>
-      <c r="D48" s="19">
+        <f>ROUND((B$13+(B$14-B$13)*7/12)*Stagionalità!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="D48" s="20">
         <f>C48*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="E48" s="19">
+      <c r="E48" s="20">
         <f>C48*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="F48" s="19">
+      <c r="F48" s="20">
         <f>'Costi B2Brand'!$E$6</f>
         <v/>
       </c>
-      <c r="G48" s="19">
+      <c r="G48" s="20">
         <f>B$9</f>
         <v/>
       </c>
-      <c r="H48" s="19">
+      <c r="H48" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,H47-(E47-F47-G47)),0)</f>
         <v/>
       </c>
-      <c r="I48" s="19">
+      <c r="I48" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(E48,F48+G48+H48+0.5*MAX(0,(E48-F48-G48)-H48)),C48*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="J48" s="20">
+      <c r="J48" s="19">
         <f>I48-F48-G48</f>
         <v/>
       </c>
-      <c r="K48" s="19">
+      <c r="K48" s="20">
         <f>K47+J48</f>
         <v/>
       </c>
-      <c r="L48" s="20">
+      <c r="L48" s="19">
         <f>E48-I48</f>
         <v/>
       </c>
-      <c r="M48" s="19">
+      <c r="M48" s="20">
         <f>M47+L48</f>
         <v/>
       </c>
       <c r="N48" s="21">
-        <f>IF(J48&gt;=Ipotesi!$B$14,A48,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(E48-F48-G48)/2,J48)&gt;=Ipotesi!$B$14,A48,"")</f>
         <v/>
       </c>
       <c r="O48" s="21">
@@ -8340,51 +8488,51 @@
         <v>3</v>
       </c>
       <c r="S48" s="4">
-        <f>ROUND(C$5*Stagionalità!$B$10,0)</f>
-        <v/>
-      </c>
-      <c r="T48" s="19">
+        <f>ROUND((C$13+(C$14-C$13)*7/12)*Stagionalità!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="T48" s="20">
         <f>S48*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="U48" s="19">
+      <c r="U48" s="20">
         <f>S48*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="V48" s="19">
+      <c r="V48" s="20">
         <f>'Costi B2Brand'!$E$6</f>
         <v/>
       </c>
-      <c r="W48" s="19">
+      <c r="W48" s="20">
         <f>C$9</f>
         <v/>
       </c>
-      <c r="X48" s="19">
+      <c r="X48" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,X47-(U47-V47-W47)),0)</f>
         <v/>
       </c>
-      <c r="Y48" s="19">
+      <c r="Y48" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(U48,V48+W48+X48+0.5*MAX(0,(U48-V48-W48)-X48)),S48*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="Z48" s="20">
+      <c r="Z48" s="19">
         <f>Y48-V48-W48</f>
         <v/>
       </c>
-      <c r="AA48" s="19">
+      <c r="AA48" s="20">
         <f>AA47+Z48</f>
         <v/>
       </c>
-      <c r="AB48" s="20">
+      <c r="AB48" s="19">
         <f>U48-Y48</f>
         <v/>
       </c>
-      <c r="AC48" s="19">
+      <c r="AC48" s="20">
         <f>AC47+AB48</f>
         <v/>
       </c>
       <c r="AD48" s="21">
-        <f>IF(Z48&gt;=Ipotesi!$B$14,Q48,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(U48-V48-W48)/2,Z48)&gt;=Ipotesi!$B$14,Q48,"")</f>
         <v/>
       </c>
       <c r="AE48" s="21">
@@ -8398,51 +8546,51 @@
         <v>3</v>
       </c>
       <c r="AI48" s="4">
-        <f>ROUND(D$5*Stagionalità!$B$10,0)</f>
-        <v/>
-      </c>
-      <c r="AJ48" s="19">
+        <f>ROUND((D$13+(D$14-D$13)*7/12)*Stagionalità!$B$10,0)</f>
+        <v/>
+      </c>
+      <c r="AJ48" s="20">
         <f>AI48*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="AK48" s="19">
+      <c r="AK48" s="20">
         <f>AI48*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AL48" s="19">
+      <c r="AL48" s="20">
         <f>'Costi B2Brand'!$E$6</f>
         <v/>
       </c>
-      <c r="AM48" s="19">
+      <c r="AM48" s="20">
         <f>D$9</f>
         <v/>
       </c>
-      <c r="AN48" s="19">
+      <c r="AN48" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,AN47-(AK47-AL47-AM47)),0)</f>
         <v/>
       </c>
-      <c r="AO48" s="19">
+      <c r="AO48" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(AK48,AL48+AM48+AN48+0.5*MAX(0,(AK48-AL48-AM48)-AN48)),AI48*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AP48" s="20">
+      <c r="AP48" s="19">
         <f>AO48-AL48-AM48</f>
         <v/>
       </c>
-      <c r="AQ48" s="19">
+      <c r="AQ48" s="20">
         <f>AQ47+AP48</f>
         <v/>
       </c>
-      <c r="AR48" s="20">
+      <c r="AR48" s="19">
         <f>AK48-AO48</f>
         <v/>
       </c>
-      <c r="AS48" s="19">
+      <c r="AS48" s="20">
         <f>AS47+AR48</f>
         <v/>
       </c>
       <c r="AT48" s="21">
-        <f>IF(AP48&gt;=Ipotesi!$B$14,AG48,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(AK48-AL48-AM48)/2,AP48)&gt;=Ipotesi!$B$14,AG48,"")</f>
         <v/>
       </c>
       <c r="AU48" s="21">
@@ -8458,51 +8606,51 @@
         <v>3</v>
       </c>
       <c r="C49" s="4">
-        <f>ROUND(B$5*Stagionalità!$B$11,0)</f>
-        <v/>
-      </c>
-      <c r="D49" s="19">
+        <f>ROUND((B$13+(B$14-B$13)*8/12)*Stagionalità!$B$11,0)</f>
+        <v/>
+      </c>
+      <c r="D49" s="20">
         <f>C49*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="E49" s="19">
+      <c r="E49" s="20">
         <f>C49*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="F49" s="19">
+      <c r="F49" s="20">
         <f>'Costi B2Brand'!$E$6</f>
         <v/>
       </c>
-      <c r="G49" s="19">
+      <c r="G49" s="20">
         <f>B$9</f>
         <v/>
       </c>
-      <c r="H49" s="19">
+      <c r="H49" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,H48-(E48-F48-G48)),0)</f>
         <v/>
       </c>
-      <c r="I49" s="19">
+      <c r="I49" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(E49,F49+G49+H49+0.5*MAX(0,(E49-F49-G49)-H49)),C49*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="J49" s="20">
+      <c r="J49" s="19">
         <f>I49-F49-G49</f>
         <v/>
       </c>
-      <c r="K49" s="19">
+      <c r="K49" s="20">
         <f>K48+J49</f>
         <v/>
       </c>
-      <c r="L49" s="20">
+      <c r="L49" s="19">
         <f>E49-I49</f>
         <v/>
       </c>
-      <c r="M49" s="19">
+      <c r="M49" s="20">
         <f>M48+L49</f>
         <v/>
       </c>
       <c r="N49" s="21">
-        <f>IF(J49&gt;=Ipotesi!$B$14,A49,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(E49-F49-G49)/2,J49)&gt;=Ipotesi!$B$14,A49,"")</f>
         <v/>
       </c>
       <c r="O49" s="21">
@@ -8516,51 +8664,51 @@
         <v>3</v>
       </c>
       <c r="S49" s="4">
-        <f>ROUND(C$5*Stagionalità!$B$11,0)</f>
-        <v/>
-      </c>
-      <c r="T49" s="19">
+        <f>ROUND((C$13+(C$14-C$13)*8/12)*Stagionalità!$B$11,0)</f>
+        <v/>
+      </c>
+      <c r="T49" s="20">
         <f>S49*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="U49" s="19">
+      <c r="U49" s="20">
         <f>S49*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="V49" s="19">
+      <c r="V49" s="20">
         <f>'Costi B2Brand'!$E$6</f>
         <v/>
       </c>
-      <c r="W49" s="19">
+      <c r="W49" s="20">
         <f>C$9</f>
         <v/>
       </c>
-      <c r="X49" s="19">
+      <c r="X49" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,X48-(U48-V48-W48)),0)</f>
         <v/>
       </c>
-      <c r="Y49" s="19">
+      <c r="Y49" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(U49,V49+W49+X49+0.5*MAX(0,(U49-V49-W49)-X49)),S49*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="Z49" s="20">
+      <c r="Z49" s="19">
         <f>Y49-V49-W49</f>
         <v/>
       </c>
-      <c r="AA49" s="19">
+      <c r="AA49" s="20">
         <f>AA48+Z49</f>
         <v/>
       </c>
-      <c r="AB49" s="20">
+      <c r="AB49" s="19">
         <f>U49-Y49</f>
         <v/>
       </c>
-      <c r="AC49" s="19">
+      <c r="AC49" s="20">
         <f>AC48+AB49</f>
         <v/>
       </c>
       <c r="AD49" s="21">
-        <f>IF(Z49&gt;=Ipotesi!$B$14,Q49,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(U49-V49-W49)/2,Z49)&gt;=Ipotesi!$B$14,Q49,"")</f>
         <v/>
       </c>
       <c r="AE49" s="21">
@@ -8574,51 +8722,51 @@
         <v>3</v>
       </c>
       <c r="AI49" s="4">
-        <f>ROUND(D$5*Stagionalità!$B$11,0)</f>
-        <v/>
-      </c>
-      <c r="AJ49" s="19">
+        <f>ROUND((D$13+(D$14-D$13)*8/12)*Stagionalità!$B$11,0)</f>
+        <v/>
+      </c>
+      <c r="AJ49" s="20">
         <f>AI49*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="AK49" s="19">
+      <c r="AK49" s="20">
         <f>AI49*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AL49" s="19">
+      <c r="AL49" s="20">
         <f>'Costi B2Brand'!$E$6</f>
         <v/>
       </c>
-      <c r="AM49" s="19">
+      <c r="AM49" s="20">
         <f>D$9</f>
         <v/>
       </c>
-      <c r="AN49" s="19">
+      <c r="AN49" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,AN48-(AK48-AL48-AM48)),0)</f>
         <v/>
       </c>
-      <c r="AO49" s="19">
+      <c r="AO49" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(AK49,AL49+AM49+AN49+0.5*MAX(0,(AK49-AL49-AM49)-AN49)),AI49*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AP49" s="20">
+      <c r="AP49" s="19">
         <f>AO49-AL49-AM49</f>
         <v/>
       </c>
-      <c r="AQ49" s="19">
+      <c r="AQ49" s="20">
         <f>AQ48+AP49</f>
         <v/>
       </c>
-      <c r="AR49" s="20">
+      <c r="AR49" s="19">
         <f>AK49-AO49</f>
         <v/>
       </c>
-      <c r="AS49" s="19">
+      <c r="AS49" s="20">
         <f>AS48+AR49</f>
         <v/>
       </c>
       <c r="AT49" s="21">
-        <f>IF(AP49&gt;=Ipotesi!$B$14,AG49,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(AK49-AL49-AM49)/2,AP49)&gt;=Ipotesi!$B$14,AG49,"")</f>
         <v/>
       </c>
       <c r="AU49" s="21">
@@ -8634,51 +8782,51 @@
         <v>3</v>
       </c>
       <c r="C50" s="4">
-        <f>ROUND(B$5*Stagionalità!$B$12,0)</f>
-        <v/>
-      </c>
-      <c r="D50" s="19">
+        <f>ROUND((B$13+(B$14-B$13)*9/12)*Stagionalità!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="D50" s="20">
         <f>C50*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="E50" s="19">
+      <c r="E50" s="20">
         <f>C50*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="F50" s="19">
+      <c r="F50" s="20">
         <f>'Costi B2Brand'!$E$6</f>
         <v/>
       </c>
-      <c r="G50" s="19">
+      <c r="G50" s="20">
         <f>B$9</f>
         <v/>
       </c>
-      <c r="H50" s="19">
+      <c r="H50" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,H49-(E49-F49-G49)),0)</f>
         <v/>
       </c>
-      <c r="I50" s="19">
+      <c r="I50" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(E50,F50+G50+H50+0.5*MAX(0,(E50-F50-G50)-H50)),C50*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="J50" s="20">
+      <c r="J50" s="19">
         <f>I50-F50-G50</f>
         <v/>
       </c>
-      <c r="K50" s="19">
+      <c r="K50" s="20">
         <f>K49+J50</f>
         <v/>
       </c>
-      <c r="L50" s="20">
+      <c r="L50" s="19">
         <f>E50-I50</f>
         <v/>
       </c>
-      <c r="M50" s="19">
+      <c r="M50" s="20">
         <f>M49+L50</f>
         <v/>
       </c>
       <c r="N50" s="21">
-        <f>IF(J50&gt;=Ipotesi!$B$14,A50,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(E50-F50-G50)/2,J50)&gt;=Ipotesi!$B$14,A50,"")</f>
         <v/>
       </c>
       <c r="O50" s="21">
@@ -8692,51 +8840,51 @@
         <v>3</v>
       </c>
       <c r="S50" s="4">
-        <f>ROUND(C$5*Stagionalità!$B$12,0)</f>
-        <v/>
-      </c>
-      <c r="T50" s="19">
+        <f>ROUND((C$13+(C$14-C$13)*9/12)*Stagionalità!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="T50" s="20">
         <f>S50*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="U50" s="19">
+      <c r="U50" s="20">
         <f>S50*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="V50" s="19">
+      <c r="V50" s="20">
         <f>'Costi B2Brand'!$E$6</f>
         <v/>
       </c>
-      <c r="W50" s="19">
+      <c r="W50" s="20">
         <f>C$9</f>
         <v/>
       </c>
-      <c r="X50" s="19">
+      <c r="X50" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,X49-(U49-V49-W49)),0)</f>
         <v/>
       </c>
-      <c r="Y50" s="19">
+      <c r="Y50" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(U50,V50+W50+X50+0.5*MAX(0,(U50-V50-W50)-X50)),S50*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="Z50" s="20">
+      <c r="Z50" s="19">
         <f>Y50-V50-W50</f>
         <v/>
       </c>
-      <c r="AA50" s="19">
+      <c r="AA50" s="20">
         <f>AA49+Z50</f>
         <v/>
       </c>
-      <c r="AB50" s="20">
+      <c r="AB50" s="19">
         <f>U50-Y50</f>
         <v/>
       </c>
-      <c r="AC50" s="19">
+      <c r="AC50" s="20">
         <f>AC49+AB50</f>
         <v/>
       </c>
       <c r="AD50" s="21">
-        <f>IF(Z50&gt;=Ipotesi!$B$14,Q50,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(U50-V50-W50)/2,Z50)&gt;=Ipotesi!$B$14,Q50,"")</f>
         <v/>
       </c>
       <c r="AE50" s="21">
@@ -8750,51 +8898,51 @@
         <v>3</v>
       </c>
       <c r="AI50" s="4">
-        <f>ROUND(D$5*Stagionalità!$B$12,0)</f>
-        <v/>
-      </c>
-      <c r="AJ50" s="19">
+        <f>ROUND((D$13+(D$14-D$13)*9/12)*Stagionalità!$B$12,0)</f>
+        <v/>
+      </c>
+      <c r="AJ50" s="20">
         <f>AI50*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="AK50" s="19">
+      <c r="AK50" s="20">
         <f>AI50*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AL50" s="19">
+      <c r="AL50" s="20">
         <f>'Costi B2Brand'!$E$6</f>
         <v/>
       </c>
-      <c r="AM50" s="19">
+      <c r="AM50" s="20">
         <f>D$9</f>
         <v/>
       </c>
-      <c r="AN50" s="19">
+      <c r="AN50" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,AN49-(AK49-AL49-AM49)),0)</f>
         <v/>
       </c>
-      <c r="AO50" s="19">
+      <c r="AO50" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(AK50,AL50+AM50+AN50+0.5*MAX(0,(AK50-AL50-AM50)-AN50)),AI50*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AP50" s="20">
+      <c r="AP50" s="19">
         <f>AO50-AL50-AM50</f>
         <v/>
       </c>
-      <c r="AQ50" s="19">
+      <c r="AQ50" s="20">
         <f>AQ49+AP50</f>
         <v/>
       </c>
-      <c r="AR50" s="20">
+      <c r="AR50" s="19">
         <f>AK50-AO50</f>
         <v/>
       </c>
-      <c r="AS50" s="19">
+      <c r="AS50" s="20">
         <f>AS49+AR50</f>
         <v/>
       </c>
       <c r="AT50" s="21">
-        <f>IF(AP50&gt;=Ipotesi!$B$14,AG50,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(AK50-AL50-AM50)/2,AP50)&gt;=Ipotesi!$B$14,AG50,"")</f>
         <v/>
       </c>
       <c r="AU50" s="21">
@@ -8810,51 +8958,51 @@
         <v>3</v>
       </c>
       <c r="C51" s="4">
-        <f>ROUND(B$5*Stagionalità!$B$13,0)</f>
-        <v/>
-      </c>
-      <c r="D51" s="19">
+        <f>ROUND((B$13+(B$14-B$13)*10/12)*Stagionalità!$B$13,0)</f>
+        <v/>
+      </c>
+      <c r="D51" s="20">
         <f>C51*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="E51" s="19">
+      <c r="E51" s="20">
         <f>C51*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="F51" s="19">
+      <c r="F51" s="20">
         <f>'Costi B2Brand'!$E$6</f>
         <v/>
       </c>
-      <c r="G51" s="19">
+      <c r="G51" s="20">
         <f>B$9</f>
         <v/>
       </c>
-      <c r="H51" s="19">
+      <c r="H51" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,H50-(E50-F50-G50)),0)</f>
         <v/>
       </c>
-      <c r="I51" s="19">
+      <c r="I51" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(E51,F51+G51+H51+0.5*MAX(0,(E51-F51-G51)-H51)),C51*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="J51" s="20">
+      <c r="J51" s="19">
         <f>I51-F51-G51</f>
         <v/>
       </c>
-      <c r="K51" s="19">
+      <c r="K51" s="20">
         <f>K50+J51</f>
         <v/>
       </c>
-      <c r="L51" s="20">
+      <c r="L51" s="19">
         <f>E51-I51</f>
         <v/>
       </c>
-      <c r="M51" s="19">
+      <c r="M51" s="20">
         <f>M50+L51</f>
         <v/>
       </c>
       <c r="N51" s="21">
-        <f>IF(J51&gt;=Ipotesi!$B$14,A51,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(E51-F51-G51)/2,J51)&gt;=Ipotesi!$B$14,A51,"")</f>
         <v/>
       </c>
       <c r="O51" s="21">
@@ -8868,51 +9016,51 @@
         <v>3</v>
       </c>
       <c r="S51" s="4">
-        <f>ROUND(C$5*Stagionalità!$B$13,0)</f>
-        <v/>
-      </c>
-      <c r="T51" s="19">
+        <f>ROUND((C$13+(C$14-C$13)*10/12)*Stagionalità!$B$13,0)</f>
+        <v/>
+      </c>
+      <c r="T51" s="20">
         <f>S51*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="U51" s="19">
+      <c r="U51" s="20">
         <f>S51*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="V51" s="19">
+      <c r="V51" s="20">
         <f>'Costi B2Brand'!$E$6</f>
         <v/>
       </c>
-      <c r="W51" s="19">
+      <c r="W51" s="20">
         <f>C$9</f>
         <v/>
       </c>
-      <c r="X51" s="19">
+      <c r="X51" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,X50-(U50-V50-W50)),0)</f>
         <v/>
       </c>
-      <c r="Y51" s="19">
+      <c r="Y51" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(U51,V51+W51+X51+0.5*MAX(0,(U51-V51-W51)-X51)),S51*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="Z51" s="20">
+      <c r="Z51" s="19">
         <f>Y51-V51-W51</f>
         <v/>
       </c>
-      <c r="AA51" s="19">
+      <c r="AA51" s="20">
         <f>AA50+Z51</f>
         <v/>
       </c>
-      <c r="AB51" s="20">
+      <c r="AB51" s="19">
         <f>U51-Y51</f>
         <v/>
       </c>
-      <c r="AC51" s="19">
+      <c r="AC51" s="20">
         <f>AC50+AB51</f>
         <v/>
       </c>
       <c r="AD51" s="21">
-        <f>IF(Z51&gt;=Ipotesi!$B$14,Q51,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(U51-V51-W51)/2,Z51)&gt;=Ipotesi!$B$14,Q51,"")</f>
         <v/>
       </c>
       <c r="AE51" s="21">
@@ -8926,51 +9074,51 @@
         <v>3</v>
       </c>
       <c r="AI51" s="4">
-        <f>ROUND(D$5*Stagionalità!$B$13,0)</f>
-        <v/>
-      </c>
-      <c r="AJ51" s="19">
+        <f>ROUND((D$13+(D$14-D$13)*10/12)*Stagionalità!$B$13,0)</f>
+        <v/>
+      </c>
+      <c r="AJ51" s="20">
         <f>AI51*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="AK51" s="19">
+      <c r="AK51" s="20">
         <f>AI51*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AL51" s="19">
+      <c r="AL51" s="20">
         <f>'Costi B2Brand'!$E$6</f>
         <v/>
       </c>
-      <c r="AM51" s="19">
+      <c r="AM51" s="20">
         <f>D$9</f>
         <v/>
       </c>
-      <c r="AN51" s="19">
+      <c r="AN51" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,AN50-(AK50-AL50-AM50)),0)</f>
         <v/>
       </c>
-      <c r="AO51" s="19">
+      <c r="AO51" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(AK51,AL51+AM51+AN51+0.5*MAX(0,(AK51-AL51-AM51)-AN51)),AI51*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AP51" s="20">
+      <c r="AP51" s="19">
         <f>AO51-AL51-AM51</f>
         <v/>
       </c>
-      <c r="AQ51" s="19">
+      <c r="AQ51" s="20">
         <f>AQ50+AP51</f>
         <v/>
       </c>
-      <c r="AR51" s="20">
+      <c r="AR51" s="19">
         <f>AK51-AO51</f>
         <v/>
       </c>
-      <c r="AS51" s="19">
+      <c r="AS51" s="20">
         <f>AS50+AR51</f>
         <v/>
       </c>
       <c r="AT51" s="21">
-        <f>IF(AP51&gt;=Ipotesi!$B$14,AG51,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(AK51-AL51-AM51)/2,AP51)&gt;=Ipotesi!$B$14,AG51,"")</f>
         <v/>
       </c>
       <c r="AU51" s="21">
@@ -8986,51 +9134,51 @@
         <v>3</v>
       </c>
       <c r="C52" s="4">
-        <f>ROUND(B$5*Stagionalità!$B$2,0)</f>
-        <v/>
-      </c>
-      <c r="D52" s="19">
+        <f>ROUND((B$13+(B$14-B$13)*11/12)*Stagionalità!$B$2,0)</f>
+        <v/>
+      </c>
+      <c r="D52" s="20">
         <f>C52*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="E52" s="19">
+      <c r="E52" s="20">
         <f>C52*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="F52" s="19">
+      <c r="F52" s="20">
         <f>'Costi B2Brand'!$E$6</f>
         <v/>
       </c>
-      <c r="G52" s="19">
+      <c r="G52" s="20">
         <f>B$9</f>
         <v/>
       </c>
-      <c r="H52" s="19">
+      <c r="H52" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,H51-(E51-F51-G51)),0)</f>
         <v/>
       </c>
-      <c r="I52" s="19">
+      <c r="I52" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(E52,F52+G52+H52+0.5*MAX(0,(E52-F52-G52)-H52)),C52*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="J52" s="20">
+      <c r="J52" s="19">
         <f>I52-F52-G52</f>
         <v/>
       </c>
-      <c r="K52" s="19">
+      <c r="K52" s="20">
         <f>K51+J52</f>
         <v/>
       </c>
-      <c r="L52" s="20">
+      <c r="L52" s="19">
         <f>E52-I52</f>
         <v/>
       </c>
-      <c r="M52" s="19">
+      <c r="M52" s="20">
         <f>M51+L52</f>
         <v/>
       </c>
       <c r="N52" s="21">
-        <f>IF(J52&gt;=Ipotesi!$B$14,A52,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(E52-F52-G52)/2,J52)&gt;=Ipotesi!$B$14,A52,"")</f>
         <v/>
       </c>
       <c r="O52" s="21">
@@ -9044,51 +9192,51 @@
         <v>3</v>
       </c>
       <c r="S52" s="4">
-        <f>ROUND(C$5*Stagionalità!$B$2,0)</f>
-        <v/>
-      </c>
-      <c r="T52" s="19">
+        <f>ROUND((C$13+(C$14-C$13)*11/12)*Stagionalità!$B$2,0)</f>
+        <v/>
+      </c>
+      <c r="T52" s="20">
         <f>S52*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="U52" s="19">
+      <c r="U52" s="20">
         <f>S52*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="V52" s="19">
+      <c r="V52" s="20">
         <f>'Costi B2Brand'!$E$6</f>
         <v/>
       </c>
-      <c r="W52" s="19">
+      <c r="W52" s="20">
         <f>C$9</f>
         <v/>
       </c>
-      <c r="X52" s="19">
+      <c r="X52" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,X51-(U51-V51-W51)),0)</f>
         <v/>
       </c>
-      <c r="Y52" s="19">
+      <c r="Y52" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(U52,V52+W52+X52+0.5*MAX(0,(U52-V52-W52)-X52)),S52*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="Z52" s="20">
+      <c r="Z52" s="19">
         <f>Y52-V52-W52</f>
         <v/>
       </c>
-      <c r="AA52" s="19">
+      <c r="AA52" s="20">
         <f>AA51+Z52</f>
         <v/>
       </c>
-      <c r="AB52" s="20">
+      <c r="AB52" s="19">
         <f>U52-Y52</f>
         <v/>
       </c>
-      <c r="AC52" s="19">
+      <c r="AC52" s="20">
         <f>AC51+AB52</f>
         <v/>
       </c>
       <c r="AD52" s="21">
-        <f>IF(Z52&gt;=Ipotesi!$B$14,Q52,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(U52-V52-W52)/2,Z52)&gt;=Ipotesi!$B$14,Q52,"")</f>
         <v/>
       </c>
       <c r="AE52" s="21">
@@ -9102,51 +9250,51 @@
         <v>3</v>
       </c>
       <c r="AI52" s="4">
-        <f>ROUND(D$5*Stagionalità!$B$2,0)</f>
-        <v/>
-      </c>
-      <c r="AJ52" s="19">
+        <f>ROUND((D$13+(D$14-D$13)*11/12)*Stagionalità!$B$2,0)</f>
+        <v/>
+      </c>
+      <c r="AJ52" s="20">
         <f>AI52*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="AK52" s="19">
+      <c r="AK52" s="20">
         <f>AI52*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AL52" s="19">
+      <c r="AL52" s="20">
         <f>'Costi B2Brand'!$E$6</f>
         <v/>
       </c>
-      <c r="AM52" s="19">
+      <c r="AM52" s="20">
         <f>D$9</f>
         <v/>
       </c>
-      <c r="AN52" s="19">
+      <c r="AN52" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,AN51-(AK51-AL51-AM51)),0)</f>
         <v/>
       </c>
-      <c r="AO52" s="19">
+      <c r="AO52" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(AK52,AL52+AM52+AN52+0.5*MAX(0,(AK52-AL52-AM52)-AN52)),AI52*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AP52" s="20">
+      <c r="AP52" s="19">
         <f>AO52-AL52-AM52</f>
         <v/>
       </c>
-      <c r="AQ52" s="19">
+      <c r="AQ52" s="20">
         <f>AQ51+AP52</f>
         <v/>
       </c>
-      <c r="AR52" s="20">
+      <c r="AR52" s="19">
         <f>AK52-AO52</f>
         <v/>
       </c>
-      <c r="AS52" s="19">
+      <c r="AS52" s="20">
         <f>AS51+AR52</f>
         <v/>
       </c>
       <c r="AT52" s="21">
-        <f>IF(AP52&gt;=Ipotesi!$B$14,AG52,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(AK52-AL52-AM52)/2,AP52)&gt;=Ipotesi!$B$14,AG52,"")</f>
         <v/>
       </c>
       <c r="AU52" s="21">
@@ -9162,51 +9310,51 @@
         <v>3</v>
       </c>
       <c r="C53" s="4">
-        <f>ROUND(B$5*Stagionalità!$B$3,0)</f>
-        <v/>
-      </c>
-      <c r="D53" s="19">
+        <f>ROUND((B$13+(B$14-B$13)*12/12)*Stagionalità!$B$3,0)</f>
+        <v/>
+      </c>
+      <c r="D53" s="20">
         <f>C53*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="E53" s="19">
+      <c r="E53" s="20">
         <f>C53*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="F53" s="19">
+      <c r="F53" s="20">
         <f>'Costi B2Brand'!$E$6</f>
         <v/>
       </c>
-      <c r="G53" s="19">
+      <c r="G53" s="20">
         <f>B$9</f>
         <v/>
       </c>
-      <c r="H53" s="19">
+      <c r="H53" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,H52-(E52-F52-G52)),0)</f>
         <v/>
       </c>
-      <c r="I53" s="19">
+      <c r="I53" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(E53,F53+G53+H53+0.5*MAX(0,(E53-F53-G53)-H53)),C53*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="J53" s="20">
+      <c r="J53" s="19">
         <f>I53-F53-G53</f>
         <v/>
       </c>
-      <c r="K53" s="19">
+      <c r="K53" s="20">
         <f>K52+J53</f>
         <v/>
       </c>
-      <c r="L53" s="20">
+      <c r="L53" s="19">
         <f>E53-I53</f>
         <v/>
       </c>
-      <c r="M53" s="19">
+      <c r="M53" s="20">
         <f>M52+L53</f>
         <v/>
       </c>
       <c r="N53" s="21">
-        <f>IF(J53&gt;=Ipotesi!$B$14,A53,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(E53-F53-G53)/2,J53)&gt;=Ipotesi!$B$14,A53,"")</f>
         <v/>
       </c>
       <c r="O53" s="21">
@@ -9220,51 +9368,51 @@
         <v>3</v>
       </c>
       <c r="S53" s="4">
-        <f>ROUND(C$5*Stagionalità!$B$3,0)</f>
-        <v/>
-      </c>
-      <c r="T53" s="19">
+        <f>ROUND((C$13+(C$14-C$13)*12/12)*Stagionalità!$B$3,0)</f>
+        <v/>
+      </c>
+      <c r="T53" s="20">
         <f>S53*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="U53" s="19">
+      <c r="U53" s="20">
         <f>S53*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="V53" s="19">
+      <c r="V53" s="20">
         <f>'Costi B2Brand'!$E$6</f>
         <v/>
       </c>
-      <c r="W53" s="19">
+      <c r="W53" s="20">
         <f>C$9</f>
         <v/>
       </c>
-      <c r="X53" s="19">
+      <c r="X53" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,X52-(U52-V52-W52)),0)</f>
         <v/>
       </c>
-      <c r="Y53" s="19">
+      <c r="Y53" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(U53,V53+W53+X53+0.5*MAX(0,(U53-V53-W53)-X53)),S53*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="Z53" s="20">
+      <c r="Z53" s="19">
         <f>Y53-V53-W53</f>
         <v/>
       </c>
-      <c r="AA53" s="19">
+      <c r="AA53" s="20">
         <f>AA52+Z53</f>
         <v/>
       </c>
-      <c r="AB53" s="20">
+      <c r="AB53" s="19">
         <f>U53-Y53</f>
         <v/>
       </c>
-      <c r="AC53" s="19">
+      <c r="AC53" s="20">
         <f>AC52+AB53</f>
         <v/>
       </c>
       <c r="AD53" s="21">
-        <f>IF(Z53&gt;=Ipotesi!$B$14,Q53,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(U53-V53-W53)/2,Z53)&gt;=Ipotesi!$B$14,Q53,"")</f>
         <v/>
       </c>
       <c r="AE53" s="21">
@@ -9278,51 +9426,51 @@
         <v>3</v>
       </c>
       <c r="AI53" s="4">
-        <f>ROUND(D$5*Stagionalità!$B$3,0)</f>
-        <v/>
-      </c>
-      <c r="AJ53" s="19">
+        <f>ROUND((D$13+(D$14-D$13)*12/12)*Stagionalità!$B$3,0)</f>
+        <v/>
+      </c>
+      <c r="AJ53" s="20">
         <f>AI53*'Conti per prodotto'!$B$10</f>
         <v/>
       </c>
-      <c r="AK53" s="19">
+      <c r="AK53" s="20">
         <f>AI53*('Conti per prodotto'!$O$10+'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AL53" s="19">
+      <c r="AL53" s="20">
         <f>'Costi B2Brand'!$E$6</f>
         <v/>
       </c>
-      <c r="AM53" s="19">
+      <c r="AM53" s="20">
         <f>D$9</f>
         <v/>
       </c>
-      <c r="AN53" s="19">
+      <c r="AN53" s="20">
         <f>IF(Ipotesi!$B$15="margine",MAX(0,AN52-(AK52-AL52-AM52)),0)</f>
         <v/>
       </c>
-      <c r="AO53" s="19">
+      <c r="AO53" s="20">
         <f>IF(Ipotesi!$B$15="margine",MIN(AK53,AL53+AM53+AN53+0.5*MAX(0,(AK53-AL53-AM53)-AN53)),AI53*'Conti per prodotto'!$I$10)</f>
         <v/>
       </c>
-      <c r="AP53" s="20">
+      <c r="AP53" s="19">
         <f>AO53-AL53-AM53</f>
         <v/>
       </c>
-      <c r="AQ53" s="19">
+      <c r="AQ53" s="20">
         <f>AQ52+AP53</f>
         <v/>
       </c>
-      <c r="AR53" s="20">
+      <c r="AR53" s="19">
         <f>AK53-AO53</f>
         <v/>
       </c>
-      <c r="AS53" s="19">
+      <c r="AS53" s="20">
         <f>AS52+AR53</f>
         <v/>
       </c>
       <c r="AT53" s="21">
-        <f>IF(AP53&gt;=Ipotesi!$B$14,AG53,"")</f>
+        <f>IF(IF(Ipotesi!$B$15="margine",(AK53-AL53-AM53)/2,AP53)&gt;=Ipotesi!$B$14,AG53,"")</f>
         <v/>
       </c>
       <c r="AU53" s="21">
@@ -9651,7 +9799,7 @@
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>Primo mese con B2Brand ≥ obiettivo</t>
+          <t>Primo mese a quota obiettivo (con «margine»: metà del guadagno del mese)</t>
         </is>
       </c>
       <c r="D61" s="22">
@@ -9660,7 +9808,7 @@
       </c>
       <c r="Q61" s="6" t="inlineStr">
         <is>
-          <t>Primo mese con B2Brand ≥ obiettivo</t>
+          <t>Primo mese a quota obiettivo (con «margine»: metà del guadagno del mese)</t>
         </is>
       </c>
       <c r="T61" s="22">
@@ -9669,7 +9817,7 @@
       </c>
       <c r="AG61" s="6" t="inlineStr">
         <is>
-          <t>Primo mese con B2Brand ≥ obiettivo</t>
+          <t>Primo mese a quota obiettivo (con «margine»: metà del guadagno del mese)</t>
         </is>
       </c>
       <c r="AJ61" s="22">
@@ -10068,17 +10216,17 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>0.015</v>
+        <v>0.012</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>0.02</v>
+        <v>0.016</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>0.025</v>
+        <v>0.019</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>tasso di conversione del sito (ordini ÷ visite)</t>
+          <t>da 0,8% (negozio nuovo) a 2,2%; mediana piccoli Shopify 1,4% (Littledata 09/2026); Food &amp; Drink UK 1,58% (IRP 08/2026) — 02 §1.1 e §3</t>
         </is>
       </c>
     </row>
@@ -10089,17 +10237,17 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="C6" s="26" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D6" s="26" t="n">
         <v>0.35</v>
       </c>
-      <c r="D6" s="26" t="n">
-        <v>0.45</v>
-      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>quota degli ordini fatta da clienti che hanno già comprato</t>
+          <t>riacquisto medio simulato (02 §2.3): nei prodotti di consumo ricompra entro un anno il 30-40% dei clienti</t>
         </is>
       </c>
     </row>
@@ -10110,17 +10258,17 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C7" s="27" t="n">
         <v>0.7</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>costo medio di un clic a pagamento (€)</t>
+          <t>clic medio fra Google Shopping (~0,55 €) e Meta (~1 €) — 05 §5, 02 §2.1</t>
         </is>
       </c>
     </row>
@@ -10131,17 +10279,17 @@
         </is>
       </c>
       <c r="B8" s="27" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C8" s="27" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D8" s="27" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>costo pubblicitario per un cliente nuovo (€)</t>
+          <t>benchmark food 25-50 € (02 §1.5); sostenibile ≤ 20 € con ordine medio 28 €, ≤ 29 € con 40 €</t>
         </is>
       </c>
     </row>
@@ -10152,17 +10300,17 @@
         </is>
       </c>
       <c r="B9" s="26" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="C9" s="26" t="n">
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
       <c r="D9" s="26" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>quota degli ordini che arriva dalla newsletter</t>
+          <t>simulazione 02 §2.4 (13-23%); media degli account Klaviyo 19% del fatturato</t>
         </is>
       </c>
     </row>
@@ -10173,17 +10321,17 @@
         </is>
       </c>
       <c r="B10" s="28" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="C10" s="28" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="D10" s="28" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ordini al mese ogni 1.000 iscritti alla newsletter</t>
+          <t>4 campagne al mese × 0,17% + benvenuto e carrelli (02 §2.1 e §2.4)</t>
         </is>
       </c>
     </row>
@@ -10193,15 +10341,15 @@
           <t>Ordini al mese (obiettivo a regime)</t>
         </is>
       </c>
-      <c r="B12" s="20">
+      <c r="B12" s="19">
         <f>Scenari!$D$3</f>
         <v/>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="19">
         <f>Scenari!$D$4</f>
         <v/>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="19">
         <f>Scenari!$D$5</f>
         <v/>
       </c>
@@ -10212,15 +10360,15 @@
           <t>Pubblicità al mese (€)</t>
         </is>
       </c>
-      <c r="B13" s="20">
+      <c r="B13" s="19">
         <f>Scenari!$D$7</f>
         <v/>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="19">
         <f>Scenari!$D$8</f>
         <v/>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="19">
         <f>Scenari!$D$9</f>
         <v/>
       </c>
@@ -10231,15 +10379,15 @@
           <t>Visite al mese necessarie</t>
         </is>
       </c>
-      <c r="B14" s="20">
+      <c r="B14" s="19">
         <f>ROUND(B12/B5,0)</f>
         <v/>
       </c>
-      <c r="C14" s="20">
+      <c r="C14" s="19">
         <f>ROUND(C12/C5,0)</f>
         <v/>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="19">
         <f>ROUND(D12/D5,0)</f>
         <v/>
       </c>
@@ -10250,15 +10398,15 @@
           <t>…di cui comprate con la pubblicità</t>
         </is>
       </c>
-      <c r="B15" s="20">
+      <c r="B15" s="19">
         <f>ROUND(B13/B7,0)</f>
         <v/>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="19">
         <f>ROUND(C13/C7,0)</f>
         <v/>
       </c>
-      <c r="D15" s="20">
+      <c r="D15" s="19">
         <f>ROUND(D13/D7,0)</f>
         <v/>
       </c>
@@ -10269,15 +10417,15 @@
           <t>…di cui da portare gratis (Google, social, eventi, passaparola)</t>
         </is>
       </c>
-      <c r="B16" s="20">
+      <c r="B16" s="19">
         <f>MAX(0,B14-B15)</f>
         <v/>
       </c>
-      <c r="C16" s="20">
+      <c r="C16" s="19">
         <f>MAX(0,C14-C15)</f>
         <v/>
       </c>
-      <c r="D16" s="20">
+      <c r="D16" s="19">
         <f>MAX(0,D14-D15)</f>
         <v/>
       </c>
@@ -10288,15 +10436,15 @@
           <t>Clienti nuovi al mese</t>
         </is>
       </c>
-      <c r="B17" s="20">
+      <c r="B17" s="19">
         <f>ROUND(B12*(1-B6),0)</f>
         <v/>
       </c>
-      <c r="C17" s="20">
+      <c r="C17" s="19">
         <f>ROUND(C12*(1-C6),0)</f>
         <v/>
       </c>
-      <c r="D17" s="20">
+      <c r="D17" s="19">
         <f>ROUND(D12*(1-D6),0)</f>
         <v/>
       </c>
@@ -10307,15 +10455,15 @@
           <t>…di cui comprati con la pubblicità</t>
         </is>
       </c>
-      <c r="B18" s="20">
+      <c r="B18" s="19">
         <f>ROUND(B13/B8,0)</f>
         <v/>
       </c>
-      <c r="C18" s="20">
+      <c r="C18" s="19">
         <f>ROUND(C13/C8,0)</f>
         <v/>
       </c>
-      <c r="D18" s="20">
+      <c r="D18" s="19">
         <f>ROUND(D13/D8,0)</f>
         <v/>
       </c>
@@ -10326,15 +10474,15 @@
           <t>…di cui da trovare gratis</t>
         </is>
       </c>
-      <c r="B19" s="20">
+      <c r="B19" s="19">
         <f>MAX(0,B17-B18)</f>
         <v/>
       </c>
-      <c r="C19" s="20">
+      <c r="C19" s="19">
         <f>MAX(0,C17-C18)</f>
         <v/>
       </c>
-      <c r="D19" s="20">
+      <c r="D19" s="19">
         <f>MAX(0,D17-D18)</f>
         <v/>
       </c>
@@ -10345,15 +10493,15 @@
           <t>Ordini di clienti che ritornano</t>
         </is>
       </c>
-      <c r="B20" s="20">
+      <c r="B20" s="19">
         <f>ROUND(B12*B6,0)</f>
         <v/>
       </c>
-      <c r="C20" s="20">
+      <c r="C20" s="19">
         <f>ROUND(C12*C6,0)</f>
         <v/>
       </c>
-      <c r="D20" s="20">
+      <c r="D20" s="19">
         <f>ROUND(D12*D6,0)</f>
         <v/>
       </c>
@@ -10364,15 +10512,15 @@
           <t>Ordini dalla newsletter</t>
         </is>
       </c>
-      <c r="B21" s="20">
+      <c r="B21" s="19">
         <f>ROUND(B12*B9,0)</f>
         <v/>
       </c>
-      <c r="C21" s="20">
+      <c r="C21" s="19">
         <f>ROUND(C12*C9,0)</f>
         <v/>
       </c>
-      <c r="D21" s="20">
+      <c r="D21" s="19">
         <f>ROUND(D12*D9,0)</f>
         <v/>
       </c>
@@ -10383,15 +10531,15 @@
           <t>Iscritti alla newsletter necessari</t>
         </is>
       </c>
-      <c r="B22" s="20">
+      <c r="B22" s="19">
         <f>ROUND(B21/B10*1000,0)</f>
         <v/>
       </c>
-      <c r="C22" s="20">
+      <c r="C22" s="19">
         <f>ROUND(C21/C10*1000,0)</f>
         <v/>
       </c>
-      <c r="D22" s="20">
+      <c r="D22" s="19">
         <f>ROUND(D21/D10*1000,0)</f>
         <v/>
       </c>
